--- a/股票損益&房貸試算收入試算.xlsx
+++ b/股票損益&房貸試算收入試算.xlsx
@@ -87,14 +87,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112">
-  <si>
-    <t>(單位:萬元)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113">
   <si>
     <t>股利+借券</t>
   </si>
   <si>
+    <t>正二</t>
+  </si>
+  <si>
     <t>台積電</t>
   </si>
   <si>
@@ -125,6 +125,9 @@
     <t>淨收入</t>
   </si>
   <si>
+    <t>裕慶-KY</t>
+  </si>
+  <si>
     <t>正二(借券)</t>
   </si>
   <si>
@@ -140,36 +143,36 @@
     <t>質借兩次</t>
   </si>
   <si>
+    <t>借出的股票</t>
+  </si>
+  <si>
+    <t>張數</t>
+  </si>
+  <si>
+    <t>成本</t>
+  </si>
+  <si>
+    <t>現價</t>
+  </si>
+  <si>
+    <t>出借收入</t>
+  </si>
+  <si>
     <t>未實</t>
   </si>
   <si>
+    <t>裕慶</t>
+  </si>
+  <si>
     <t>已實</t>
   </si>
   <si>
-    <t>借出的股票</t>
-  </si>
-  <si>
     <t>共賺</t>
   </si>
   <si>
-    <t>張數</t>
-  </si>
-  <si>
-    <t>成本</t>
-  </si>
-  <si>
-    <t>現價</t>
-  </si>
-  <si>
-    <t>出借收入</t>
-  </si>
-  <si>
     <t>扣掉去年未實(這才是真正的YTD)</t>
   </si>
   <si>
-    <t>正二</t>
-  </si>
-  <si>
     <t>皇鼎</t>
   </si>
   <si>
@@ -395,7 +398,7 @@
     <t>補加上房貸已繳的錢</t>
   </si>
   <si>
-    <t>第十期工程款</t>
+    <t>第11期工程款</t>
   </si>
   <si>
     <t>LINE</t>
@@ -407,7 +410,7 @@
     <t>股利</t>
   </si>
   <si>
-    <t>借券收入</t>
+    <t>台積電4/9</t>
   </si>
   <si>
     <t>股票尚未交割金額</t>
@@ -430,17 +433,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="13">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="178" formatCode="m/d;@"/>
     <numFmt numFmtId="179" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
-    <numFmt numFmtId="180" formatCode="m/d;@"/>
-    <numFmt numFmtId="181" formatCode="0.0%"/>
-    <numFmt numFmtId="182" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="181" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="182" formatCode="0.0%"/>
     <numFmt numFmtId="183" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="184" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
@@ -480,6 +483,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -505,14 +522,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F76"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -526,9 +536,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -550,20 +559,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,7 +569,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -595,6 +590,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -603,15 +612,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -638,13 +641,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -656,19 +659,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -680,7 +677,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -698,13 +695,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -722,7 +755,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,13 +767,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -752,73 +815,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,6 +929,30 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -943,21 +970,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -982,21 +994,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1012,11 +1009,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1025,148 +1028,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="28" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1180,40 +1183,40 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1240,16 +1243,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1258,10 +1261,10 @@
     <xf numFmtId="179" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1273,7 +1276,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1288,7 +1291,7 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
@@ -1309,7 +1312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1626,14 +1629,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="A1:AC209"/>
+  <dimension ref="A1:AC213"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="10.1111111111111"/>
     <col min="3" max="3" width="14.6666666666667" customWidth="1"/>
     <col min="4" max="4" width="12.2222222222222" style="1"/>
-    <col min="5" max="5" width="10.4444444444444" style="1"/>
+    <col min="5" max="5" width="11.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
     <col min="8" max="8" width="11.5555555555556"/>
     <col min="9" max="9" width="13.1111111111111" customWidth="1"/>
@@ -1650,7 +1653,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="17">
-        <f>D28+D46+D66+D83+D106+D116</f>
+        <f>D32+D50+D70+D87+D110+D120</f>
         <v>8235533</v>
       </c>
       <c r="C1" s="17"/>
@@ -1658,7 +1661,7 @@
     <row r="2" spans="1:16">
       <c r="A2" s="17">
         <f>A1+M8</f>
-        <v>12516374</v>
+        <v>10128546</v>
       </c>
       <c r="C2" s="17"/>
       <c r="O2" s="1">
@@ -1685,24 +1688,28 @@
       <c r="B4" s="18">
         <v>2026</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>0</v>
-      </c>
+      <c r="C4" s="19"/>
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="19"/>
       <c r="G4" s="21" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="35">
-        <f>SUM($I5:$I14)</f>
-        <v>54650</v>
+        <f>SUM($I5:$I18)</f>
+        <v>116360</v>
       </c>
       <c r="J4" s="36"/>
     </row>
     <row r="5" spans="2:22">
       <c r="B5" s="22"/>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1273965</v>
+      </c>
       <c r="G5" s="23">
         <v>45665</v>
       </c>
@@ -1717,7 +1724,7 @@
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <v>54650</v>
+        <v>6369897</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>4</v>
@@ -1746,21 +1753,31 @@
     </row>
     <row r="6" spans="2:22">
       <c r="B6" s="22"/>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-16424</v>
+      </c>
       <c r="G6" s="4">
         <v>46055</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I6" s="1">
         <v>6650</v>
       </c>
       <c r="J6" s="37"/>
       <c r="L6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" s="1">
-        <v>9460301</v>
+        <v>803226</v>
+      </c>
+      <c r="N6" s="1">
+        <f>Q12</f>
+        <v>-46000</v>
       </c>
       <c r="O6" s="1">
         <v>12000000</v>
@@ -1793,46 +1810,60 @@
     </row>
     <row r="7" ht="16.95" spans="2:23">
       <c r="B7" s="22"/>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4995996</v>
+      </c>
       <c r="E7" s="13"/>
-      <c r="G7" s="4"/>
-      <c r="I7" s="1"/>
+      <c r="G7" s="4">
+        <v>46121</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>61710</v>
+      </c>
       <c r="J7" s="37"/>
       <c r="L7" s="25" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" s="9">
         <v>5234110</v>
       </c>
       <c r="R7" s="39"/>
       <c r="S7" s="1">
-        <f>S6/12</f>
+        <f t="shared" ref="S7:V7" si="0">S6/12</f>
         <v>93333.3333333333</v>
       </c>
       <c r="T7" s="39"/>
       <c r="U7" s="1">
-        <f>U6/12</f>
+        <f t="shared" si="0"/>
         <v>26000</v>
       </c>
       <c r="V7" s="1">
-        <f>V6/12</f>
+        <f t="shared" si="0"/>
         <v>67333.3333333333</v>
       </c>
       <c r="W7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:22">
       <c r="B8" s="22"/>
+      <c r="E8" s="13"/>
       <c r="G8" s="4"/>
       <c r="I8" s="1"/>
       <c r="J8" s="37"/>
       <c r="L8"/>
       <c r="M8" s="1">
-        <f>M5+M6-M7</f>
-        <v>4280841</v>
+        <f>M5+M6-M7+N6</f>
+        <v>1893013</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
@@ -1840,9 +1871,7 @@
     </row>
     <row r="9" spans="2:22">
       <c r="B9" s="22"/>
-      <c r="C9" t="s">
-        <v>17</v>
-      </c>
+      <c r="E9" s="13"/>
       <c r="G9" s="4"/>
       <c r="I9" s="1"/>
       <c r="J9" s="37"/>
@@ -1866,55 +1895,47 @@
     </row>
     <row r="10" spans="2:22">
       <c r="B10" s="22"/>
-      <c r="C10" t="s">
-        <v>18</v>
-      </c>
+      <c r="E10" s="13"/>
       <c r="G10" s="4"/>
       <c r="I10" s="1"/>
       <c r="J10" s="37"/>
       <c r="L10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S10" s="1">
-        <f>S9/12</f>
+        <f t="shared" ref="S10:V10" si="1">S9/12</f>
         <v>114333.333333333</v>
       </c>
       <c r="T10" s="1"/>
       <c r="U10" s="1">
-        <f>U9/12</f>
+        <f t="shared" si="1"/>
         <v>38600</v>
       </c>
       <c r="V10" s="1">
-        <f>V9/12</f>
+        <f t="shared" si="1"/>
         <v>75733.3333333333</v>
       </c>
     </row>
     <row r="11" spans="2:22">
       <c r="B11" s="22"/>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="1">
-        <f>D9+D10</f>
-        <v>0</v>
-      </c>
+      <c r="E11" s="13"/>
       <c r="G11" s="4"/>
       <c r="I11" s="1"/>
       <c r="J11" s="37"/>
       <c r="M11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
@@ -1922,38 +1943,31 @@
     </row>
     <row r="12" spans="2:22">
       <c r="B12" s="22"/>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" s="1">
-        <f>D11-D28</f>
-        <v>-4458133</v>
-      </c>
       <c r="G12" s="4"/>
       <c r="I12" s="1"/>
       <c r="J12" s="37"/>
       <c r="L12" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="13">
-        <v>239.17</v>
+        <v>179.5</v>
       </c>
       <c r="O12" s="13">
-        <v>486.1</v>
+        <v>156.5</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
       </c>
       <c r="Q12" s="1">
         <f>(O12-N12)*M12*1000+P12</f>
-        <v>0</v>
+        <v>-46000</v>
       </c>
       <c r="R12" s="1">
         <f>O12*M12*1000</f>
-        <v>0</v>
+        <v>313000</v>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="1"/>
@@ -1962,169 +1976,135 @@
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="22"/>
+      <c r="C13" t="s">
+        <v>23</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="I13" s="1"/>
       <c r="J13" s="37"/>
       <c r="N13" s="13"/>
       <c r="O13" s="6">
         <f>(O12-N12)/N12</f>
-        <v>1.0324455408287</v>
+        <v>-0.128133704735376</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
       <c r="R13" s="7">
-        <v>18119476</v>
+        <v>22315376</v>
       </c>
       <c r="S13"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" ht="16.95" spans="2:22">
-      <c r="B14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="38"/>
+    <row r="14" spans="2:22">
+      <c r="B14" s="22"/>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="37"/>
       <c r="Q14"/>
       <c r="R14" s="1">
         <f>SUM(R11:R13)</f>
-        <v>18119476</v>
+        <v>22628376</v>
       </c>
       <c r="S14"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" spans="3:22">
-      <c r="C15" s="17"/>
+    <row r="15" spans="2:22">
+      <c r="B15" s="22"/>
+      <c r="C15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="1">
+        <f>D13+D14</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="37"/>
       <c r="Q15"/>
       <c r="S15"/>
       <c r="T15" s="1"/>
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" ht="16.95" spans="3:3">
-      <c r="C16" s="17"/>
-    </row>
-    <row r="17" ht="16.95" spans="2:10">
-      <c r="B17" s="18">
+    <row r="16" spans="2:10">
+      <c r="B16" s="22"/>
+      <c r="C16" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1">
+        <f>D15-D29</f>
+        <v>-5234110</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="37"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="22"/>
+      <c r="G17" s="4"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="37"/>
+    </row>
+    <row r="18" ht="16.95" spans="2:10">
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="38"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20" ht="16.95" spans="3:3">
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" ht="16.95" spans="2:15">
+      <c r="B21" s="18">
         <v>2025</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C21" s="19"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="19"/>
-      <c r="I17" s="35">
-        <f>SUM($I18:$I32)</f>
+      <c r="H21" s="19"/>
+      <c r="I21" s="35">
+        <f>SUM($I22:$I36)</f>
         <v>490723</v>
       </c>
-      <c r="J17" s="36"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="22"/>
-      <c r="C18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="1">
-        <v>-139300</v>
-      </c>
-      <c r="G18" s="23">
-        <v>45666</v>
-      </c>
-      <c r="H18" t="s">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1">
-        <v>12000</v>
-      </c>
-      <c r="J18" s="37"/>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="22"/>
-      <c r="C19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="1">
-        <v>-210100</v>
-      </c>
-      <c r="G19" s="4">
-        <v>45706</v>
-      </c>
-      <c r="H19" t="s">
-        <v>29</v>
-      </c>
-      <c r="I19" s="1">
-        <v>201960</v>
-      </c>
-      <c r="J19" s="37"/>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="22"/>
-      <c r="C20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="1">
-        <v>-91300</v>
-      </c>
-      <c r="G20" s="4">
-        <v>45723</v>
-      </c>
-      <c r="H20" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="1">
-        <v>17325</v>
-      </c>
-      <c r="J20" s="37"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="22"/>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="1">
-        <v>-610300</v>
-      </c>
-      <c r="G21" s="4">
-        <v>45733</v>
-      </c>
-      <c r="H21" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="1">
-        <v>360</v>
-      </c>
-      <c r="J21" s="37"/>
+      <c r="J21" s="36"/>
       <c r="N21" s="4"/>
       <c r="O21"/>
     </row>
     <row r="22" spans="2:15">
       <c r="B22" s="22"/>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D22" s="1">
-        <v>180900</v>
-      </c>
-      <c r="G22" s="4">
-        <v>45737</v>
+        <v>-139300</v>
+      </c>
+      <c r="G22" s="23">
+        <v>45666</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I22" s="1">
-        <v>2078</v>
+        <v>12000</v>
       </c>
       <c r="J22" s="37"/>
       <c r="N22" s="4"/>
@@ -2133,19 +2113,19 @@
     <row r="23" spans="2:15">
       <c r="B23" s="22"/>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D23" s="1">
-        <v>-165600</v>
+        <v>-210100</v>
       </c>
       <c r="G23" s="4">
-        <v>45757</v>
+        <v>45706</v>
       </c>
       <c r="H23" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I23" s="1">
-        <v>20250</v>
+        <v>201960</v>
       </c>
       <c r="J23" s="37"/>
       <c r="N23" s="4"/>
@@ -2153,15 +2133,20 @@
     </row>
     <row r="24" spans="2:15">
       <c r="B24" s="22"/>
-      <c r="D24" s="27"/>
+      <c r="C24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-91300</v>
+      </c>
       <c r="G24" s="4">
-        <v>45763</v>
+        <v>45723</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="1">
-        <v>175500</v>
+        <v>17325</v>
       </c>
       <c r="J24" s="37"/>
       <c r="N24" s="4"/>
@@ -2170,19 +2155,19 @@
     <row r="25" spans="2:15">
       <c r="B25" s="22"/>
       <c r="C25" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D25" s="1">
-        <v>5234110</v>
+        <v>-610300</v>
       </c>
       <c r="G25" s="4">
-        <v>45848</v>
+        <v>45733</v>
       </c>
       <c r="H25" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="I25" s="1">
-        <v>20250</v>
+        <v>360</v>
       </c>
       <c r="J25" s="37"/>
       <c r="O25" s="13"/>
@@ -2190,20 +2175,19 @@
     <row r="26" spans="2:29">
       <c r="B26" s="22"/>
       <c r="C26" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1">
-        <f>SUM(D18:D23)+I17</f>
-        <v>-544977</v>
+        <v>180900</v>
       </c>
       <c r="G26" s="4">
-        <v>45939</v>
+        <v>45737</v>
       </c>
       <c r="H26" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I26" s="1">
-        <v>41000</v>
+        <v>2078</v>
       </c>
       <c r="J26" s="37"/>
       <c r="O26" s="13"/>
@@ -2215,14 +2199,20 @@
     <row r="27" spans="2:29">
       <c r="B27" s="22"/>
       <c r="C27" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D27" s="1">
-        <f>D25+D26</f>
-        <v>4689133</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="I27" s="1"/>
+        <v>-165600</v>
+      </c>
+      <c r="G27" s="4">
+        <v>45757</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>20250</v>
+      </c>
       <c r="J27" s="37"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
@@ -2231,15 +2221,16 @@
     </row>
     <row r="28" spans="2:29">
       <c r="B28" s="22"/>
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-      <c r="D28" s="28">
-        <f>D27-D43</f>
-        <v>4458133</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="I28" s="1"/>
+      <c r="D28" s="27"/>
+      <c r="G28" s="4">
+        <v>45763</v>
+      </c>
+      <c r="H28" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="1">
+        <v>175500</v>
+      </c>
       <c r="J28" s="37"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
@@ -2248,8 +2239,21 @@
     </row>
     <row r="29" spans="2:29">
       <c r="B29" s="22"/>
-      <c r="G29" s="4"/>
-      <c r="I29" s="1"/>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="1">
+        <v>5234110</v>
+      </c>
+      <c r="G29" s="4">
+        <v>45848</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>20250</v>
+      </c>
       <c r="J29" s="37"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
@@ -2259,10 +2263,21 @@
     <row r="30" spans="2:29">
       <c r="B30" s="22"/>
       <c r="C30" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="I30" s="1"/>
+        <v>25</v>
+      </c>
+      <c r="D30" s="1">
+        <f>SUM(D22:D27)+I21</f>
+        <v>-544977</v>
+      </c>
+      <c r="G30" s="4">
+        <v>45939</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>41000</v>
+      </c>
       <c r="J30" s="37"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
@@ -2272,7 +2287,11 @@
     <row r="31" spans="2:29">
       <c r="B31" s="22"/>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>26</v>
+      </c>
+      <c r="D31" s="1">
+        <f>D29+D30</f>
+        <v>4689133</v>
       </c>
       <c r="G31" s="4"/>
       <c r="I31" s="1"/>
@@ -2282,16 +2301,18 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
-    <row r="32" ht="16.95" spans="2:29">
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="38"/>
+    <row r="32" spans="2:29">
+      <c r="B32" s="22"/>
+      <c r="C32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="28">
+        <f>D31-D47</f>
+        <v>4458133</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="37"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -2300,7 +2321,11 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
     </row>
-    <row r="33" spans="23:29">
+    <row r="33" spans="2:29">
+      <c r="B33" s="22"/>
+      <c r="G33" s="4"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="37"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
@@ -2309,7 +2334,14 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
     </row>
-    <row r="34" ht="16.95" spans="23:29">
+    <row r="34" spans="2:29">
+      <c r="B34" s="22"/>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="37"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -2318,25 +2350,14 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
     </row>
-    <row r="35" ht="16.95" spans="2:29">
-      <c r="B35" s="18">
-        <v>2024</v>
-      </c>
-      <c r="C35" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="H35" s="19"/>
-      <c r="I35" s="35">
-        <f>SUM(I$36:I$52)</f>
-        <v>307025</v>
-      </c>
-      <c r="J35" s="36"/>
+    <row r="35" spans="2:29">
+      <c r="B35" s="22"/>
+      <c r="C35" t="s">
+        <v>38</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="37"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -2345,24 +2366,16 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
     </row>
-    <row r="36" spans="2:29">
-      <c r="B36" s="22"/>
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" s="1">
-        <v>-19000</v>
-      </c>
-      <c r="G36" s="4">
-        <v>45303</v>
-      </c>
-      <c r="H36" t="s">
-        <v>39</v>
-      </c>
-      <c r="I36" s="1">
-        <v>6210</v>
-      </c>
-      <c r="J36" s="37"/>
+    <row r="36" ht="16.95" spans="2:29">
+      <c r="B36" s="24"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="38"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -2371,24 +2384,7 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
     </row>
-    <row r="37" spans="2:29">
-      <c r="B37" s="22"/>
-      <c r="C37" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="1">
-        <v>657000</v>
-      </c>
-      <c r="G37" s="4">
-        <v>45343</v>
-      </c>
-      <c r="H37" t="s">
-        <v>39</v>
-      </c>
-      <c r="I37" s="1">
-        <v>12080</v>
-      </c>
-      <c r="J37" s="37"/>
+    <row r="37" spans="20:29">
       <c r="T37" s="1"/>
       <c r="U37" s="1"/>
       <c r="V37" s="1"/>
@@ -2400,24 +2396,7 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
     </row>
-    <row r="38" spans="2:29">
-      <c r="B38" s="22"/>
-      <c r="C38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D38" s="1">
-        <v>-10000</v>
-      </c>
-      <c r="G38" s="4">
-        <v>45376</v>
-      </c>
-      <c r="H38" t="s">
-        <v>39</v>
-      </c>
-      <c r="I38" s="1">
-        <v>3900</v>
-      </c>
-      <c r="J38" s="37"/>
+    <row r="38" ht="16.95" spans="20:29">
       <c r="T38" s="1"/>
       <c r="U38" s="1"/>
       <c r="V38" s="1"/>
@@ -2429,24 +2408,23 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
     </row>
-    <row r="39" spans="2:29">
-      <c r="B39" s="22"/>
-      <c r="C39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="1">
-        <v>663000</v>
-      </c>
-      <c r="G39" s="4">
-        <v>45393</v>
-      </c>
-      <c r="H39" t="s">
-        <v>2</v>
-      </c>
-      <c r="I39" s="1">
-        <v>7000</v>
-      </c>
-      <c r="J39" s="37"/>
+    <row r="39" ht="16.95" spans="2:29">
+      <c r="B39" s="18">
+        <v>2024</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="35">
+        <f>SUM(I$40:I$56)</f>
+        <v>307025</v>
+      </c>
+      <c r="J39" s="36"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
@@ -2461,19 +2439,19 @@
     <row r="40" spans="2:29">
       <c r="B40" s="22"/>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D40" s="1">
-        <v>38600</v>
+        <v>-19000</v>
       </c>
       <c r="G40" s="4">
-        <v>45400</v>
+        <v>45303</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I40" s="1">
-        <v>155000</v>
+        <v>6210</v>
       </c>
       <c r="J40" s="37"/>
       <c r="T40" s="1"/>
@@ -2490,20 +2468,19 @@
     <row r="41" spans="2:29">
       <c r="B41" s="22"/>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D41" s="1">
-        <v>-74000</v>
-      </c>
-      <c r="E41" s="13"/>
+        <v>657000</v>
+      </c>
       <c r="G41" s="4">
-        <v>45470</v>
+        <v>45343</v>
       </c>
       <c r="H41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I41" s="1">
-        <v>3879</v>
+        <v>12080</v>
       </c>
       <c r="J41" s="37"/>
       <c r="T41" s="1"/>
@@ -2519,17 +2496,20 @@
     </row>
     <row r="42" spans="2:29">
       <c r="B42" s="22"/>
+      <c r="C42" t="s">
+        <v>40</v>
+      </c>
       <c r="D42" s="1">
-        <v>0</v>
+        <v>-10000</v>
       </c>
       <c r="G42" s="4">
-        <v>45484</v>
+        <v>45376</v>
       </c>
       <c r="H42" t="s">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I42" s="1">
-        <v>7000</v>
+        <v>3900</v>
       </c>
       <c r="J42" s="37"/>
       <c r="T42" s="1"/>
@@ -2546,19 +2526,19 @@
     <row r="43" spans="2:29">
       <c r="B43" s="22"/>
       <c r="C43" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D43" s="1">
-        <v>231000</v>
+        <v>663000</v>
       </c>
       <c r="G43" s="4">
-        <v>45489</v>
+        <v>45393</v>
       </c>
       <c r="H43" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I43" s="1">
-        <v>13902</v>
+        <v>7000</v>
       </c>
       <c r="J43" s="37"/>
       <c r="T43" s="1"/>
@@ -2575,20 +2555,19 @@
     <row r="44" spans="2:29">
       <c r="B44" s="22"/>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D44" s="1">
-        <f>SUM(D36:D41)+I35</f>
-        <v>1562625</v>
+        <v>38600</v>
       </c>
       <c r="G44" s="4">
-        <v>45506</v>
+        <v>45400</v>
       </c>
       <c r="H44" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I44" s="1">
-        <v>81600</v>
+        <v>155000</v>
       </c>
       <c r="J44" s="37"/>
       <c r="T44" s="1"/>
@@ -2605,412 +2584,427 @@
     <row r="45" spans="2:10">
       <c r="B45" s="22"/>
       <c r="C45" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D45" s="1">
-        <f>D43+D44</f>
-        <v>1793625</v>
-      </c>
+        <v>-74000</v>
+      </c>
+      <c r="E45" s="13"/>
       <c r="G45" s="4">
-        <v>45513</v>
+        <v>45470</v>
       </c>
       <c r="H45" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I45" s="1">
-        <v>783</v>
+        <v>3879</v>
       </c>
       <c r="J45" s="37"/>
     </row>
     <row r="46" spans="2:10">
       <c r="B46" s="22"/>
-      <c r="C46" t="s">
-        <v>25</v>
-      </c>
-      <c r="D46" s="28">
-        <f>D45-D63</f>
-        <v>1455625</v>
-      </c>
       <c r="G46" s="4">
-        <v>45523</v>
+        <v>45484</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I46" s="1">
-        <v>1161</v>
+        <v>7000</v>
       </c>
       <c r="J46" s="37"/>
     </row>
     <row r="47" spans="2:10">
       <c r="B47" s="22"/>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="1">
+        <v>231000</v>
+      </c>
       <c r="G47" s="4">
-        <v>45525</v>
+        <v>45489</v>
       </c>
       <c r="H47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I47" s="1">
-        <v>1237</v>
+        <v>13902</v>
       </c>
       <c r="J47" s="37"/>
     </row>
     <row r="48" spans="2:10">
       <c r="B48" s="22"/>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>25</v>
+      </c>
+      <c r="D48" s="1">
+        <f>SUM(D40:D45)+I39</f>
+        <v>1562625</v>
       </c>
       <c r="G48" s="4">
+        <v>45506</v>
+      </c>
+      <c r="H48" t="s">
+        <v>28</v>
+      </c>
+      <c r="I48" s="1">
+        <v>81600</v>
+      </c>
+      <c r="J48" s="37"/>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="22"/>
+      <c r="C49" t="s">
+        <v>26</v>
+      </c>
+      <c r="D49" s="1">
+        <f>D47+D48</f>
+        <v>1793625</v>
+      </c>
+      <c r="G49" s="4">
+        <v>45513</v>
+      </c>
+      <c r="H49" t="s">
+        <v>41</v>
+      </c>
+      <c r="I49" s="1">
+        <v>783</v>
+      </c>
+      <c r="J49" s="37"/>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="22"/>
+      <c r="C50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" s="28">
+        <f>D49-D67</f>
+        <v>1455625</v>
+      </c>
+      <c r="G50" s="4">
+        <v>45523</v>
+      </c>
+      <c r="H50" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1161</v>
+      </c>
+      <c r="J50" s="37"/>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="22"/>
+      <c r="G51" s="4">
+        <v>45525</v>
+      </c>
+      <c r="H51" t="s">
+        <v>34</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1237</v>
+      </c>
+      <c r="J51" s="37"/>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="22"/>
+      <c r="C52" t="s">
+        <v>37</v>
+      </c>
+      <c r="G52" s="4">
         <v>45574</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H52" t="s">
         <v>2</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I52" s="1">
         <v>12000</v>
       </c>
-      <c r="J48" s="37"/>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="29"/>
-      <c r="C49" t="s">
-        <v>37</v>
-      </c>
-      <c r="G49" s="4">
+      <c r="J52" s="37"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="29"/>
+      <c r="C53" t="s">
+        <v>38</v>
+      </c>
+      <c r="G53" s="4">
         <v>45643</v>
       </c>
-      <c r="H49" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="H53" t="s">
+        <v>43</v>
+      </c>
+      <c r="I53" s="1">
         <v>1273</v>
       </c>
-      <c r="J49" s="37"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="29"/>
-      <c r="J50" s="37"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="29"/>
-      <c r="G51" s="30"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="37"/>
-    </row>
-    <row r="52" ht="16.95" spans="2:10">
-      <c r="B52" s="24"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="9"/>
-      <c r="J52" s="38"/>
-    </row>
-    <row r="53" spans="2:2">
-      <c r="B53" s="4"/>
-    </row>
-    <row r="54" ht="16.95" spans="2:2">
-      <c r="B54" s="4"/>
-    </row>
-    <row r="55" ht="16.95" spans="2:10">
-      <c r="B55" s="18">
+      <c r="J53" s="37"/>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="29"/>
+      <c r="J54" s="37"/>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="29"/>
+      <c r="G55" s="30"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="37"/>
+    </row>
+    <row r="56" ht="16.95" spans="2:10">
+      <c r="B56" s="24"/>
+      <c r="C56" s="25"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="25"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="38"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" ht="16.95" spans="2:2">
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" ht="16.95" spans="2:10">
+      <c r="B59" s="18">
         <v>2023</v>
       </c>
-      <c r="C55" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="20"/>
-      <c r="E55" s="20"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="H55" s="19"/>
-      <c r="I55" s="35">
-        <f>SUM(I56:I62)</f>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="35">
+        <f>SUM(I60:I66)</f>
         <v>103800</v>
       </c>
-      <c r="J55" s="36"/>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="22"/>
-      <c r="C56" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" s="32">
-        <v>346100</v>
-      </c>
-      <c r="E56" s="33"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="34">
-        <v>45135</v>
-      </c>
-      <c r="H56" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="I56" s="33">
-        <v>4750</v>
-      </c>
-      <c r="J56" s="37"/>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="22"/>
-      <c r="C57" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" s="32">
-        <v>32738</v>
-      </c>
-      <c r="E57" s="33"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="34">
-        <v>45149</v>
-      </c>
-      <c r="H57" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="I57" s="33">
-        <v>2300</v>
-      </c>
-      <c r="J57" s="37"/>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="22"/>
-      <c r="C58" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="32">
-        <v>-14900</v>
-      </c>
-      <c r="E58" s="33"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="34">
-        <v>45149</v>
-      </c>
-      <c r="H58" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I58" s="33">
-        <v>54266</v>
-      </c>
-      <c r="J58" s="37"/>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="22"/>
-      <c r="C59" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D59" s="32">
-        <v>-171900</v>
-      </c>
-      <c r="E59" s="33"/>
-      <c r="F59" s="31"/>
-      <c r="G59" s="34">
-        <v>45244</v>
-      </c>
-      <c r="H59" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="I59" s="33">
-        <v>4790</v>
-      </c>
-      <c r="J59" s="37"/>
+      <c r="J59" s="36"/>
     </row>
     <row r="60" spans="2:10">
       <c r="B60" s="22"/>
       <c r="C60" s="31" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D60" s="32">
-        <v>-68600</v>
+        <v>346100</v>
       </c>
       <c r="E60" s="33"/>
       <c r="F60" s="31"/>
       <c r="G60" s="34">
-        <v>45244</v>
+        <v>45135</v>
       </c>
       <c r="H60" s="31" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I60" s="33">
-        <v>635</v>
+        <v>4750</v>
       </c>
       <c r="J60" s="37"/>
     </row>
     <row r="61" spans="2:10">
       <c r="B61" s="22"/>
       <c r="C61" s="31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D61" s="32">
-        <v>18500</v>
+        <v>32738</v>
       </c>
       <c r="E61" s="33"/>
       <c r="F61" s="31"/>
       <c r="G61" s="34">
-        <v>45272</v>
+        <v>45149</v>
       </c>
       <c r="H61" s="31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I61" s="33">
-        <v>34599</v>
+        <v>2300</v>
       </c>
       <c r="J61" s="37"/>
     </row>
     <row r="62" spans="2:10">
       <c r="B62" s="22"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="32"/>
+      <c r="C62" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="32">
+        <v>-14900</v>
+      </c>
       <c r="E62" s="33"/>
       <c r="F62" s="31"/>
       <c r="G62" s="34">
-        <v>45272</v>
+        <v>45149</v>
       </c>
       <c r="H62" s="31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I62" s="33">
-        <v>2460</v>
+        <v>54266</v>
       </c>
       <c r="J62" s="37"/>
     </row>
     <row r="63" spans="2:10">
       <c r="B63" s="22"/>
       <c r="C63" s="31" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="D63" s="32">
-        <v>338000</v>
+        <v>-171900</v>
       </c>
       <c r="E63" s="33"/>
       <c r="F63" s="31"/>
-      <c r="G63" s="31"/>
-      <c r="H63" s="31"/>
-      <c r="I63" s="31"/>
+      <c r="G63" s="34">
+        <v>45244</v>
+      </c>
+      <c r="H63" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I63" s="33">
+        <v>4790</v>
+      </c>
       <c r="J63" s="37"/>
     </row>
     <row r="64" spans="2:10">
       <c r="B64" s="22"/>
       <c r="C64" s="31" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="D64" s="32">
-        <f>SUM(D56:D61)+I55</f>
-        <v>245738</v>
+        <v>-68600</v>
       </c>
       <c r="E64" s="33"/>
       <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
+      <c r="G64" s="34">
+        <v>45244</v>
+      </c>
+      <c r="H64" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="I64" s="33">
+        <v>635</v>
+      </c>
       <c r="J64" s="37"/>
     </row>
     <row r="65" spans="2:10">
       <c r="B65" s="22"/>
       <c r="C65" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65" s="33">
-        <f>D63+D64</f>
-        <v>583738</v>
+        <v>50</v>
+      </c>
+      <c r="D65" s="32">
+        <v>18500</v>
       </c>
       <c r="E65" s="33"/>
       <c r="F65" s="31"/>
-      <c r="G65" s="31"/>
-      <c r="H65" s="31"/>
-      <c r="I65" s="31"/>
+      <c r="G65" s="34">
+        <v>45272</v>
+      </c>
+      <c r="H65" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="I65" s="33">
+        <v>34599</v>
+      </c>
       <c r="J65" s="37"/>
     </row>
-    <row r="66" ht="16.95" spans="2:10">
-      <c r="B66" s="41"/>
-      <c r="C66" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D66" s="42">
-        <f>D65-D80</f>
-        <v>443038</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="38"/>
+    <row r="66" spans="2:10">
+      <c r="B66" s="22"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="33"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="34">
+        <v>45272</v>
+      </c>
+      <c r="H66" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="I66" s="33">
+        <v>2460</v>
+      </c>
+      <c r="J66" s="37"/>
     </row>
     <row r="67" spans="2:10">
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="33"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D67" s="32">
+        <v>338000</v>
+      </c>
       <c r="E67" s="33"/>
       <c r="F67" s="31"/>
       <c r="G67" s="31"/>
       <c r="H67" s="31"/>
       <c r="I67" s="31"/>
-      <c r="J67" s="33"/>
-    </row>
-    <row r="68" ht="16.95" spans="2:10">
-      <c r="B68" s="31"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="43"/>
+      <c r="J67" s="37"/>
+    </row>
+    <row r="68" spans="2:10">
+      <c r="B68" s="22"/>
+      <c r="C68" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="D68" s="32">
+        <f>SUM(D60:D65)+I59</f>
+        <v>245738</v>
+      </c>
       <c r="E68" s="33"/>
       <c r="F68" s="31"/>
       <c r="G68" s="31"/>
       <c r="H68" s="31"/>
       <c r="I68" s="31"/>
-      <c r="J68" s="33"/>
+      <c r="J68" s="37"/>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="18">
-        <v>2022</v>
-      </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="36"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D69" s="33">
+        <f>D67+D68</f>
+        <v>583738</v>
+      </c>
       <c r="E69" s="33"/>
       <c r="F69" s="31"/>
       <c r="G69" s="31"/>
       <c r="H69" s="31"/>
       <c r="I69" s="31"/>
-      <c r="J69" s="33"/>
-    </row>
-    <row r="70" spans="2:10">
-      <c r="B70" s="22"/>
-      <c r="C70" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="37">
-        <v>890500</v>
-      </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="31"/>
-      <c r="H70" s="31"/>
-      <c r="I70" s="31"/>
-      <c r="J70" s="33"/>
+      <c r="J69" s="37"/>
+    </row>
+    <row r="70" ht="16.95" spans="2:10">
+      <c r="B70" s="41"/>
+      <c r="C70" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D70" s="42">
+        <f>D69-D84</f>
+        <v>443038</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="25"/>
+      <c r="H70" s="25"/>
+      <c r="I70" s="25"/>
+      <c r="J70" s="38"/>
     </row>
     <row r="71" spans="2:10">
-      <c r="B71" s="22"/>
-      <c r="C71" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D71" s="37">
-        <v>-9600</v>
-      </c>
+      <c r="B71" s="31"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
       <c r="F71" s="31"/>
       <c r="G71" s="31"/>
       <c r="H71" s="31"/>
       <c r="I71" s="31"/>
       <c r="J71" s="33"/>
     </row>
-    <row r="72" spans="2:10">
-      <c r="B72" s="22"/>
-      <c r="C72" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="D72" s="37">
-        <v>-38800</v>
-      </c>
+    <row r="72" ht="16.95" spans="2:10">
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="33"/>
       <c r="F72" s="31"/>
       <c r="G72" s="31"/>
       <c r="H72" s="31"/>
@@ -3018,13 +3012,12 @@
       <c r="J72" s="33"/>
     </row>
     <row r="73" spans="2:10">
-      <c r="B73" s="22"/>
-      <c r="C73" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D73" s="37">
-        <v>137800</v>
-      </c>
+      <c r="B73" s="18">
+        <v>2022</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="33"/>
       <c r="F73" s="31"/>
       <c r="G73" s="31"/>
       <c r="H73" s="31"/>
@@ -3034,10 +3027,10 @@
     <row r="74" spans="2:10">
       <c r="B74" s="22"/>
       <c r="C74" s="31" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D74" s="37">
-        <v>-49300</v>
+        <v>890500</v>
       </c>
       <c r="F74" s="31"/>
       <c r="G74" s="31"/>
@@ -3048,10 +3041,10 @@
     <row r="75" spans="2:10">
       <c r="B75" s="22"/>
       <c r="C75" s="31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D75" s="37">
-        <v>15600</v>
+        <v>-9600</v>
       </c>
       <c r="F75" s="31"/>
       <c r="G75" s="31"/>
@@ -3062,10 +3055,10 @@
     <row r="76" spans="2:10">
       <c r="B76" s="22"/>
       <c r="C76" s="31" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D76" s="37">
-        <v>-19600</v>
+        <v>-38800</v>
       </c>
       <c r="F76" s="31"/>
       <c r="G76" s="31"/>
@@ -3076,10 +3069,10 @@
     <row r="77" spans="2:10">
       <c r="B77" s="22"/>
       <c r="C77" s="31" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D77" s="37">
-        <v>58600</v>
+        <v>137800</v>
       </c>
       <c r="F77" s="31"/>
       <c r="G77" s="31"/>
@@ -3089,11 +3082,11 @@
     </row>
     <row r="78" spans="2:10">
       <c r="B78" s="22"/>
-      <c r="C78" t="s">
-        <v>46</v>
+      <c r="C78" s="31" t="s">
+        <v>53</v>
       </c>
       <c r="D78" s="37">
-        <v>75005</v>
+        <v>-49300</v>
       </c>
       <c r="F78" s="31"/>
       <c r="G78" s="31"/>
@@ -3103,8 +3096,12 @@
     </row>
     <row r="79" spans="2:10">
       <c r="B79" s="22"/>
-      <c r="C79" s="31"/>
-      <c r="D79" s="37"/>
+      <c r="C79" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="37">
+        <v>15600</v>
+      </c>
       <c r="F79" s="31"/>
       <c r="G79" s="31"/>
       <c r="H79" s="31"/>
@@ -3114,10 +3111,10 @@
     <row r="80" spans="2:10">
       <c r="B80" s="22"/>
       <c r="C80" s="31" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="D80" s="37">
-        <v>140700</v>
+        <v>-19600</v>
       </c>
       <c r="F80" s="31"/>
       <c r="G80" s="31"/>
@@ -3128,11 +3125,10 @@
     <row r="81" spans="2:10">
       <c r="B81" s="22"/>
       <c r="C81" s="31" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="D81" s="37">
-        <f>SUM(D70:D78)</f>
-        <v>1060205</v>
+        <v>58600</v>
       </c>
       <c r="F81" s="31"/>
       <c r="G81" s="31"/>
@@ -3142,12 +3138,11 @@
     </row>
     <row r="82" spans="2:10">
       <c r="B82" s="22"/>
-      <c r="C82" s="31" t="s">
-        <v>20</v>
+      <c r="C82" t="s">
+        <v>47</v>
       </c>
       <c r="D82" s="37">
-        <f>D80+D81</f>
-        <v>1200905</v>
+        <v>75005</v>
       </c>
       <c r="F82" s="31"/>
       <c r="G82" s="31"/>
@@ -3155,286 +3150,328 @@
       <c r="I82" s="31"/>
       <c r="J82" s="33"/>
     </row>
-    <row r="83" ht="16.95" spans="2:4">
-      <c r="B83" s="41"/>
-      <c r="C83" s="25" t="s">
+    <row r="83" spans="2:10">
+      <c r="B83" s="22"/>
+      <c r="C83" s="31"/>
+      <c r="D83" s="37"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="31"/>
+      <c r="J83" s="33"/>
+    </row>
+    <row r="84" spans="2:10">
+      <c r="B84" s="22"/>
+      <c r="C84" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="37">
+        <v>140700</v>
+      </c>
+      <c r="F84" s="31"/>
+      <c r="G84" s="31"/>
+      <c r="H84" s="31"/>
+      <c r="I84" s="31"/>
+      <c r="J84" s="33"/>
+    </row>
+    <row r="85" spans="2:10">
+      <c r="B85" s="22"/>
+      <c r="C85" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="D83" s="44">
-        <f>D82-D103</f>
+      <c r="D85" s="37">
+        <f>SUM(D74:D82)</f>
+        <v>1060205</v>
+      </c>
+      <c r="F85" s="31"/>
+      <c r="G85" s="31"/>
+      <c r="H85" s="31"/>
+      <c r="I85" s="31"/>
+      <c r="J85" s="33"/>
+    </row>
+    <row r="86" spans="2:10">
+      <c r="B86" s="22"/>
+      <c r="C86" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" s="37">
+        <f>D84+D85</f>
+        <v>1200905</v>
+      </c>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="31"/>
+      <c r="I86" s="31"/>
+      <c r="J86" s="33"/>
+    </row>
+    <row r="87" ht="16.95" spans="2:4">
+      <c r="B87" s="41"/>
+      <c r="C87" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D87" s="44">
+        <f>D86-D107</f>
         <v>488305</v>
       </c>
     </row>
-    <row r="84" spans="4:4">
-      <c r="D84" s="27"/>
-    </row>
-    <row r="85" ht="16.95" spans="4:4">
-      <c r="D85" s="27"/>
-    </row>
-    <row r="86" spans="2:4">
-      <c r="B86" s="18">
+    <row r="88" spans="4:4">
+      <c r="D88" s="27"/>
+    </row>
+    <row r="89" ht="16.95" spans="4:4">
+      <c r="D89" s="27"/>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="18">
         <v>2021</v>
       </c>
-      <c r="C86" s="19"/>
-      <c r="D86" s="45"/>
-    </row>
-    <row r="87" spans="2:4">
-      <c r="B87" s="22"/>
-      <c r="C87" t="s">
-        <v>56</v>
-      </c>
-      <c r="D87" s="37">
-        <v>11300</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4">
-      <c r="B88" s="22"/>
-      <c r="C88" t="s">
-        <v>57</v>
-      </c>
-      <c r="D88" s="37">
-        <v>33300</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4">
-      <c r="B89" s="22"/>
-      <c r="C89" t="s">
-        <v>58</v>
-      </c>
-      <c r="D89" s="37">
-        <v>108700</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" s="22"/>
-      <c r="C90" t="s">
-        <v>59</v>
-      </c>
-      <c r="D90" s="37">
-        <v>-14800</v>
-      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="45"/>
     </row>
     <row r="91" spans="2:4">
       <c r="B91" s="22"/>
       <c r="C91" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D91" s="37">
-        <v>35300</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="92" spans="2:4">
       <c r="B92" s="22"/>
       <c r="C92" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D92" s="37">
-        <v>-8900</v>
+        <v>33300</v>
       </c>
     </row>
     <row r="93" spans="2:4">
       <c r="B93" s="22"/>
       <c r="C93" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D93" s="37">
-        <v>-6000</v>
+        <v>108700</v>
       </c>
     </row>
     <row r="94" spans="2:4">
       <c r="B94" s="22"/>
       <c r="C94" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D94" s="37">
-        <v>56100</v>
+        <v>-14800</v>
       </c>
     </row>
     <row r="95" spans="2:4">
       <c r="B95" s="22"/>
       <c r="C95" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D95" s="37">
-        <v>1900</v>
+        <v>35300</v>
       </c>
     </row>
     <row r="96" spans="2:4">
       <c r="B96" s="22"/>
       <c r="C96" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D96" s="37">
-        <v>-12700</v>
+        <v>-8900</v>
       </c>
     </row>
     <row r="97" spans="2:4">
       <c r="B97" s="22"/>
       <c r="C97" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D97" s="37">
-        <v>77700</v>
+        <v>-6000</v>
       </c>
     </row>
     <row r="98" spans="2:4">
       <c r="B98" s="22"/>
       <c r="C98" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D98" s="37">
-        <v>-13200</v>
+        <v>56100</v>
       </c>
     </row>
     <row r="99" spans="2:4">
       <c r="B99" s="22"/>
       <c r="C99" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D99" s="37">
-        <v>-10500</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="100" spans="2:4">
       <c r="B100" s="22"/>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D100" s="37">
-        <v>244900</v>
+        <v>-12700</v>
       </c>
     </row>
     <row r="101" spans="2:4">
       <c r="B101" s="22"/>
       <c r="C101" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="D101" s="37">
-        <v>67032</v>
+        <v>77700</v>
       </c>
     </row>
     <row r="102" spans="2:4">
       <c r="B102" s="22"/>
-      <c r="D102" s="37"/>
+      <c r="C102" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102" s="37">
+        <v>-13200</v>
+      </c>
     </row>
     <row r="103" spans="2:4">
       <c r="B103" s="22"/>
       <c r="C103" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="D103" s="37">
-        <v>712600</v>
+        <v>-10500</v>
       </c>
     </row>
     <row r="104" spans="2:4">
       <c r="B104" s="22"/>
       <c r="C104" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D104" s="37">
-        <f>SUM(D87:D101)</f>
-        <v>570132</v>
+        <v>244900</v>
       </c>
     </row>
     <row r="105" spans="2:4">
       <c r="B105" s="22"/>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D105" s="37">
-        <f>D103+D104</f>
+        <v>67032</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="22"/>
+      <c r="D106" s="37"/>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="22"/>
+      <c r="C107" t="s">
+        <v>23</v>
+      </c>
+      <c r="D107" s="37">
+        <v>712600</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="22"/>
+      <c r="C108" t="s">
+        <v>25</v>
+      </c>
+      <c r="D108" s="37">
+        <f>SUM(D91:D105)</f>
+        <v>570132</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="22"/>
+      <c r="C109" t="s">
+        <v>26</v>
+      </c>
+      <c r="D109" s="37">
+        <f>D107+D108</f>
         <v>1282732</v>
       </c>
     </row>
-    <row r="106" ht="16.95" spans="2:4">
-      <c r="B106" s="41"/>
-      <c r="C106" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D106" s="44">
-        <f>D105-D114</f>
+    <row r="110" ht="16.95" spans="2:4">
+      <c r="B110" s="41"/>
+      <c r="C110" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" s="44">
+        <f>D109-D118</f>
         <v>1219032</v>
       </c>
     </row>
-    <row r="108" ht="16.95"/>
-    <row r="109" spans="2:4">
-      <c r="B109" s="18">
+    <row r="112" ht="16.95"/>
+    <row r="113" spans="2:4">
+      <c r="B113" s="18">
         <v>2020</v>
       </c>
-      <c r="C109" s="19"/>
-      <c r="D109" s="36"/>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" s="22"/>
-      <c r="C110" t="s">
-        <v>56</v>
-      </c>
-      <c r="D110" s="37">
-        <v>49400</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" s="22"/>
-      <c r="C111" t="s">
-        <v>57</v>
-      </c>
-      <c r="D111" s="37">
-        <v>64300</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" s="22"/>
-      <c r="C112" t="s">
-        <v>68</v>
-      </c>
-      <c r="D112" s="37">
-        <v>-6000</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4">
-      <c r="B113" s="22"/>
-      <c r="D113" s="37"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="36"/>
     </row>
     <row r="114" spans="2:4">
       <c r="B114" s="22"/>
       <c r="C114" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="D114" s="37">
-        <v>63700</v>
+        <v>49400</v>
       </c>
     </row>
     <row r="115" spans="2:4">
       <c r="B115" s="22"/>
       <c r="C115" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="D115" s="37">
-        <f>SUM(D110:D112)</f>
+        <v>64300</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="22"/>
+      <c r="C116" t="s">
+        <v>69</v>
+      </c>
+      <c r="D116" s="37">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="22"/>
+      <c r="D117" s="37"/>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="22"/>
+      <c r="C118" t="s">
+        <v>23</v>
+      </c>
+      <c r="D118" s="37">
+        <v>63700</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="22"/>
+      <c r="C119" t="s">
+        <v>25</v>
+      </c>
+      <c r="D119" s="37">
+        <f>SUM(D114:D116)</f>
         <v>107700</v>
       </c>
     </row>
-    <row r="116" ht="16.95" spans="2:4">
-      <c r="B116" s="41"/>
-      <c r="C116" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" s="44">
-        <f>D114+D115</f>
+    <row r="120" ht="16.95" spans="2:4">
+      <c r="B120" s="41"/>
+      <c r="C120" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="D120" s="44">
+        <f>D118+D119</f>
         <v>171400</v>
       </c>
-    </row>
-    <row r="117" spans="4:4">
-      <c r="D117" s="27"/>
-    </row>
-    <row r="118" spans="4:4">
-      <c r="D118" s="27"/>
-    </row>
-    <row r="119" spans="4:4">
-      <c r="D119" s="27"/>
-    </row>
-    <row r="120" spans="4:4">
-      <c r="D120" s="27"/>
     </row>
     <row r="121" spans="4:4">
       <c r="D121" s="27"/>
@@ -3695,13 +3732,25 @@
       <c r="D206" s="27"/>
     </row>
     <row r="207" spans="4:4">
-      <c r="D207" s="46"/>
+      <c r="D207" s="27"/>
     </row>
     <row r="208" spans="4:4">
-      <c r="D208" s="46"/>
+      <c r="D208" s="27"/>
     </row>
     <row r="209" spans="4:4">
-      <c r="D209" s="46"/>
+      <c r="D209" s="27"/>
+    </row>
+    <row r="210" spans="4:4">
+      <c r="D210" s="27"/>
+    </row>
+    <row r="211" spans="4:4">
+      <c r="D211" s="46"/>
+    </row>
+    <row r="212" spans="4:4">
+      <c r="D212" s="46"/>
+    </row>
+    <row r="213" spans="4:4">
+      <c r="D213" s="46"/>
     </row>
   </sheetData>
   <sortState ref="G5:I11">
@@ -3732,20 +3781,20 @@
   <sheetData>
     <row r="1" spans="4:15">
       <c r="D1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E1" s="10">
         <v>0.04</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I1" s="1">
         <v>10000000</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -3754,20 +3803,20 @@
     </row>
     <row r="2" spans="4:15">
       <c r="D2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E2" s="11">
         <v>2</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I2" s="14">
         <v>0.03</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L2" s="1">
         <f>F9</f>
@@ -3779,13 +3828,13 @@
     </row>
     <row r="3" spans="4:15">
       <c r="D3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3">
         <v>500000</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I3" s="1">
         <f>I1*I2</f>
@@ -3793,7 +3842,7 @@
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L3" s="1">
         <v>207000</v>
@@ -3804,14 +3853,14 @@
     </row>
     <row r="4" spans="4:15">
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" s="1">
         <f>K18</f>
         <v>173506.24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I4" s="1">
         <f>I3/12</f>
@@ -3819,7 +3868,7 @@
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" s="1">
         <f>L2-L3</f>
@@ -3835,7 +3884,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L5" s="1">
         <f>I3</f>
@@ -3869,7 +3918,7 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L6" s="1">
         <v>270000</v>
@@ -3898,7 +3947,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -3910,7 +3959,7 @@
     <row r="8" spans="3:15">
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E8" s="1">
         <f>$E$3</f>
@@ -3925,7 +3974,7 @@
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" s="1">
         <v>124000</v>
@@ -3941,7 +3990,7 @@
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E9" s="1">
         <f>SUM(E6:E8)</f>
@@ -3959,7 +4008,7 @@
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L9" s="1">
         <f>(L4+MAX(0,L5-L6))-L8</f>
@@ -3976,7 +4025,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1">
         <f>E9+$I$3</f>
@@ -3996,7 +4045,7 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -4004,7 +4053,7 @@
     <row r="11" spans="3:15">
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E11" s="1">
         <f>E10-$E$4</f>
@@ -4019,10 +4068,10 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -4030,7 +4079,7 @@
     <row r="12" spans="3:15">
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E12" s="1">
         <f>E11/12</f>
@@ -4045,7 +4094,7 @@
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L12" s="12">
         <v>0.05</v>
@@ -4069,7 +4118,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L13" s="12">
         <v>0.12</v>
@@ -4094,7 +4143,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L14" s="12">
         <v>0.2</v>
@@ -4115,7 +4164,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L15" s="12">
         <v>0.3</v>
@@ -4136,7 +4185,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L16" s="12">
         <v>0.4</v>
@@ -4194,7 +4243,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J20" s="1">
         <v>3500000</v>
@@ -4210,7 +4259,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J21" s="1">
         <f>IF(J20&lt;560000,J20-J20*L12,IF(J20&lt;1260000,J20-(J20*L13-M13),IF(J20&lt;2520000,J20-(J20*L14-M14),IF(J20&lt;4720000,J20-(J20*L15-M15),J20-(J20*L16-M16)))))</f>
@@ -5597,10 +5646,10 @@
         <v>0.14005196969697</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J3" s="1">
-        <v>23186151</v>
+        <v>21470696</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -5619,10 +5668,10 @@
         <v>0.0599474266391099</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J4" s="1">
-        <v>-6660000</v>
+        <v>-7860000</v>
       </c>
     </row>
     <row r="5" spans="2:11">
@@ -5641,13 +5690,13 @@
         <v>-0.0388919287890977</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J5" s="1">
-        <v>5590000</v>
+        <v>5790000</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -5669,7 +5718,7 @@
         <v>5</v>
       </c>
       <c r="J6" s="1">
-        <v>-1435278</v>
+        <v>-1389043</v>
       </c>
     </row>
     <row r="7" ht="16.95" spans="2:14">
@@ -5688,15 +5737,15 @@
         <v>0.0852958051483765</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J7" s="1">
-        <v>53765</v>
+        <v>61132</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9">
         <f>SUM(N8:N99)</f>
-        <v>0</v>
+        <v>61710</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -5715,17 +5764,20 @@
         <v>-0.0471663352257339</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="1">
         <f>N7</f>
-        <v>0</v>
+        <v>61710</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="N8" s="1">
+        <v>61710</v>
       </c>
       <c r="O8" s="4"/>
     </row>
@@ -5745,7 +5797,7 @@
         <v>-0.0242376362491937</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L9" s="4"/>
       <c r="O9" s="4"/>
@@ -5766,9 +5818,12 @@
         <v>0.0264542637625841</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="J10" s="9"/>
+        <v>109</v>
+      </c>
+      <c r="J10" s="9">
+        <f>股票損益!R12</f>
+        <v>313000</v>
+      </c>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="3">
@@ -5786,11 +5841,11 @@
         <v>0.0226648161548103</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J11" s="1">
         <f>SUM(J3:J10)</f>
-        <v>20734638</v>
+        <v>18447495</v>
       </c>
     </row>
     <row r="12" spans="2:5">
@@ -6039,27 +6094,32 @@
       <c r="B27" s="3">
         <v>46081</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="7" t="str">
+      <c r="C27" s="5">
+        <v>21685552</v>
+      </c>
+      <c r="D27" s="7">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E27" s="6" t="str">
+        <v>4112518</v>
+      </c>
+      <c r="E27" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.234024358002153</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="3">
         <v>46112</v>
       </c>
-      <c r="D28" s="1" t="str">
+      <c r="C28" s="1">
+        <v>18447495</v>
+      </c>
+      <c r="D28" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E28" s="6" t="str">
+        <v>-3238057</v>
+      </c>
+      <c r="E28" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-0.149318633899658</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -7698,10 +7758,10 @@
   <sheetData>
     <row r="1" spans="4:5">
       <c r="D1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="3:4">

--- a/股票損益&房貸試算收入試算.xlsx
+++ b/股票損益&房貸試算收入試算.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22391" windowHeight="10067" activeTab="2"/>
+    <workbookView windowWidth="22391" windowHeight="10067" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="股票損益" sheetId="1" r:id="rId1"/>
-    <sheet name="房貸收入試算" sheetId="2" r:id="rId2"/>
-    <sheet name="淨值表" sheetId="3" r:id="rId3"/>
-    <sheet name="東哥券差借券紀錄" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="股票損益 (2)" sheetId="2" r:id="rId2"/>
+    <sheet name="房貸收入試算" sheetId="3" r:id="rId3"/>
+    <sheet name="淨值表" sheetId="4" r:id="rId4"/>
+    <sheet name="東哥券差借券紀錄" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112">
   <si>
     <t>股利+借券</t>
   </si>
@@ -140,6 +141,9 @@
     <t>每月</t>
   </si>
   <si>
+    <t>裕慶(借券)</t>
+  </si>
+  <si>
     <t>質借兩次</t>
   </si>
   <si>
@@ -410,13 +414,7 @@
     <t>股利</t>
   </si>
   <si>
-    <t>台積電4/9</t>
-  </si>
-  <si>
     <t>股票尚未交割金額</t>
-  </si>
-  <si>
-    <t>借出去的股票市值</t>
   </si>
   <si>
     <t>Total</t>
@@ -434,18 +432,18 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="13">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="m/d;@"/>
-    <numFmt numFmtId="179" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
-    <numFmt numFmtId="180" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="181" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    <numFmt numFmtId="182" formatCode="0.0%"/>
-    <numFmt numFmtId="183" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="184" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="178" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
+    <numFmt numFmtId="179" formatCode="m/d;@"/>
+    <numFmt numFmtId="180" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="182" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
+    <numFmt numFmtId="183" formatCode="0.0%"/>
+    <numFmt numFmtId="184" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -483,20 +481,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -521,8 +505,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -537,7 +522,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -559,9 +559,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -569,7 +575,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -590,8 +596,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -599,22 +613,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -641,13 +639,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -659,25 +663,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -695,7 +687,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -707,13 +747,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -725,103 +807,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -864,6 +862,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -878,17 +887,6 @@
       </left>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -928,24 +926,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -974,6 +959,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -985,11 +985,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1031,7 +1029,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1046,130 +1044,130 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1177,46 +1175,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1225,7 +1223,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1">
+    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
@@ -1234,85 +1232,85 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="184" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1369,6 +1367,990 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.1505"/>
+          <c:y val="0.0481816075978689"/>
+          <c:w val="0.818944444444444"/>
+          <c:h val="0.717952281677091"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>淨值表!$B$2:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy/m/d;@</c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0" c:formatCode="yyyy/m/d;@">
+                  <c:v>45331</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="yyyy/m/d;@">
+                  <c:v>45356</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="yyyy/m/d;@">
+                  <c:v>45382</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="yyyy/m/d;@">
+                  <c:v>45412</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="yyyy/m/d;@">
+                  <c:v>45443</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="yyyy/m/d;@">
+                  <c:v>45473</c:v>
+                </c:pt>
+                <c:pt idx="6" c:formatCode="yyyy/m/d;@">
+                  <c:v>45504</c:v>
+                </c:pt>
+                <c:pt idx="7" c:formatCode="yyyy/m/d;@">
+                  <c:v>45535</c:v>
+                </c:pt>
+                <c:pt idx="8" c:formatCode="yyyy/m/d;@">
+                  <c:v>45565</c:v>
+                </c:pt>
+                <c:pt idx="9" c:formatCode="yyyy/m/d;@">
+                  <c:v>45596</c:v>
+                </c:pt>
+                <c:pt idx="10" c:formatCode="yyyy/m/d;@">
+                  <c:v>45626</c:v>
+                </c:pt>
+                <c:pt idx="11" c:formatCode="yyyy/m/d;@">
+                  <c:v>45657</c:v>
+                </c:pt>
+                <c:pt idx="12" c:formatCode="yyyy/m/d;@">
+                  <c:v>45688</c:v>
+                </c:pt>
+                <c:pt idx="13" c:formatCode="yyyy/m/d;@">
+                  <c:v>45747</c:v>
+                </c:pt>
+                <c:pt idx="14" c:formatCode="yyyy/m/d;@">
+                  <c:v>45749</c:v>
+                </c:pt>
+                <c:pt idx="15" c:formatCode="yyyy/m/d;@">
+                  <c:v>45777</c:v>
+                </c:pt>
+                <c:pt idx="16" c:formatCode="yyyy/m/d;@">
+                  <c:v>45806</c:v>
+                </c:pt>
+                <c:pt idx="17" c:formatCode="yyyy/m/d;@">
+                  <c:v>45838</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="yyyy/m/d;@">
+                  <c:v>45869</c:v>
+                </c:pt>
+                <c:pt idx="19" c:formatCode="yyyy/m/d;@">
+                  <c:v>45899</c:v>
+                </c:pt>
+                <c:pt idx="20" c:formatCode="yyyy/m/d;@">
+                  <c:v>45930</c:v>
+                </c:pt>
+                <c:pt idx="21" c:formatCode="yyyy/m/d;@">
+                  <c:v>45961</c:v>
+                </c:pt>
+                <c:pt idx="22" c:formatCode="yyyy/m/d;@">
+                  <c:v>45991</c:v>
+                </c:pt>
+                <c:pt idx="23" c:formatCode="yyyy/m/d;@">
+                  <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="24" c:formatCode="yyyy/m/d;@">
+                  <c:v>46053</c:v>
+                </c:pt>
+                <c:pt idx="25" c:formatCode="yyyy/m/d;@">
+                  <c:v>46081</c:v>
+                </c:pt>
+                <c:pt idx="26" c:formatCode="yyyy/m/d;@">
+                  <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="27" c:formatCode="yyyy/m/d;@">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="28" c:formatCode="yyyy/m/d;@">
+                  <c:v>46173</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>淨值表!$C$2:$C$30</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ ;[Red]\-#,##0\ </c:formatCode>
+                <c:ptCount val="29"/>
+                <c:pt idx="0" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>6600000</c:v>
+                </c:pt>
+                <c:pt idx="1" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7524343</c:v>
+                </c:pt>
+                <c:pt idx="2" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7975408</c:v>
+                </c:pt>
+                <c:pt idx="3" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7665229</c:v>
+                </c:pt>
+                <c:pt idx="4" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7569493</c:v>
+                </c:pt>
+                <c:pt idx="5" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8215139</c:v>
+                </c:pt>
+                <c:pt idx="6" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7827661</c:v>
+                </c:pt>
+                <c:pt idx="7" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7637937</c:v>
+                </c:pt>
+                <c:pt idx="8" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>7839993</c:v>
+                </c:pt>
+                <c:pt idx="9" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8017685</c:v>
+                </c:pt>
+                <c:pt idx="10" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8101815</c:v>
+                </c:pt>
+                <c:pt idx="11" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8506389</c:v>
+                </c:pt>
+                <c:pt idx="12" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>10316721</c:v>
+                </c:pt>
+                <c:pt idx="13" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8764502</c:v>
+                </c:pt>
+                <c:pt idx="14" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>9239455</c:v>
+                </c:pt>
+                <c:pt idx="15" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>8638664</c:v>
+                </c:pt>
+                <c:pt idx="16" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>9157060</c:v>
+                </c:pt>
+                <c:pt idx="17" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>9627683</c:v>
+                </c:pt>
+                <c:pt idx="18" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>10728568</c:v>
+                </c:pt>
+                <c:pt idx="19" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>10849001</c:v>
+                </c:pt>
+                <c:pt idx="20" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>12393462</c:v>
+                </c:pt>
+                <c:pt idx="21" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>14234577</c:v>
+                </c:pt>
+                <c:pt idx="22" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>13639890</c:v>
+                </c:pt>
+                <c:pt idx="23" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>14942275</c:v>
+                </c:pt>
+                <c:pt idx="24" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>17573034</c:v>
+                </c:pt>
+                <c:pt idx="25" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>21685552</c:v>
+                </c:pt>
+                <c:pt idx="26" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>18447495</c:v>
+                </c:pt>
+                <c:pt idx="27" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>25704540</c:v>
+                </c:pt>
+                <c:pt idx="28" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
+                  <c:v>28603591</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="731100761"/>
+        <c:axId val="533450541"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="731100761"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-TW" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="533450541"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="6"/>
+        <c:majorTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="533450541"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="29000000"/>
+          <c:min val="6000000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_ ;[Red]\-#,##0\ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="zh-TW" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="731100761"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="zh-TW"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>500380</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>168275</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>576580</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="圖表 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="4653280" y="2440940"/>
+        <a:ext cx="6995160" cy="4175125"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1661,7 +2643,7 @@
     <row r="2" spans="1:16">
       <c r="A2" s="17">
         <f>A1+M8</f>
-        <v>10128546</v>
+        <v>20114060</v>
       </c>
       <c r="C2" s="17"/>
       <c r="O2" s="1">
@@ -1689,28 +2671,31 @@
         <v>2026</v>
       </c>
       <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="D4" s="20">
+        <f>SUM($D5:$D10)</f>
+        <v>8538149</v>
+      </c>
+      <c r="E4" s="21"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="22" t="s">
         <v>0</v>
       </c>
       <c r="H4" s="19"/>
-      <c r="I4" s="35">
+      <c r="I4" s="20">
         <f>SUM($I5:$I18)</f>
-        <v>116360</v>
+        <v>117104</v>
       </c>
       <c r="J4" s="36"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="22"/>
+      <c r="B5" s="23"/>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>1273965</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="24">
         <v>45665</v>
       </c>
       <c r="H5" t="s">
@@ -1724,7 +2709,7 @@
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <v>6369897</v>
+        <v>8655253</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>4</v>
@@ -1752,12 +2737,12 @@
       </c>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="22"/>
+      <c r="B6" s="23"/>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="1">
-        <v>-16424</v>
+        <v>-73320</v>
       </c>
       <c r="G6" s="4">
         <v>46055</v>
@@ -1773,11 +2758,11 @@
         <v>14</v>
       </c>
       <c r="M6" s="1">
-        <v>803226</v>
+        <v>8457384</v>
       </c>
       <c r="N6" s="1">
         <f>Q12</f>
-        <v>-46000</v>
+        <v>0</v>
       </c>
       <c r="O6" s="1">
         <v>12000000</v>
@@ -1789,14 +2774,14 @@
         <f>(O6+P6)*1.6</f>
         <v>22400000</v>
       </c>
-      <c r="R6" s="39">
+      <c r="R6" s="38">
         <v>0.05</v>
       </c>
       <c r="S6" s="1">
         <f>Q6*R6</f>
         <v>1120000</v>
       </c>
-      <c r="T6" s="39">
+      <c r="T6" s="38">
         <v>0.03</v>
       </c>
       <c r="U6" s="1">
@@ -1809,12 +2794,12 @@
       </c>
     </row>
     <row r="7" ht="16.95" spans="2:23">
-      <c r="B7" s="22"/>
+      <c r="B7" s="23"/>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>4995996</v>
+        <v>7337504</v>
       </c>
       <c r="E7" s="13"/>
       <c r="G7" s="4">
@@ -1827,18 +2812,18 @@
         <v>61710</v>
       </c>
       <c r="J7" s="37"/>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="26" t="s">
         <v>15</v>
       </c>
       <c r="M7" s="9">
         <v>5234110</v>
       </c>
-      <c r="R7" s="39"/>
+      <c r="R7" s="38"/>
       <c r="S7" s="1">
         <f t="shared" ref="S7:V7" si="0">S6/12</f>
         <v>93333.3333333333</v>
       </c>
-      <c r="T7" s="39"/>
+      <c r="T7" s="38"/>
       <c r="U7" s="1">
         <f t="shared" si="0"/>
         <v>26000</v>
@@ -1852,25 +2837,32 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="22"/>
+      <c r="B8" s="23"/>
       <c r="E8" s="13"/>
-      <c r="G8" s="4"/>
-      <c r="I8" s="1"/>
+      <c r="G8" s="4">
+        <v>46142</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1">
+        <v>744</v>
+      </c>
       <c r="J8" s="37"/>
       <c r="L8"/>
       <c r="M8" s="1">
         <f>M5+M6-M7+N6</f>
-        <v>1893013</v>
+        <v>11878527</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T8" s="1"/>
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="22"/>
+      <c r="B9" s="23"/>
       <c r="E9" s="13"/>
       <c r="G9" s="4"/>
       <c r="I9" s="1"/>
@@ -1894,13 +2886,13 @@
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="B10" s="22"/>
+      <c r="B10" s="23"/>
       <c r="E10" s="13"/>
       <c r="G10" s="4"/>
       <c r="I10" s="1"/>
       <c r="J10" s="37"/>
       <c r="L10" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S10" s="1">
         <f t="shared" ref="S10:V10" si="1">S9/12</f>
@@ -1917,57 +2909,57 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="B11" s="22"/>
+      <c r="B11" s="23"/>
       <c r="E11" s="13"/>
       <c r="G11" s="4"/>
       <c r="I11" s="1"/>
       <c r="J11" s="37"/>
       <c r="M11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="22"/>
+      <c r="B12" s="23"/>
       <c r="G12" s="4"/>
       <c r="I12" s="1"/>
       <c r="J12" s="37"/>
       <c r="L12" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M12" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="13">
         <v>179.5</v>
       </c>
       <c r="O12" s="13">
-        <v>156.5</v>
+        <v>160</v>
       </c>
       <c r="P12" s="1">
         <v>0</v>
       </c>
       <c r="Q12" s="1">
         <f>(O12-N12)*M12*1000+P12</f>
-        <v>-46000</v>
+        <v>0</v>
       </c>
       <c r="R12" s="1">
         <f>O12*M12*1000</f>
-        <v>313000</v>
+        <v>0</v>
       </c>
       <c r="S12" s="40"/>
       <c r="T12" s="1"/>
@@ -1975,17 +2967,17 @@
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="22"/>
+      <c r="B13" s="23"/>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" s="4"/>
       <c r="I13" s="1"/>
       <c r="J13" s="37"/>
       <c r="N13" s="13"/>
-      <c r="O13" s="6">
+      <c r="O13" s="38">
         <f>(O12-N12)/N12</f>
-        <v>-0.128133704735376</v>
+        <v>-0.108635097493036</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
@@ -1998,9 +2990,9 @@
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="22"/>
+      <c r="B14" s="23"/>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G14" s="4"/>
       <c r="I14" s="1"/>
@@ -2008,7 +3000,7 @@
       <c r="Q14"/>
       <c r="R14" s="1">
         <f>SUM(R11:R13)</f>
-        <v>22628376</v>
+        <v>22315376</v>
       </c>
       <c r="S14"/>
       <c r="T14" s="1"/>
@@ -2016,9 +3008,9 @@
       <c r="V14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="22"/>
+      <c r="B15" s="23"/>
       <c r="C15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="1">
         <f>D13+D14</f>
@@ -2034,9 +3026,9 @@
       <c r="V15" s="1"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="22"/>
+      <c r="B16" s="23"/>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16" s="1">
         <f>D15-D29</f>
@@ -2047,21 +3039,21 @@
       <c r="J16" s="37"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="22"/>
+      <c r="B17" s="23"/>
       <c r="G17" s="4"/>
       <c r="I17" s="1"/>
       <c r="J17" s="37"/>
     </row>
     <row r="18" ht="16.95" spans="2:10">
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="26"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="38"/>
+      <c r="J18" s="39"/>
     </row>
     <row r="19" spans="3:3">
       <c r="C19" s="17"/>
@@ -2074,14 +3066,14 @@
         <v>2025</v>
       </c>
       <c r="C21" s="19"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
       <c r="F21" s="19"/>
-      <c r="G21" s="21" t="s">
+      <c r="G21" s="22" t="s">
         <v>0</v>
       </c>
       <c r="H21" s="19"/>
-      <c r="I21" s="35">
+      <c r="I21" s="20">
         <f>SUM($I22:$I36)</f>
         <v>490723</v>
       </c>
@@ -2090,14 +3082,14 @@
       <c r="O21"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="22"/>
+      <c r="B22" s="23"/>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>-139300</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="24">
         <v>45666</v>
       </c>
       <c r="H22" t="s">
@@ -2111,9 +3103,9 @@
       <c r="O22"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="22"/>
+      <c r="B23" s="23"/>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1">
         <v>-210100</v>
@@ -2122,7 +3114,7 @@
         <v>45706</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="1">
         <v>201960</v>
@@ -2132,9 +3124,9 @@
       <c r="O23"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="22"/>
+      <c r="B24" s="23"/>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D24" s="1">
         <v>-91300</v>
@@ -2143,7 +3135,7 @@
         <v>45723</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="1">
         <v>17325</v>
@@ -2153,9 +3145,9 @@
       <c r="O24"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="22"/>
+      <c r="B25" s="23"/>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" s="1">
         <v>-610300</v>
@@ -2164,7 +3156,7 @@
         <v>45733</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" s="1">
         <v>360</v>
@@ -2173,9 +3165,9 @@
       <c r="O25" s="13"/>
     </row>
     <row r="26" spans="2:29">
-      <c r="B26" s="22"/>
+      <c r="B26" s="23"/>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" s="1">
         <v>180900</v>
@@ -2184,7 +3176,7 @@
         <v>45737</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="1">
         <v>2078</v>
@@ -2197,9 +3189,9 @@
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="2:29">
-      <c r="B27" s="22"/>
+      <c r="B27" s="23"/>
       <c r="C27" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D27" s="1">
         <v>-165600</v>
@@ -2220,13 +3212,13 @@
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="2:29">
-      <c r="B28" s="22"/>
-      <c r="D28" s="27"/>
+      <c r="B28" s="23"/>
+      <c r="D28" s="28"/>
       <c r="G28" s="4">
         <v>45763</v>
       </c>
       <c r="H28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I28" s="1">
         <v>175500</v>
@@ -2238,9 +3230,9 @@
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="2:29">
-      <c r="B29" s="22"/>
+      <c r="B29" s="23"/>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D29" s="1">
         <v>5234110</v>
@@ -2261,9 +3253,9 @@
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="2:29">
-      <c r="B30" s="22"/>
+      <c r="B30" s="23"/>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" s="1">
         <f>SUM(D22:D27)+I21</f>
@@ -2285,9 +3277,9 @@
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="2:29">
-      <c r="B31" s="22"/>
+      <c r="B31" s="23"/>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D31" s="1">
         <f>D29+D30</f>
@@ -2302,11 +3294,11 @@
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="2:29">
-      <c r="B32" s="22"/>
+      <c r="B32" s="23"/>
       <c r="C32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="28">
+        <v>28</v>
+      </c>
+      <c r="D32" s="29">
         <f>D31-D47</f>
         <v>4458133</v>
       </c>
@@ -2322,7 +3314,7 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="2:29">
-      <c r="B33" s="22"/>
+      <c r="B33" s="23"/>
       <c r="G33" s="4"/>
       <c r="I33" s="1"/>
       <c r="J33" s="37"/>
@@ -2335,9 +3327,9 @@
       <c r="AC33" s="1"/>
     </row>
     <row r="34" spans="2:29">
-      <c r="B34" s="22"/>
+      <c r="B34" s="23"/>
       <c r="C34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G34" s="4"/>
       <c r="I34" s="1"/>
@@ -2351,9 +3343,9 @@
       <c r="AC34" s="1"/>
     </row>
     <row r="35" spans="2:29">
-      <c r="B35" s="22"/>
+      <c r="B35" s="23"/>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G35" s="4"/>
       <c r="I35" s="1"/>
@@ -2367,15 +3359,15 @@
       <c r="AC35" s="1"/>
     </row>
     <row r="36" ht="16.95" spans="2:29">
-      <c r="B36" s="24"/>
-      <c r="C36" s="25"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="25"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="26"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="38"/>
+      <c r="J36" s="39"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -2413,14 +3405,14 @@
         <v>2024</v>
       </c>
       <c r="C39" s="19"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
       <c r="F39" s="19"/>
-      <c r="G39" s="21" t="s">
+      <c r="G39" s="22" t="s">
         <v>0</v>
       </c>
       <c r="H39" s="19"/>
-      <c r="I39" s="35">
+      <c r="I39" s="20">
         <f>SUM(I$40:I$56)</f>
         <v>307025</v>
       </c>
@@ -2437,9 +3429,9 @@
       <c r="AC39" s="1"/>
     </row>
     <row r="40" spans="2:29">
-      <c r="B40" s="22"/>
+      <c r="B40" s="23"/>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D40" s="1">
         <v>-19000</v>
@@ -2448,7 +3440,7 @@
         <v>45303</v>
       </c>
       <c r="H40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I40" s="1">
         <v>6210</v>
@@ -2466,9 +3458,9 @@
       <c r="AC40" s="1"/>
     </row>
     <row r="41" spans="2:29">
-      <c r="B41" s="22"/>
+      <c r="B41" s="23"/>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41" s="1">
         <v>657000</v>
@@ -2477,7 +3469,7 @@
         <v>45343</v>
       </c>
       <c r="H41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I41" s="1">
         <v>12080</v>
@@ -2495,9 +3487,9 @@
       <c r="AC41" s="1"/>
     </row>
     <row r="42" spans="2:29">
-      <c r="B42" s="22"/>
+      <c r="B42" s="23"/>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D42" s="1">
         <v>-10000</v>
@@ -2506,7 +3498,7 @@
         <v>45376</v>
       </c>
       <c r="H42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I42" s="1">
         <v>3900</v>
@@ -2524,9 +3516,9 @@
       <c r="AC42" s="1"/>
     </row>
     <row r="43" spans="2:29">
-      <c r="B43" s="22"/>
+      <c r="B43" s="23"/>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D43" s="1">
         <v>663000</v>
@@ -2553,9 +3545,9 @@
       <c r="AC43" s="1"/>
     </row>
     <row r="44" spans="2:29">
-      <c r="B44" s="22"/>
+      <c r="B44" s="23"/>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44" s="1">
         <v>38600</v>
@@ -2564,7 +3556,7 @@
         <v>45400</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I44" s="1">
         <v>155000</v>
@@ -2582,9 +3574,9 @@
       <c r="AC44" s="1"/>
     </row>
     <row r="45" spans="2:10">
-      <c r="B45" s="22"/>
+      <c r="B45" s="23"/>
       <c r="C45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" s="1">
         <v>-74000</v>
@@ -2594,7 +3586,7 @@
         <v>45470</v>
       </c>
       <c r="H45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I45" s="1">
         <v>3879</v>
@@ -2602,7 +3594,7 @@
       <c r="J45" s="37"/>
     </row>
     <row r="46" spans="2:10">
-      <c r="B46" s="22"/>
+      <c r="B46" s="23"/>
       <c r="G46" s="4">
         <v>45484</v>
       </c>
@@ -2615,9 +3607,9 @@
       <c r="J46" s="37"/>
     </row>
     <row r="47" spans="2:10">
-      <c r="B47" s="22"/>
+      <c r="B47" s="23"/>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D47" s="1">
         <v>231000</v>
@@ -2626,7 +3618,7 @@
         <v>45489</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I47" s="1">
         <v>13902</v>
@@ -2634,9 +3626,9 @@
       <c r="J47" s="37"/>
     </row>
     <row r="48" spans="2:10">
-      <c r="B48" s="22"/>
+      <c r="B48" s="23"/>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" s="1">
         <f>SUM(D40:D45)+I39</f>
@@ -2646,7 +3638,7 @@
         <v>45506</v>
       </c>
       <c r="H48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1">
         <v>81600</v>
@@ -2654,9 +3646,9 @@
       <c r="J48" s="37"/>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="22"/>
+      <c r="B49" s="23"/>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D49" s="1">
         <f>D47+D48</f>
@@ -2666,7 +3658,7 @@
         <v>45513</v>
       </c>
       <c r="H49" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I49" s="1">
         <v>783</v>
@@ -2674,11 +3666,11 @@
       <c r="J49" s="37"/>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="22"/>
+      <c r="B50" s="23"/>
       <c r="C50" t="s">
-        <v>27</v>
-      </c>
-      <c r="D50" s="28">
+        <v>28</v>
+      </c>
+      <c r="D50" s="29">
         <f>D49-D67</f>
         <v>1455625</v>
       </c>
@@ -2686,7 +3678,7 @@
         <v>45523</v>
       </c>
       <c r="H50" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I50" s="1">
         <v>1161</v>
@@ -2694,12 +3686,12 @@
       <c r="J50" s="37"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="22"/>
+      <c r="B51" s="23"/>
       <c r="G51" s="4">
         <v>45525</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I51" s="1">
         <v>1237</v>
@@ -2707,9 +3699,9 @@
       <c r="J51" s="37"/>
     </row>
     <row r="52" spans="2:10">
-      <c r="B52" s="22"/>
+      <c r="B52" s="23"/>
       <c r="C52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G52" s="4">
         <v>45574</v>
@@ -2723,15 +3715,15 @@
       <c r="J52" s="37"/>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="29"/>
+      <c r="B53" s="30"/>
       <c r="C53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G53" s="4">
         <v>45643</v>
       </c>
       <c r="H53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I53" s="1">
         <v>1273</v>
@@ -2739,25 +3731,25 @@
       <c r="J53" s="37"/>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="29"/>
+      <c r="B54" s="30"/>
       <c r="J54" s="37"/>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="29"/>
-      <c r="G55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="G55" s="31"/>
       <c r="I55" s="1"/>
       <c r="J55" s="37"/>
     </row>
     <row r="56" ht="16.95" spans="2:10">
-      <c r="B56" s="24"/>
-      <c r="C56" s="25"/>
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="25"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="25"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
       <c r="I56" s="9"/>
-      <c r="J56" s="38"/>
+      <c r="J56" s="39"/>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="4"/>
@@ -2770,246 +3762,246 @@
         <v>2023</v>
       </c>
       <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
       <c r="F59" s="19"/>
-      <c r="G59" s="21" t="s">
-        <v>44</v>
+      <c r="G59" s="22" t="s">
+        <v>45</v>
       </c>
       <c r="H59" s="19"/>
-      <c r="I59" s="35">
+      <c r="I59" s="20">
         <f>SUM(I60:I66)</f>
         <v>103800</v>
       </c>
       <c r="J59" s="36"/>
     </row>
     <row r="60" spans="2:10">
-      <c r="B60" s="22"/>
-      <c r="C60" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="32">
+      <c r="B60" s="23"/>
+      <c r="C60" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="33">
         <v>346100</v>
       </c>
-      <c r="E60" s="33"/>
-      <c r="F60" s="31"/>
-      <c r="G60" s="34">
+      <c r="E60" s="34"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="35">
         <v>45135</v>
       </c>
-      <c r="H60" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="I60" s="33">
+      <c r="H60" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" s="34">
         <v>4750</v>
       </c>
       <c r="J60" s="37"/>
     </row>
     <row r="61" spans="2:10">
-      <c r="B61" s="22"/>
-      <c r="C61" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D61" s="32">
+      <c r="B61" s="23"/>
+      <c r="C61" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="33">
         <v>32738</v>
       </c>
-      <c r="E61" s="33"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="34">
+      <c r="E61" s="34"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="35">
         <v>45149</v>
       </c>
-      <c r="H61" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I61" s="33">
+      <c r="H61" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I61" s="34">
         <v>2300</v>
       </c>
       <c r="J61" s="37"/>
     </row>
     <row r="62" spans="2:10">
-      <c r="B62" s="22"/>
-      <c r="C62" s="31" t="s">
+      <c r="B62" s="23"/>
+      <c r="C62" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="33">
+        <v>-14900</v>
+      </c>
+      <c r="E62" s="34"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="35">
+        <v>45149</v>
+      </c>
+      <c r="H62" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="34">
+        <v>54266</v>
+      </c>
+      <c r="J62" s="37"/>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="23"/>
+      <c r="C63" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D63" s="33">
+        <v>-171900</v>
+      </c>
+      <c r="E63" s="34"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="35">
+        <v>45244</v>
+      </c>
+      <c r="H63" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I63" s="34">
+        <v>4790</v>
+      </c>
+      <c r="J63" s="37"/>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="B64" s="23"/>
+      <c r="C64" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="33">
+        <v>-68600</v>
+      </c>
+      <c r="E64" s="34"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="35">
+        <v>45244</v>
+      </c>
+      <c r="H64" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="32">
-        <v>-14900</v>
-      </c>
-      <c r="E62" s="33"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="34">
-        <v>45149</v>
-      </c>
-      <c r="H62" s="31" t="s">
+      <c r="I64" s="34">
+        <v>635</v>
+      </c>
+      <c r="J64" s="37"/>
+    </row>
+    <row r="65" spans="2:10">
+      <c r="B65" s="23"/>
+      <c r="C65" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" s="33">
+        <v>18500</v>
+      </c>
+      <c r="E65" s="34"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="35">
+        <v>45272</v>
+      </c>
+      <c r="H65" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="34">
+        <v>34599</v>
+      </c>
+      <c r="J65" s="37"/>
+    </row>
+    <row r="66" spans="2:10">
+      <c r="B66" s="23"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="35">
+        <v>45272</v>
+      </c>
+      <c r="H66" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="I62" s="33">
-        <v>54266</v>
-      </c>
-      <c r="J62" s="37"/>
-    </row>
-    <row r="63" spans="2:10">
-      <c r="B63" s="22"/>
-      <c r="C63" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D63" s="32">
-        <v>-171900</v>
-      </c>
-      <c r="E63" s="33"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="34">
-        <v>45244</v>
-      </c>
-      <c r="H63" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="I63" s="33">
-        <v>4790</v>
-      </c>
-      <c r="J63" s="37"/>
-    </row>
-    <row r="64" spans="2:10">
-      <c r="B64" s="22"/>
-      <c r="C64" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" s="32">
-        <v>-68600</v>
-      </c>
-      <c r="E64" s="33"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="34">
-        <v>45244</v>
-      </c>
-      <c r="H64" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I64" s="33">
-        <v>635</v>
-      </c>
-      <c r="J64" s="37"/>
-    </row>
-    <row r="65" spans="2:10">
-      <c r="B65" s="22"/>
-      <c r="C65" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="32">
-        <v>18500</v>
-      </c>
-      <c r="E65" s="33"/>
-      <c r="F65" s="31"/>
-      <c r="G65" s="34">
-        <v>45272</v>
-      </c>
-      <c r="H65" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="I65" s="33">
-        <v>34599</v>
-      </c>
-      <c r="J65" s="37"/>
-    </row>
-    <row r="66" spans="2:10">
-      <c r="B66" s="22"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="33"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="34">
-        <v>45272</v>
-      </c>
-      <c r="H66" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>2460</v>
       </c>
       <c r="J66" s="37"/>
     </row>
     <row r="67" spans="2:10">
-      <c r="B67" s="22"/>
-      <c r="C67" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="D67" s="32">
+      <c r="B67" s="23"/>
+      <c r="C67" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="33">
         <v>338000</v>
       </c>
-      <c r="E67" s="33"/>
-      <c r="F67" s="31"/>
-      <c r="G67" s="31"/>
-      <c r="H67" s="31"/>
-      <c r="I67" s="31"/>
+      <c r="E67" s="34"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
       <c r="J67" s="37"/>
     </row>
     <row r="68" spans="2:10">
-      <c r="B68" s="22"/>
-      <c r="C68" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="D68" s="32">
+      <c r="B68" s="23"/>
+      <c r="C68" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="33">
         <f>SUM(D60:D65)+I59</f>
         <v>245738</v>
       </c>
-      <c r="E68" s="33"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="31"/>
-      <c r="H68" s="31"/>
-      <c r="I68" s="31"/>
+      <c r="E68" s="34"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
       <c r="J68" s="37"/>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="22"/>
-      <c r="C69" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D69" s="33">
+      <c r="B69" s="23"/>
+      <c r="C69" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" s="34">
         <f>D67+D68</f>
         <v>583738</v>
       </c>
-      <c r="E69" s="33"/>
-      <c r="F69" s="31"/>
-      <c r="G69" s="31"/>
-      <c r="H69" s="31"/>
-      <c r="I69" s="31"/>
+      <c r="E69" s="34"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
       <c r="J69" s="37"/>
     </row>
     <row r="70" ht="16.95" spans="2:10">
       <c r="B70" s="41"/>
-      <c r="C70" s="25" t="s">
-        <v>27</v>
+      <c r="C70" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="D70" s="42">
         <f>D69-D84</f>
         <v>443038</v>
       </c>
       <c r="E70" s="9"/>
-      <c r="F70" s="25"/>
-      <c r="G70" s="25"/>
-      <c r="H70" s="25"/>
-      <c r="I70" s="25"/>
-      <c r="J70" s="38"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="39"/>
     </row>
     <row r="71" spans="2:10">
-      <c r="B71" s="31"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="31"/>
-      <c r="G71" s="31"/>
-      <c r="H71" s="31"/>
-      <c r="I71" s="31"/>
-      <c r="J71" s="33"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="34"/>
     </row>
     <row r="72" ht="16.95" spans="2:10">
-      <c r="B72" s="31"/>
-      <c r="C72" s="31"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
       <c r="D72" s="43"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="33"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="34"/>
     </row>
     <row r="73" spans="2:10">
       <c r="B73" s="18">
@@ -3017,197 +4009,197 @@
       </c>
       <c r="C73" s="19"/>
       <c r="D73" s="36"/>
-      <c r="E73" s="33"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="31"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="33"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="34"/>
     </row>
     <row r="74" spans="2:10">
-      <c r="B74" s="22"/>
-      <c r="C74" s="31" t="s">
-        <v>45</v>
+      <c r="B74" s="23"/>
+      <c r="C74" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="D74" s="37">
         <v>890500</v>
       </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="31"/>
-      <c r="H74" s="31"/>
-      <c r="I74" s="31"/>
-      <c r="J74" s="33"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="34"/>
     </row>
     <row r="75" spans="2:10">
-      <c r="B75" s="22"/>
-      <c r="C75" s="31" t="s">
-        <v>51</v>
+      <c r="B75" s="23"/>
+      <c r="C75" s="32" t="s">
+        <v>52</v>
       </c>
       <c r="D75" s="37">
         <v>-9600</v>
       </c>
-      <c r="F75" s="31"/>
-      <c r="G75" s="31"/>
-      <c r="H75" s="31"/>
-      <c r="I75" s="31"/>
-      <c r="J75" s="33"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="34"/>
     </row>
     <row r="76" spans="2:10">
-      <c r="B76" s="22"/>
-      <c r="C76" s="31" t="s">
-        <v>41</v>
+      <c r="B76" s="23"/>
+      <c r="C76" s="32" t="s">
+        <v>42</v>
       </c>
       <c r="D76" s="37">
         <v>-38800</v>
       </c>
-      <c r="F76" s="31"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="31"/>
-      <c r="I76" s="31"/>
-      <c r="J76" s="33"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="34"/>
     </row>
     <row r="77" spans="2:10">
-      <c r="B77" s="22"/>
-      <c r="C77" s="31" t="s">
-        <v>52</v>
+      <c r="B77" s="23"/>
+      <c r="C77" s="32" t="s">
+        <v>53</v>
       </c>
       <c r="D77" s="37">
         <v>137800</v>
       </c>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="33"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
+      <c r="J77" s="34"/>
     </row>
     <row r="78" spans="2:10">
-      <c r="B78" s="22"/>
-      <c r="C78" s="31" t="s">
-        <v>53</v>
+      <c r="B78" s="23"/>
+      <c r="C78" s="32" t="s">
+        <v>54</v>
       </c>
       <c r="D78" s="37">
         <v>-49300</v>
       </c>
-      <c r="F78" s="31"/>
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="33"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="34"/>
     </row>
     <row r="79" spans="2:10">
-      <c r="B79" s="22"/>
-      <c r="C79" s="31" t="s">
-        <v>54</v>
+      <c r="B79" s="23"/>
+      <c r="C79" s="32" t="s">
+        <v>55</v>
       </c>
       <c r="D79" s="37">
         <v>15600</v>
       </c>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="33"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="34"/>
     </row>
     <row r="80" spans="2:10">
-      <c r="B80" s="22"/>
-      <c r="C80" s="31" t="s">
-        <v>55</v>
+      <c r="B80" s="23"/>
+      <c r="C80" s="32" t="s">
+        <v>56</v>
       </c>
       <c r="D80" s="37">
         <v>-19600</v>
       </c>
-      <c r="F80" s="31"/>
-      <c r="G80" s="31"/>
-      <c r="H80" s="31"/>
-      <c r="I80" s="31"/>
-      <c r="J80" s="33"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="34"/>
     </row>
     <row r="81" spans="2:10">
-      <c r="B81" s="22"/>
-      <c r="C81" s="31" t="s">
-        <v>56</v>
+      <c r="B81" s="23"/>
+      <c r="C81" s="32" t="s">
+        <v>57</v>
       </c>
       <c r="D81" s="37">
         <v>58600</v>
       </c>
-      <c r="F81" s="31"/>
-      <c r="G81" s="31"/>
-      <c r="H81" s="31"/>
-      <c r="I81" s="31"/>
-      <c r="J81" s="33"/>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
+      <c r="J81" s="34"/>
     </row>
     <row r="82" spans="2:10">
-      <c r="B82" s="22"/>
+      <c r="B82" s="23"/>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D82" s="37">
         <v>75005</v>
       </c>
-      <c r="F82" s="31"/>
-      <c r="G82" s="31"/>
-      <c r="H82" s="31"/>
-      <c r="I82" s="31"/>
-      <c r="J82" s="33"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+      <c r="J82" s="34"/>
     </row>
     <row r="83" spans="2:10">
-      <c r="B83" s="22"/>
-      <c r="C83" s="31"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="32"/>
       <c r="D83" s="37"/>
-      <c r="F83" s="31"/>
-      <c r="G83" s="31"/>
-      <c r="H83" s="31"/>
-      <c r="I83" s="31"/>
-      <c r="J83" s="33"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="34"/>
     </row>
     <row r="84" spans="2:10">
-      <c r="B84" s="22"/>
-      <c r="C84" s="31" t="s">
-        <v>23</v>
+      <c r="B84" s="23"/>
+      <c r="C84" s="32" t="s">
+        <v>24</v>
       </c>
       <c r="D84" s="37">
         <v>140700</v>
       </c>
-      <c r="F84" s="31"/>
-      <c r="G84" s="31"/>
-      <c r="H84" s="31"/>
-      <c r="I84" s="31"/>
-      <c r="J84" s="33"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+      <c r="J84" s="34"/>
     </row>
     <row r="85" spans="2:10">
-      <c r="B85" s="22"/>
-      <c r="C85" s="31" t="s">
-        <v>25</v>
+      <c r="B85" s="23"/>
+      <c r="C85" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="D85" s="37">
         <f>SUM(D74:D82)</f>
         <v>1060205</v>
       </c>
-      <c r="F85" s="31"/>
-      <c r="G85" s="31"/>
-      <c r="H85" s="31"/>
-      <c r="I85" s="31"/>
-      <c r="J85" s="33"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
+      <c r="J85" s="34"/>
     </row>
     <row r="86" spans="2:10">
-      <c r="B86" s="22"/>
-      <c r="C86" s="31" t="s">
-        <v>26</v>
+      <c r="B86" s="23"/>
+      <c r="C86" s="32" t="s">
+        <v>27</v>
       </c>
       <c r="D86" s="37">
         <f>D84+D85</f>
         <v>1200905</v>
       </c>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="33"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="34"/>
     </row>
     <row r="87" ht="16.95" spans="2:4">
       <c r="B87" s="41"/>
-      <c r="C87" s="25" t="s">
-        <v>27</v>
+      <c r="C87" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="D87" s="44">
         <f>D86-D107</f>
@@ -3215,10 +4207,10 @@
       </c>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="27"/>
+      <c r="D88" s="28"/>
     </row>
     <row r="89" ht="16.95" spans="4:4">
-      <c r="D89" s="27"/>
+      <c r="D89" s="28"/>
     </row>
     <row r="90" spans="2:4">
       <c r="B90" s="18">
@@ -3228,157 +4220,157 @@
       <c r="D90" s="45"/>
     </row>
     <row r="91" spans="2:4">
-      <c r="B91" s="22"/>
+      <c r="B91" s="23"/>
       <c r="C91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D91" s="37">
         <v>11300</v>
       </c>
     </row>
     <row r="92" spans="2:4">
-      <c r="B92" s="22"/>
+      <c r="B92" s="23"/>
       <c r="C92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D92" s="37">
         <v>33300</v>
       </c>
     </row>
     <row r="93" spans="2:4">
-      <c r="B93" s="22"/>
+      <c r="B93" s="23"/>
       <c r="C93" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D93" s="37">
         <v>108700</v>
       </c>
     </row>
     <row r="94" spans="2:4">
-      <c r="B94" s="22"/>
+      <c r="B94" s="23"/>
       <c r="C94" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D94" s="37">
         <v>-14800</v>
       </c>
     </row>
     <row r="95" spans="2:4">
-      <c r="B95" s="22"/>
+      <c r="B95" s="23"/>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D95" s="37">
         <v>35300</v>
       </c>
     </row>
     <row r="96" spans="2:4">
-      <c r="B96" s="22"/>
+      <c r="B96" s="23"/>
       <c r="C96" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D96" s="37">
         <v>-8900</v>
       </c>
     </row>
     <row r="97" spans="2:4">
-      <c r="B97" s="22"/>
+      <c r="B97" s="23"/>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D97" s="37">
         <v>-6000</v>
       </c>
     </row>
     <row r="98" spans="2:4">
-      <c r="B98" s="22"/>
+      <c r="B98" s="23"/>
       <c r="C98" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D98" s="37">
         <v>56100</v>
       </c>
     </row>
     <row r="99" spans="2:4">
-      <c r="B99" s="22"/>
+      <c r="B99" s="23"/>
       <c r="C99" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D99" s="37">
         <v>1900</v>
       </c>
     </row>
     <row r="100" spans="2:4">
-      <c r="B100" s="22"/>
+      <c r="B100" s="23"/>
       <c r="C100" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D100" s="37">
         <v>-12700</v>
       </c>
     </row>
     <row r="101" spans="2:4">
-      <c r="B101" s="22"/>
+      <c r="B101" s="23"/>
       <c r="C101" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D101" s="37">
         <v>77700</v>
       </c>
     </row>
     <row r="102" spans="2:4">
-      <c r="B102" s="22"/>
+      <c r="B102" s="23"/>
       <c r="C102" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D102" s="37">
         <v>-13200</v>
       </c>
     </row>
     <row r="103" spans="2:4">
-      <c r="B103" s="22"/>
+      <c r="B103" s="23"/>
       <c r="C103" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D103" s="37">
         <v>-10500</v>
       </c>
     </row>
     <row r="104" spans="2:4">
-      <c r="B104" s="22"/>
+      <c r="B104" s="23"/>
       <c r="C104" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D104" s="37">
         <v>244900</v>
       </c>
     </row>
     <row r="105" spans="2:4">
-      <c r="B105" s="22"/>
+      <c r="B105" s="23"/>
       <c r="C105" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D105" s="37">
         <v>67032</v>
       </c>
     </row>
     <row r="106" spans="2:4">
-      <c r="B106" s="22"/>
+      <c r="B106" s="23"/>
       <c r="D106" s="37"/>
     </row>
     <row r="107" spans="2:4">
-      <c r="B107" s="22"/>
+      <c r="B107" s="23"/>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D107" s="37">
         <v>712600</v>
       </c>
     </row>
     <row r="108" spans="2:4">
-      <c r="B108" s="22"/>
+      <c r="B108" s="23"/>
       <c r="C108" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D108" s="37">
         <f>SUM(D91:D105)</f>
@@ -3386,9 +4378,9 @@
       </c>
     </row>
     <row r="109" spans="2:4">
-      <c r="B109" s="22"/>
+      <c r="B109" s="23"/>
       <c r="C109" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D109" s="37">
         <f>D107+D108</f>
@@ -3397,8 +4389,8 @@
     </row>
     <row r="110" ht="16.95" spans="2:4">
       <c r="B110" s="41"/>
-      <c r="C110" s="25" t="s">
-        <v>27</v>
+      <c r="C110" s="26" t="s">
+        <v>28</v>
       </c>
       <c r="D110" s="44">
         <f>D109-D118</f>
@@ -3414,49 +4406,49 @@
       <c r="D113" s="36"/>
     </row>
     <row r="114" spans="2:4">
-      <c r="B114" s="22"/>
+      <c r="B114" s="23"/>
       <c r="C114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D114" s="37">
         <v>49400</v>
       </c>
     </row>
     <row r="115" spans="2:4">
-      <c r="B115" s="22"/>
+      <c r="B115" s="23"/>
       <c r="C115" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D115" s="37">
         <v>64300</v>
       </c>
     </row>
     <row r="116" spans="2:4">
-      <c r="B116" s="22"/>
+      <c r="B116" s="23"/>
       <c r="C116" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D116" s="37">
         <v>-6000</v>
       </c>
     </row>
     <row r="117" spans="2:4">
-      <c r="B117" s="22"/>
+      <c r="B117" s="23"/>
       <c r="D117" s="37"/>
     </row>
     <row r="118" spans="2:4">
-      <c r="B118" s="22"/>
+      <c r="B118" s="23"/>
       <c r="C118" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D118" s="37">
         <v>63700</v>
       </c>
     </row>
     <row r="119" spans="2:4">
-      <c r="B119" s="22"/>
+      <c r="B119" s="23"/>
       <c r="C119" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D119" s="37">
         <f>SUM(D114:D116)</f>
@@ -3465,8 +4457,8 @@
     </row>
     <row r="120" ht="16.95" spans="2:4">
       <c r="B120" s="41"/>
-      <c r="C120" s="25" t="s">
-        <v>26</v>
+      <c r="C120" s="26" t="s">
+        <v>27</v>
       </c>
       <c r="D120" s="44">
         <f>D118+D119</f>
@@ -3474,274 +4466,274 @@
       </c>
     </row>
     <row r="121" spans="4:4">
-      <c r="D121" s="27"/>
+      <c r="D121" s="28"/>
     </row>
     <row r="122" spans="4:4">
-      <c r="D122" s="27"/>
+      <c r="D122" s="28"/>
     </row>
     <row r="123" spans="4:4">
-      <c r="D123" s="27"/>
+      <c r="D123" s="28"/>
     </row>
     <row r="124" spans="4:4">
-      <c r="D124" s="27"/>
+      <c r="D124" s="28"/>
     </row>
     <row r="125" spans="4:4">
-      <c r="D125" s="27"/>
+      <c r="D125" s="28"/>
     </row>
     <row r="126" spans="4:4">
-      <c r="D126" s="27"/>
+      <c r="D126" s="28"/>
     </row>
     <row r="127" spans="4:4">
-      <c r="D127" s="27"/>
+      <c r="D127" s="28"/>
     </row>
     <row r="128" spans="4:4">
-      <c r="D128" s="27"/>
+      <c r="D128" s="28"/>
     </row>
     <row r="129" spans="4:4">
-      <c r="D129" s="27"/>
+      <c r="D129" s="28"/>
     </row>
     <row r="130" spans="4:4">
-      <c r="D130" s="27"/>
+      <c r="D130" s="28"/>
     </row>
     <row r="131" spans="4:4">
-      <c r="D131" s="27"/>
+      <c r="D131" s="28"/>
     </row>
     <row r="132" spans="4:4">
-      <c r="D132" s="27"/>
+      <c r="D132" s="28"/>
     </row>
     <row r="133" spans="4:4">
-      <c r="D133" s="27"/>
+      <c r="D133" s="28"/>
     </row>
     <row r="134" spans="4:4">
-      <c r="D134" s="27"/>
+      <c r="D134" s="28"/>
     </row>
     <row r="135" spans="4:4">
-      <c r="D135" s="27"/>
+      <c r="D135" s="28"/>
     </row>
     <row r="136" spans="4:4">
-      <c r="D136" s="27"/>
+      <c r="D136" s="28"/>
     </row>
     <row r="137" spans="4:4">
-      <c r="D137" s="27"/>
+      <c r="D137" s="28"/>
     </row>
     <row r="138" spans="4:4">
-      <c r="D138" s="27"/>
+      <c r="D138" s="28"/>
     </row>
     <row r="139" spans="4:4">
-      <c r="D139" s="27"/>
+      <c r="D139" s="28"/>
     </row>
     <row r="140" spans="4:4">
-      <c r="D140" s="27"/>
+      <c r="D140" s="28"/>
     </row>
     <row r="141" spans="4:4">
-      <c r="D141" s="27"/>
+      <c r="D141" s="28"/>
     </row>
     <row r="142" spans="4:4">
-      <c r="D142" s="27"/>
+      <c r="D142" s="28"/>
     </row>
     <row r="143" spans="4:4">
-      <c r="D143" s="27"/>
+      <c r="D143" s="28"/>
     </row>
     <row r="144" spans="4:4">
-      <c r="D144" s="27"/>
+      <c r="D144" s="28"/>
     </row>
     <row r="145" spans="4:4">
-      <c r="D145" s="27"/>
+      <c r="D145" s="28"/>
     </row>
     <row r="146" spans="4:4">
-      <c r="D146" s="27"/>
+      <c r="D146" s="28"/>
     </row>
     <row r="147" spans="4:4">
-      <c r="D147" s="27"/>
+      <c r="D147" s="28"/>
     </row>
     <row r="148" spans="4:4">
-      <c r="D148" s="27"/>
+      <c r="D148" s="28"/>
     </row>
     <row r="149" spans="4:4">
-      <c r="D149" s="27"/>
+      <c r="D149" s="28"/>
     </row>
     <row r="150" spans="4:4">
-      <c r="D150" s="27"/>
+      <c r="D150" s="28"/>
     </row>
     <row r="151" spans="4:4">
-      <c r="D151" s="27"/>
+      <c r="D151" s="28"/>
     </row>
     <row r="152" spans="4:4">
-      <c r="D152" s="27"/>
+      <c r="D152" s="28"/>
     </row>
     <row r="153" spans="4:4">
-      <c r="D153" s="27"/>
+      <c r="D153" s="28"/>
     </row>
     <row r="154" spans="4:4">
-      <c r="D154" s="27"/>
+      <c r="D154" s="28"/>
     </row>
     <row r="155" spans="4:4">
-      <c r="D155" s="27"/>
+      <c r="D155" s="28"/>
     </row>
     <row r="156" spans="4:4">
-      <c r="D156" s="27"/>
+      <c r="D156" s="28"/>
     </row>
     <row r="157" spans="4:4">
-      <c r="D157" s="27"/>
+      <c r="D157" s="28"/>
     </row>
     <row r="158" spans="4:4">
-      <c r="D158" s="27"/>
+      <c r="D158" s="28"/>
     </row>
     <row r="159" spans="4:4">
-      <c r="D159" s="27"/>
+      <c r="D159" s="28"/>
     </row>
     <row r="160" spans="4:4">
-      <c r="D160" s="27"/>
+      <c r="D160" s="28"/>
     </row>
     <row r="161" spans="4:4">
-      <c r="D161" s="27"/>
+      <c r="D161" s="28"/>
     </row>
     <row r="162" spans="4:4">
-      <c r="D162" s="27"/>
+      <c r="D162" s="28"/>
     </row>
     <row r="163" spans="4:4">
-      <c r="D163" s="27"/>
+      <c r="D163" s="28"/>
     </row>
     <row r="164" spans="4:4">
-      <c r="D164" s="27"/>
+      <c r="D164" s="28"/>
     </row>
     <row r="165" spans="4:4">
-      <c r="D165" s="27"/>
+      <c r="D165" s="28"/>
     </row>
     <row r="166" spans="4:4">
-      <c r="D166" s="27"/>
+      <c r="D166" s="28"/>
     </row>
     <row r="167" spans="4:4">
-      <c r="D167" s="27"/>
+      <c r="D167" s="28"/>
     </row>
     <row r="168" spans="4:4">
-      <c r="D168" s="27"/>
+      <c r="D168" s="28"/>
     </row>
     <row r="169" spans="4:4">
-      <c r="D169" s="27"/>
+      <c r="D169" s="28"/>
     </row>
     <row r="170" spans="4:4">
-      <c r="D170" s="27"/>
+      <c r="D170" s="28"/>
     </row>
     <row r="171" spans="4:4">
-      <c r="D171" s="27"/>
+      <c r="D171" s="28"/>
     </row>
     <row r="172" spans="4:4">
-      <c r="D172" s="27"/>
+      <c r="D172" s="28"/>
     </row>
     <row r="173" spans="4:4">
-      <c r="D173" s="27"/>
+      <c r="D173" s="28"/>
     </row>
     <row r="174" spans="4:4">
-      <c r="D174" s="27"/>
+      <c r="D174" s="28"/>
     </row>
     <row r="175" spans="4:4">
-      <c r="D175" s="27"/>
+      <c r="D175" s="28"/>
     </row>
     <row r="176" spans="4:4">
-      <c r="D176" s="27"/>
+      <c r="D176" s="28"/>
     </row>
     <row r="177" spans="4:4">
-      <c r="D177" s="27"/>
+      <c r="D177" s="28"/>
     </row>
     <row r="178" spans="4:4">
-      <c r="D178" s="27"/>
+      <c r="D178" s="28"/>
     </row>
     <row r="179" spans="4:4">
-      <c r="D179" s="27"/>
+      <c r="D179" s="28"/>
     </row>
     <row r="180" spans="4:4">
-      <c r="D180" s="27"/>
+      <c r="D180" s="28"/>
     </row>
     <row r="181" spans="4:4">
-      <c r="D181" s="27"/>
+      <c r="D181" s="28"/>
     </row>
     <row r="182" spans="4:4">
-      <c r="D182" s="27"/>
+      <c r="D182" s="28"/>
     </row>
     <row r="183" spans="4:4">
-      <c r="D183" s="27"/>
+      <c r="D183" s="28"/>
     </row>
     <row r="184" spans="4:4">
-      <c r="D184" s="27"/>
+      <c r="D184" s="28"/>
     </row>
     <row r="185" spans="4:4">
-      <c r="D185" s="27"/>
+      <c r="D185" s="28"/>
     </row>
     <row r="186" spans="4:4">
-      <c r="D186" s="27"/>
+      <c r="D186" s="28"/>
     </row>
     <row r="187" spans="4:4">
-      <c r="D187" s="27"/>
+      <c r="D187" s="28"/>
     </row>
     <row r="188" spans="4:4">
-      <c r="D188" s="27"/>
+      <c r="D188" s="28"/>
     </row>
     <row r="189" spans="4:4">
-      <c r="D189" s="27"/>
+      <c r="D189" s="28"/>
     </row>
     <row r="190" spans="4:4">
-      <c r="D190" s="27"/>
+      <c r="D190" s="28"/>
     </row>
     <row r="191" spans="4:4">
-      <c r="D191" s="27"/>
+      <c r="D191" s="28"/>
     </row>
     <row r="192" spans="4:4">
-      <c r="D192" s="27"/>
+      <c r="D192" s="28"/>
     </row>
     <row r="193" spans="4:4">
-      <c r="D193" s="27"/>
+      <c r="D193" s="28"/>
     </row>
     <row r="194" spans="4:4">
-      <c r="D194" s="27"/>
+      <c r="D194" s="28"/>
     </row>
     <row r="195" spans="4:4">
-      <c r="D195" s="27"/>
+      <c r="D195" s="28"/>
     </row>
     <row r="196" spans="4:4">
-      <c r="D196" s="27"/>
+      <c r="D196" s="28"/>
     </row>
     <row r="197" spans="4:4">
-      <c r="D197" s="27"/>
+      <c r="D197" s="28"/>
     </row>
     <row r="198" spans="4:4">
-      <c r="D198" s="27"/>
+      <c r="D198" s="28"/>
     </row>
     <row r="199" spans="4:4">
-      <c r="D199" s="27"/>
+      <c r="D199" s="28"/>
     </row>
     <row r="200" spans="4:4">
-      <c r="D200" s="27"/>
+      <c r="D200" s="28"/>
     </row>
     <row r="201" spans="4:4">
-      <c r="D201" s="27"/>
+      <c r="D201" s="28"/>
     </row>
     <row r="202" spans="4:4">
-      <c r="D202" s="27"/>
+      <c r="D202" s="28"/>
     </row>
     <row r="203" spans="4:4">
-      <c r="D203" s="27"/>
+      <c r="D203" s="28"/>
     </row>
     <row r="204" spans="4:4">
-      <c r="D204" s="27"/>
+      <c r="D204" s="28"/>
     </row>
     <row r="205" spans="4:4">
-      <c r="D205" s="27"/>
+      <c r="D205" s="28"/>
     </row>
     <row r="206" spans="4:4">
-      <c r="D206" s="27"/>
+      <c r="D206" s="28"/>
     </row>
     <row r="207" spans="4:4">
-      <c r="D207" s="27"/>
+      <c r="D207" s="28"/>
     </row>
     <row r="208" spans="4:4">
-      <c r="D208" s="27"/>
+      <c r="D208" s="28"/>
     </row>
     <row r="209" spans="4:4">
-      <c r="D209" s="27"/>
+      <c r="D209" s="28"/>
     </row>
     <row r="210" spans="4:4">
-      <c r="D210" s="27"/>
+      <c r="D210" s="28"/>
     </row>
     <row r="211" spans="4:4">
       <c r="D211" s="46"/>
@@ -3762,6 +4754,2148 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr/>
+  <dimension ref="A1:AC213"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="2" max="2" width="10.1111111111111"/>
+    <col min="3" max="3" width="14.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.2222222222222" style="1"/>
+    <col min="5" max="5" width="11.3333333333333" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="11.5555555555556"/>
+    <col min="9" max="9" width="13.1111111111111" customWidth="1"/>
+    <col min="10" max="10" width="14.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="12" width="11.5555555555556" style="1"/>
+    <col min="13" max="15" width="10.6666666666667" style="1" customWidth="1"/>
+    <col min="16" max="17" width="10.4444444444444" style="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5555555555556" style="1"/>
+    <col min="19" max="19" width="10.4444444444444" style="1"/>
+    <col min="20" max="20" width="11.5555555555556"/>
+    <col min="21" max="21" width="15.6666666666667" customWidth="1"/>
+    <col min="22" max="22" width="10.4444444444444"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="17">
+        <f>D32+D50+D70+D87+D110+D120</f>
+        <v>8235533</v>
+      </c>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="17">
+        <f>A1+M8</f>
+        <v>20114060</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="O2" s="1">
+        <f>O6*R6</f>
+        <v>550000</v>
+      </c>
+      <c r="P2" s="1">
+        <f>O2/12</f>
+        <v>45833.3333333333</v>
+      </c>
+    </row>
+    <row r="3" ht="16.95" spans="3:16">
+      <c r="C3" s="17"/>
+      <c r="O3" s="1">
+        <f>(O6+P6)*R6-P6*T6</f>
+        <v>550000</v>
+      </c>
+      <c r="P3" s="1">
+        <f>O3/12</f>
+        <v>45833.3333333333</v>
+      </c>
+    </row>
+    <row r="4" ht="16.95" spans="2:10">
+      <c r="B4" s="18">
+        <v>2026</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20">
+        <f>SUM($D5:$D10)</f>
+        <v>8538149</v>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="20">
+        <f>SUM($I5:$I18)</f>
+        <v>117104</v>
+      </c>
+      <c r="J4" s="36"/>
+    </row>
+    <row r="5" spans="2:22">
+      <c r="B5" s="23"/>
+      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1273965</v>
+      </c>
+      <c r="G5" s="24">
+        <v>45665</v>
+      </c>
+      <c r="H5" t="s">
+        <v>2</v>
+      </c>
+      <c r="I5" s="1">
+        <v>48000</v>
+      </c>
+      <c r="J5" s="37"/>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M5" s="1">
+        <v>8655253</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="2:22">
+      <c r="B6" s="23"/>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="1">
+        <v>-73320</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46055</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1">
+        <v>6650</v>
+      </c>
+      <c r="J6" s="37"/>
+      <c r="L6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="1">
+        <v>8457384</v>
+      </c>
+      <c r="N6" s="1">
+        <f>Q12</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>10000000</v>
+      </c>
+      <c r="P6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <f>(O6+P6)*1.6</f>
+        <v>16000000</v>
+      </c>
+      <c r="R6" s="38">
+        <v>0.055</v>
+      </c>
+      <c r="S6" s="1">
+        <f>Q6*R6</f>
+        <v>880000</v>
+      </c>
+      <c r="T6" s="38">
+        <v>0.03</v>
+      </c>
+      <c r="U6" s="1">
+        <f>(Q6-O6)*T6</f>
+        <v>180000</v>
+      </c>
+      <c r="V6" s="1">
+        <f>S6-U6</f>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="7" ht="16.95" spans="2:23">
+      <c r="B7" s="23"/>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7337504</v>
+      </c>
+      <c r="E7" s="13"/>
+      <c r="G7" s="4">
+        <v>46121</v>
+      </c>
+      <c r="H7" t="s">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>61710</v>
+      </c>
+      <c r="J7" s="37"/>
+      <c r="L7" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="9">
+        <v>5234110</v>
+      </c>
+      <c r="R7" s="38"/>
+      <c r="S7" s="1">
+        <f t="shared" ref="S7:V7" si="0">S6/12</f>
+        <v>73333.3333333333</v>
+      </c>
+      <c r="T7" s="38"/>
+      <c r="U7" s="1">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+      <c r="V7" s="1">
+        <f t="shared" si="0"/>
+        <v>58333.3333333333</v>
+      </c>
+      <c r="W7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="2:22">
+      <c r="B8" s="23"/>
+      <c r="E8" s="13"/>
+      <c r="G8" s="4">
+        <v>46142</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="1">
+        <v>744</v>
+      </c>
+      <c r="J8" s="37"/>
+      <c r="L8"/>
+      <c r="M8" s="1">
+        <f>M5+M6-M7+N6</f>
+        <v>11878527</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T8" s="1"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+    </row>
+    <row r="9" spans="2:22">
+      <c r="B9" s="23"/>
+      <c r="E9" s="13"/>
+      <c r="G9" s="4"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="37"/>
+      <c r="Q9" s="1">
+        <f>(O6+P6)*1.96</f>
+        <v>19600000</v>
+      </c>
+      <c r="S9" s="1">
+        <f>Q9*R6</f>
+        <v>1078000</v>
+      </c>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1">
+        <f>(Q9-O6)*T6</f>
+        <v>288000</v>
+      </c>
+      <c r="V9" s="1">
+        <f>S9-U9</f>
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:22">
+      <c r="B10" s="23"/>
+      <c r="E10" s="13"/>
+      <c r="G10" s="4"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="37"/>
+      <c r="L10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S10" s="1">
+        <f t="shared" ref="S10:V10" si="1">S9/12</f>
+        <v>89833.3333333333</v>
+      </c>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1">
+        <f t="shared" si="1"/>
+        <v>24000</v>
+      </c>
+      <c r="V10" s="1">
+        <f t="shared" si="1"/>
+        <v>65833.3333333333</v>
+      </c>
+    </row>
+    <row r="11" spans="2:22">
+      <c r="B11" s="23"/>
+      <c r="E11" s="13"/>
+      <c r="G11" s="4"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="37"/>
+      <c r="M11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+    </row>
+    <row r="12" spans="2:22">
+      <c r="B12" s="23"/>
+      <c r="G12" s="4"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="37"/>
+      <c r="L12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="13">
+        <v>179.5</v>
+      </c>
+      <c r="O12" s="13">
+        <v>160</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <f>(O12-N12)*M12*1000+P12</f>
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <f>O12*M12*1000</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="40"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+    </row>
+    <row r="13" spans="2:22">
+      <c r="B13" s="23"/>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="37"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="38">
+        <f>(O12-N12)/N12</f>
+        <v>-0.108635097493036</v>
+      </c>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13" s="7">
+        <v>22315376</v>
+      </c>
+      <c r="S13"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="2:22">
+      <c r="B14" s="23"/>
+      <c r="C14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="37"/>
+      <c r="Q14"/>
+      <c r="R14" s="1">
+        <f>SUM(R11:R13)</f>
+        <v>22315376</v>
+      </c>
+      <c r="S14"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="2:22">
+      <c r="B15" s="23"/>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1">
+        <f>D13+D14</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="37"/>
+      <c r="Q15"/>
+      <c r="S15"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="23"/>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="1">
+        <f>D15-D29</f>
+        <v>-5234110</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="37"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="23"/>
+      <c r="G17" s="4"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="37"/>
+    </row>
+    <row r="18" ht="16.95" spans="2:10">
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="39"/>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="17"/>
+    </row>
+    <row r="20" ht="16.95" spans="3:3">
+      <c r="C20" s="17"/>
+    </row>
+    <row r="21" ht="16.95" spans="2:15">
+      <c r="B21" s="18">
+        <v>2025</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="20">
+        <f>SUM($I22:$I36)</f>
+        <v>490723</v>
+      </c>
+      <c r="J21" s="36"/>
+      <c r="N21" s="4"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" spans="2:15">
+      <c r="B22" s="23"/>
+      <c r="C22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="1">
+        <v>-139300</v>
+      </c>
+      <c r="G22" s="24">
+        <v>45666</v>
+      </c>
+      <c r="H22" t="s">
+        <v>2</v>
+      </c>
+      <c r="I22" s="1">
+        <v>12000</v>
+      </c>
+      <c r="J22" s="37"/>
+      <c r="N22" s="4"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" spans="2:15">
+      <c r="B23" s="23"/>
+      <c r="C23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="1">
+        <v>-210100</v>
+      </c>
+      <c r="G23" s="4">
+        <v>45706</v>
+      </c>
+      <c r="H23" t="s">
+        <v>31</v>
+      </c>
+      <c r="I23" s="1">
+        <v>201960</v>
+      </c>
+      <c r="J23" s="37"/>
+      <c r="N23" s="4"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" spans="2:15">
+      <c r="B24" s="23"/>
+      <c r="C24" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="1">
+        <v>-91300</v>
+      </c>
+      <c r="G24" s="4">
+        <v>45723</v>
+      </c>
+      <c r="H24" t="s">
+        <v>33</v>
+      </c>
+      <c r="I24" s="1">
+        <v>17325</v>
+      </c>
+      <c r="J24" s="37"/>
+      <c r="N24" s="4"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" spans="2:15">
+      <c r="B25" s="23"/>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="1">
+        <v>-610300</v>
+      </c>
+      <c r="G25" s="4">
+        <v>45733</v>
+      </c>
+      <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="1">
+        <v>360</v>
+      </c>
+      <c r="J25" s="37"/>
+      <c r="O25" s="13"/>
+    </row>
+    <row r="26" spans="2:29">
+      <c r="B26" s="23"/>
+      <c r="C26" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="1">
+        <v>180900</v>
+      </c>
+      <c r="G26" s="4">
+        <v>45737</v>
+      </c>
+      <c r="H26" t="s">
+        <v>33</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2078</v>
+      </c>
+      <c r="J26" s="37"/>
+      <c r="O26" s="13"/>
+      <c r="Z26" s="1"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" spans="2:29">
+      <c r="B27" s="23"/>
+      <c r="C27" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="1">
+        <v>-165600</v>
+      </c>
+      <c r="G27" s="4">
+        <v>45757</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>20250</v>
+      </c>
+      <c r="J27" s="37"/>
+      <c r="Z27" s="1"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" spans="2:29">
+      <c r="B28" s="23"/>
+      <c r="D28" s="28"/>
+      <c r="G28" s="4">
+        <v>45763</v>
+      </c>
+      <c r="H28" t="s">
+        <v>34</v>
+      </c>
+      <c r="I28" s="1">
+        <v>175500</v>
+      </c>
+      <c r="J28" s="37"/>
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" spans="2:29">
+      <c r="B29" s="23"/>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="1">
+        <v>5234110</v>
+      </c>
+      <c r="G29" s="4">
+        <v>45848</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29" s="1">
+        <v>20250</v>
+      </c>
+      <c r="J29" s="37"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+    </row>
+    <row r="30" spans="2:29">
+      <c r="B30" s="23"/>
+      <c r="C30" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="1">
+        <f>SUM(D22:D27)+I21</f>
+        <v>-544977</v>
+      </c>
+      <c r="G30" s="4">
+        <v>45939</v>
+      </c>
+      <c r="H30" t="s">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>41000</v>
+      </c>
+      <c r="J30" s="37"/>
+      <c r="Z30" s="1"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+    </row>
+    <row r="31" spans="2:29">
+      <c r="B31" s="23"/>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" s="1">
+        <f>D29+D30</f>
+        <v>4689133</v>
+      </c>
+      <c r="G31" s="4"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="37"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+    </row>
+    <row r="32" spans="2:29">
+      <c r="B32" s="23"/>
+      <c r="C32" t="s">
+        <v>28</v>
+      </c>
+      <c r="D32" s="29">
+        <f>D31-D47</f>
+        <v>4458133</v>
+      </c>
+      <c r="G32" s="4"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="37"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
+      <c r="Z32" s="1"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+    </row>
+    <row r="33" spans="2:29">
+      <c r="B33" s="23"/>
+      <c r="G33" s="4"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="37"/>
+      <c r="W33" s="1"/>
+      <c r="X33" s="1"/>
+      <c r="Y33" s="1"/>
+      <c r="Z33" s="1"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+    </row>
+    <row r="34" spans="2:29">
+      <c r="B34" s="23"/>
+      <c r="C34" t="s">
+        <v>38</v>
+      </c>
+      <c r="G34" s="4"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="37"/>
+      <c r="W34" s="1"/>
+      <c r="X34" s="1"/>
+      <c r="Y34" s="1"/>
+      <c r="Z34" s="1"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+    </row>
+    <row r="35" spans="2:29">
+      <c r="B35" s="23"/>
+      <c r="C35" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="4"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="37"/>
+      <c r="W35" s="1"/>
+      <c r="X35" s="1"/>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+    </row>
+    <row r="36" ht="16.95" spans="2:29">
+      <c r="B36" s="25"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="39"/>
+      <c r="W36" s="1"/>
+      <c r="X36" s="1"/>
+      <c r="Y36" s="1"/>
+      <c r="Z36" s="1"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+    </row>
+    <row r="37" spans="20:29">
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="1"/>
+      <c r="X37" s="1"/>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+    </row>
+    <row r="38" ht="16.95" spans="20:29">
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+    </row>
+    <row r="39" ht="16.95" spans="2:29">
+      <c r="B39" s="18">
+        <v>2024</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="20">
+        <f>SUM(I$40:I$56)</f>
+        <v>307025</v>
+      </c>
+      <c r="J39" s="36"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+    </row>
+    <row r="40" spans="2:29">
+      <c r="B40" s="23"/>
+      <c r="C40" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="1">
+        <v>-19000</v>
+      </c>
+      <c r="G40" s="4">
+        <v>45303</v>
+      </c>
+      <c r="H40" t="s">
+        <v>41</v>
+      </c>
+      <c r="I40" s="1">
+        <v>6210</v>
+      </c>
+      <c r="J40" s="37"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+    </row>
+    <row r="41" spans="2:29">
+      <c r="B41" s="23"/>
+      <c r="C41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="1">
+        <v>657000</v>
+      </c>
+      <c r="G41" s="4">
+        <v>45343</v>
+      </c>
+      <c r="H41" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="1">
+        <v>12080</v>
+      </c>
+      <c r="J41" s="37"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
+      <c r="Z41" s="1"/>
+      <c r="AA41" s="1"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+    </row>
+    <row r="42" spans="2:29">
+      <c r="B42" s="23"/>
+      <c r="C42" t="s">
+        <v>41</v>
+      </c>
+      <c r="D42" s="1">
+        <v>-10000</v>
+      </c>
+      <c r="G42" s="4">
+        <v>45376</v>
+      </c>
+      <c r="H42" t="s">
+        <v>41</v>
+      </c>
+      <c r="I42" s="1">
+        <v>3900</v>
+      </c>
+      <c r="J42" s="37"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+      <c r="Y42" s="1"/>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+    </row>
+    <row r="43" spans="2:29">
+      <c r="B43" s="23"/>
+      <c r="C43" t="s">
+        <v>43</v>
+      </c>
+      <c r="D43" s="1">
+        <v>663000</v>
+      </c>
+      <c r="G43" s="4">
+        <v>45393</v>
+      </c>
+      <c r="H43" t="s">
+        <v>2</v>
+      </c>
+      <c r="I43" s="1">
+        <v>7000</v>
+      </c>
+      <c r="J43" s="37"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+      <c r="Y43" s="1"/>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+    </row>
+    <row r="44" spans="2:29">
+      <c r="B44" s="23"/>
+      <c r="C44" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="1">
+        <v>38600</v>
+      </c>
+      <c r="G44" s="4">
+        <v>45400</v>
+      </c>
+      <c r="H44" t="s">
+        <v>34</v>
+      </c>
+      <c r="I44" s="1">
+        <v>155000</v>
+      </c>
+      <c r="J44" s="37"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="23"/>
+      <c r="C45" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="1">
+        <v>-74000</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="G45" s="4">
+        <v>45470</v>
+      </c>
+      <c r="H45" t="s">
+        <v>44</v>
+      </c>
+      <c r="I45" s="1">
+        <v>3879</v>
+      </c>
+      <c r="J45" s="37"/>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="23"/>
+      <c r="G46" s="4">
+        <v>45484</v>
+      </c>
+      <c r="H46" t="s">
+        <v>2</v>
+      </c>
+      <c r="I46" s="1">
+        <v>7000</v>
+      </c>
+      <c r="J46" s="37"/>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="23"/>
+      <c r="C47" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1">
+        <v>231000</v>
+      </c>
+      <c r="G47" s="4">
+        <v>45489</v>
+      </c>
+      <c r="H47" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" s="1">
+        <v>13902</v>
+      </c>
+      <c r="J47" s="37"/>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="23"/>
+      <c r="C48" t="s">
+        <v>26</v>
+      </c>
+      <c r="D48" s="1">
+        <f>SUM(D40:D45)+I39</f>
+        <v>1562625</v>
+      </c>
+      <c r="G48" s="4">
+        <v>45506</v>
+      </c>
+      <c r="H48" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" s="1">
+        <v>81600</v>
+      </c>
+      <c r="J48" s="37"/>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="23"/>
+      <c r="C49" t="s">
+        <v>27</v>
+      </c>
+      <c r="D49" s="1">
+        <f>D47+D48</f>
+        <v>1793625</v>
+      </c>
+      <c r="G49" s="4">
+        <v>45513</v>
+      </c>
+      <c r="H49" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="1">
+        <v>783</v>
+      </c>
+      <c r="J49" s="37"/>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="23"/>
+      <c r="C50" t="s">
+        <v>28</v>
+      </c>
+      <c r="D50" s="29">
+        <f>D49-D67</f>
+        <v>1455625</v>
+      </c>
+      <c r="G50" s="4">
+        <v>45523</v>
+      </c>
+      <c r="H50" t="s">
+        <v>44</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1161</v>
+      </c>
+      <c r="J50" s="37"/>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="23"/>
+      <c r="G51" s="4">
+        <v>45525</v>
+      </c>
+      <c r="H51" t="s">
+        <v>35</v>
+      </c>
+      <c r="I51" s="1">
+        <v>1237</v>
+      </c>
+      <c r="J51" s="37"/>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="23"/>
+      <c r="C52" t="s">
+        <v>38</v>
+      </c>
+      <c r="G52" s="4">
+        <v>45574</v>
+      </c>
+      <c r="H52" t="s">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1">
+        <v>12000</v>
+      </c>
+      <c r="J52" s="37"/>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="30"/>
+      <c r="C53" t="s">
+        <v>39</v>
+      </c>
+      <c r="G53" s="4">
+        <v>45643</v>
+      </c>
+      <c r="H53" t="s">
+        <v>44</v>
+      </c>
+      <c r="I53" s="1">
+        <v>1273</v>
+      </c>
+      <c r="J53" s="37"/>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="30"/>
+      <c r="J54" s="37"/>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="30"/>
+      <c r="G55" s="31"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="37"/>
+    </row>
+    <row r="56" ht="16.95" spans="2:10">
+      <c r="B56" s="25"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="27"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="39"/>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" s="4"/>
+    </row>
+    <row r="58" ht="16.95" spans="2:2">
+      <c r="B58" s="4"/>
+    </row>
+    <row r="59" ht="16.95" spans="2:10">
+      <c r="B59" s="18">
+        <v>2023</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="20">
+        <f>SUM(I60:I66)</f>
+        <v>103800</v>
+      </c>
+      <c r="J59" s="36"/>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="B60" s="23"/>
+      <c r="C60" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="33">
+        <v>346100</v>
+      </c>
+      <c r="E60" s="34"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="35">
+        <v>45135</v>
+      </c>
+      <c r="H60" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="I60" s="34">
+        <v>4750</v>
+      </c>
+      <c r="J60" s="37"/>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="23"/>
+      <c r="C61" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="33">
+        <v>32738</v>
+      </c>
+      <c r="E61" s="34"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="35">
+        <v>45149</v>
+      </c>
+      <c r="H61" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I61" s="34">
+        <v>2300</v>
+      </c>
+      <c r="J61" s="37"/>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="B62" s="23"/>
+      <c r="C62" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D62" s="33">
+        <v>-14900</v>
+      </c>
+      <c r="E62" s="34"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="35">
+        <v>45149</v>
+      </c>
+      <c r="H62" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I62" s="34">
+        <v>54266</v>
+      </c>
+      <c r="J62" s="37"/>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="23"/>
+      <c r="C63" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D63" s="33">
+        <v>-171900</v>
+      </c>
+      <c r="E63" s="34"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="35">
+        <v>45244</v>
+      </c>
+      <c r="H63" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="I63" s="34">
+        <v>4790</v>
+      </c>
+      <c r="J63" s="37"/>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="B64" s="23"/>
+      <c r="C64" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="33">
+        <v>-68600</v>
+      </c>
+      <c r="E64" s="34"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="35">
+        <v>45244</v>
+      </c>
+      <c r="H64" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I64" s="34">
+        <v>635</v>
+      </c>
+      <c r="J64" s="37"/>
+    </row>
+    <row r="65" spans="2:10">
+      <c r="B65" s="23"/>
+      <c r="C65" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65" s="33">
+        <v>18500</v>
+      </c>
+      <c r="E65" s="34"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="35">
+        <v>45272</v>
+      </c>
+      <c r="H65" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="I65" s="34">
+        <v>34599</v>
+      </c>
+      <c r="J65" s="37"/>
+    </row>
+    <row r="66" spans="2:10">
+      <c r="B66" s="23"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="33"/>
+      <c r="E66" s="34"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="35">
+        <v>45272</v>
+      </c>
+      <c r="H66" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="I66" s="34">
+        <v>2460</v>
+      </c>
+      <c r="J66" s="37"/>
+    </row>
+    <row r="67" spans="2:10">
+      <c r="B67" s="23"/>
+      <c r="C67" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="33">
+        <v>338000</v>
+      </c>
+      <c r="E67" s="34"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
+      <c r="J67" s="37"/>
+    </row>
+    <row r="68" spans="2:10">
+      <c r="B68" s="23"/>
+      <c r="C68" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" s="33">
+        <f>SUM(D60:D65)+I59</f>
+        <v>245738</v>
+      </c>
+      <c r="E68" s="34"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
+      <c r="J68" s="37"/>
+    </row>
+    <row r="69" spans="2:10">
+      <c r="B69" s="23"/>
+      <c r="C69" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D69" s="34">
+        <f>D67+D68</f>
+        <v>583738</v>
+      </c>
+      <c r="E69" s="34"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="37"/>
+    </row>
+    <row r="70" ht="16.95" spans="2:10">
+      <c r="B70" s="41"/>
+      <c r="C70" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D70" s="42">
+        <f>D69-D84</f>
+        <v>443038</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="39"/>
+    </row>
+    <row r="71" spans="2:10">
+      <c r="B71" s="32"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
+      <c r="J71" s="34"/>
+    </row>
+    <row r="72" ht="16.95" spans="2:10">
+      <c r="B72" s="32"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="43"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="34"/>
+    </row>
+    <row r="73" spans="2:10">
+      <c r="B73" s="18">
+        <v>2022</v>
+      </c>
+      <c r="C73" s="19"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
+      <c r="J73" s="34"/>
+    </row>
+    <row r="74" spans="2:10">
+      <c r="B74" s="23"/>
+      <c r="C74" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D74" s="37">
+        <v>890500</v>
+      </c>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="34"/>
+    </row>
+    <row r="75" spans="2:10">
+      <c r="B75" s="23"/>
+      <c r="C75" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75" s="37">
+        <v>-9600</v>
+      </c>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
+      <c r="J75" s="34"/>
+    </row>
+    <row r="76" spans="2:10">
+      <c r="B76" s="23"/>
+      <c r="C76" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D76" s="37">
+        <v>-38800</v>
+      </c>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="34"/>
+    </row>
+    <row r="77" spans="2:10">
+      <c r="B77" s="23"/>
+      <c r="C77" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D77" s="37">
+        <v>137800</v>
+      </c>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
+      <c r="J77" s="34"/>
+    </row>
+    <row r="78" spans="2:10">
+      <c r="B78" s="23"/>
+      <c r="C78" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="37">
+        <v>-49300</v>
+      </c>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+      <c r="J78" s="34"/>
+    </row>
+    <row r="79" spans="2:10">
+      <c r="B79" s="23"/>
+      <c r="C79" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="37">
+        <v>15600</v>
+      </c>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="34"/>
+    </row>
+    <row r="80" spans="2:10">
+      <c r="B80" s="23"/>
+      <c r="C80" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D80" s="37">
+        <v>-19600</v>
+      </c>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
+      <c r="J80" s="34"/>
+    </row>
+    <row r="81" spans="2:10">
+      <c r="B81" s="23"/>
+      <c r="C81" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="37">
+        <v>58600</v>
+      </c>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
+      <c r="J81" s="34"/>
+    </row>
+    <row r="82" spans="2:10">
+      <c r="B82" s="23"/>
+      <c r="C82" t="s">
+        <v>48</v>
+      </c>
+      <c r="D82" s="37">
+        <v>75005</v>
+      </c>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
+      <c r="J82" s="34"/>
+    </row>
+    <row r="83" spans="2:10">
+      <c r="B83" s="23"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="37"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
+      <c r="J83" s="34"/>
+    </row>
+    <row r="84" spans="2:10">
+      <c r="B84" s="23"/>
+      <c r="C84" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="37">
+        <v>140700</v>
+      </c>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
+      <c r="J84" s="34"/>
+    </row>
+    <row r="85" spans="2:10">
+      <c r="B85" s="23"/>
+      <c r="C85" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D85" s="37">
+        <f>SUM(D74:D82)</f>
+        <v>1060205</v>
+      </c>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
+      <c r="J85" s="34"/>
+    </row>
+    <row r="86" spans="2:10">
+      <c r="B86" s="23"/>
+      <c r="C86" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="D86" s="37">
+        <f>D84+D85</f>
+        <v>1200905</v>
+      </c>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="34"/>
+    </row>
+    <row r="87" ht="16.95" spans="2:4">
+      <c r="B87" s="41"/>
+      <c r="C87" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D87" s="44">
+        <f>D86-D107</f>
+        <v>488305</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="28"/>
+    </row>
+    <row r="89" ht="16.95" spans="4:4">
+      <c r="D89" s="28"/>
+    </row>
+    <row r="90" spans="2:4">
+      <c r="B90" s="18">
+        <v>2021</v>
+      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="45"/>
+    </row>
+    <row r="91" spans="2:4">
+      <c r="B91" s="23"/>
+      <c r="C91" t="s">
+        <v>58</v>
+      </c>
+      <c r="D91" s="37">
+        <v>11300</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4">
+      <c r="B92" s="23"/>
+      <c r="C92" t="s">
+        <v>59</v>
+      </c>
+      <c r="D92" s="37">
+        <v>33300</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4">
+      <c r="B93" s="23"/>
+      <c r="C93" t="s">
+        <v>60</v>
+      </c>
+      <c r="D93" s="37">
+        <v>108700</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4">
+      <c r="B94" s="23"/>
+      <c r="C94" t="s">
+        <v>61</v>
+      </c>
+      <c r="D94" s="37">
+        <v>-14800</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4">
+      <c r="B95" s="23"/>
+      <c r="C95" t="s">
+        <v>62</v>
+      </c>
+      <c r="D95" s="37">
+        <v>35300</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4">
+      <c r="B96" s="23"/>
+      <c r="C96" t="s">
+        <v>63</v>
+      </c>
+      <c r="D96" s="37">
+        <v>-8900</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4">
+      <c r="B97" s="23"/>
+      <c r="C97" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" s="37">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4">
+      <c r="B98" s="23"/>
+      <c r="C98" t="s">
+        <v>53</v>
+      </c>
+      <c r="D98" s="37">
+        <v>56100</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4">
+      <c r="B99" s="23"/>
+      <c r="C99" t="s">
+        <v>65</v>
+      </c>
+      <c r="D99" s="37">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4">
+      <c r="B100" s="23"/>
+      <c r="C100" t="s">
+        <v>66</v>
+      </c>
+      <c r="D100" s="37">
+        <v>-12700</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4">
+      <c r="B101" s="23"/>
+      <c r="C101" t="s">
+        <v>67</v>
+      </c>
+      <c r="D101" s="37">
+        <v>77700</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4">
+      <c r="B102" s="23"/>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" s="37">
+        <v>-13200</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4">
+      <c r="B103" s="23"/>
+      <c r="C103" t="s">
+        <v>69</v>
+      </c>
+      <c r="D103" s="37">
+        <v>-10500</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4">
+      <c r="B104" s="23"/>
+      <c r="C104" t="s">
+        <v>46</v>
+      </c>
+      <c r="D104" s="37">
+        <v>244900</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4">
+      <c r="B105" s="23"/>
+      <c r="C105" t="s">
+        <v>48</v>
+      </c>
+      <c r="D105" s="37">
+        <v>67032</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4">
+      <c r="B106" s="23"/>
+      <c r="D106" s="37"/>
+    </row>
+    <row r="107" spans="2:4">
+      <c r="B107" s="23"/>
+      <c r="C107" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" s="37">
+        <v>712600</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4">
+      <c r="B108" s="23"/>
+      <c r="C108" t="s">
+        <v>26</v>
+      </c>
+      <c r="D108" s="37">
+        <f>SUM(D91:D105)</f>
+        <v>570132</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4">
+      <c r="B109" s="23"/>
+      <c r="C109" t="s">
+        <v>27</v>
+      </c>
+      <c r="D109" s="37">
+        <f>D107+D108</f>
+        <v>1282732</v>
+      </c>
+    </row>
+    <row r="110" ht="16.95" spans="2:4">
+      <c r="B110" s="41"/>
+      <c r="C110" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D110" s="44">
+        <f>D109-D118</f>
+        <v>1219032</v>
+      </c>
+    </row>
+    <row r="112" ht="16.95"/>
+    <row r="113" spans="2:4">
+      <c r="B113" s="18">
+        <v>2020</v>
+      </c>
+      <c r="C113" s="19"/>
+      <c r="D113" s="36"/>
+    </row>
+    <row r="114" spans="2:4">
+      <c r="B114" s="23"/>
+      <c r="C114" t="s">
+        <v>58</v>
+      </c>
+      <c r="D114" s="37">
+        <v>49400</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4">
+      <c r="B115" s="23"/>
+      <c r="C115" t="s">
+        <v>59</v>
+      </c>
+      <c r="D115" s="37">
+        <v>64300</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4">
+      <c r="B116" s="23"/>
+      <c r="C116" t="s">
+        <v>70</v>
+      </c>
+      <c r="D116" s="37">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4">
+      <c r="B117" s="23"/>
+      <c r="D117" s="37"/>
+    </row>
+    <row r="118" spans="2:4">
+      <c r="B118" s="23"/>
+      <c r="C118" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="37">
+        <v>63700</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4">
+      <c r="B119" s="23"/>
+      <c r="C119" t="s">
+        <v>26</v>
+      </c>
+      <c r="D119" s="37">
+        <f>SUM(D114:D116)</f>
+        <v>107700</v>
+      </c>
+    </row>
+    <row r="120" ht="16.95" spans="2:4">
+      <c r="B120" s="41"/>
+      <c r="C120" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D120" s="44">
+        <f>D118+D119</f>
+        <v>171400</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4">
+      <c r="D121" s="28"/>
+    </row>
+    <row r="122" spans="4:4">
+      <c r="D122" s="28"/>
+    </row>
+    <row r="123" spans="4:4">
+      <c r="D123" s="28"/>
+    </row>
+    <row r="124" spans="4:4">
+      <c r="D124" s="28"/>
+    </row>
+    <row r="125" spans="4:4">
+      <c r="D125" s="28"/>
+    </row>
+    <row r="126" spans="4:4">
+      <c r="D126" s="28"/>
+    </row>
+    <row r="127" spans="4:4">
+      <c r="D127" s="28"/>
+    </row>
+    <row r="128" spans="4:4">
+      <c r="D128" s="28"/>
+    </row>
+    <row r="129" spans="4:4">
+      <c r="D129" s="28"/>
+    </row>
+    <row r="130" spans="4:4">
+      <c r="D130" s="28"/>
+    </row>
+    <row r="131" spans="4:4">
+      <c r="D131" s="28"/>
+    </row>
+    <row r="132" spans="4:4">
+      <c r="D132" s="28"/>
+    </row>
+    <row r="133" spans="4:4">
+      <c r="D133" s="28"/>
+    </row>
+    <row r="134" spans="4:4">
+      <c r="D134" s="28"/>
+    </row>
+    <row r="135" spans="4:4">
+      <c r="D135" s="28"/>
+    </row>
+    <row r="136" spans="4:4">
+      <c r="D136" s="28"/>
+    </row>
+    <row r="137" spans="4:4">
+      <c r="D137" s="28"/>
+    </row>
+    <row r="138" spans="4:4">
+      <c r="D138" s="28"/>
+    </row>
+    <row r="139" spans="4:4">
+      <c r="D139" s="28"/>
+    </row>
+    <row r="140" spans="4:4">
+      <c r="D140" s="28"/>
+    </row>
+    <row r="141" spans="4:4">
+      <c r="D141" s="28"/>
+    </row>
+    <row r="142" spans="4:4">
+      <c r="D142" s="28"/>
+    </row>
+    <row r="143" spans="4:4">
+      <c r="D143" s="28"/>
+    </row>
+    <row r="144" spans="4:4">
+      <c r="D144" s="28"/>
+    </row>
+    <row r="145" spans="4:4">
+      <c r="D145" s="28"/>
+    </row>
+    <row r="146" spans="4:4">
+      <c r="D146" s="28"/>
+    </row>
+    <row r="147" spans="4:4">
+      <c r="D147" s="28"/>
+    </row>
+    <row r="148" spans="4:4">
+      <c r="D148" s="28"/>
+    </row>
+    <row r="149" spans="4:4">
+      <c r="D149" s="28"/>
+    </row>
+    <row r="150" spans="4:4">
+      <c r="D150" s="28"/>
+    </row>
+    <row r="151" spans="4:4">
+      <c r="D151" s="28"/>
+    </row>
+    <row r="152" spans="4:4">
+      <c r="D152" s="28"/>
+    </row>
+    <row r="153" spans="4:4">
+      <c r="D153" s="28"/>
+    </row>
+    <row r="154" spans="4:4">
+      <c r="D154" s="28"/>
+    </row>
+    <row r="155" spans="4:4">
+      <c r="D155" s="28"/>
+    </row>
+    <row r="156" spans="4:4">
+      <c r="D156" s="28"/>
+    </row>
+    <row r="157" spans="4:4">
+      <c r="D157" s="28"/>
+    </row>
+    <row r="158" spans="4:4">
+      <c r="D158" s="28"/>
+    </row>
+    <row r="159" spans="4:4">
+      <c r="D159" s="28"/>
+    </row>
+    <row r="160" spans="4:4">
+      <c r="D160" s="28"/>
+    </row>
+    <row r="161" spans="4:4">
+      <c r="D161" s="28"/>
+    </row>
+    <row r="162" spans="4:4">
+      <c r="D162" s="28"/>
+    </row>
+    <row r="163" spans="4:4">
+      <c r="D163" s="28"/>
+    </row>
+    <row r="164" spans="4:4">
+      <c r="D164" s="28"/>
+    </row>
+    <row r="165" spans="4:4">
+      <c r="D165" s="28"/>
+    </row>
+    <row r="166" spans="4:4">
+      <c r="D166" s="28"/>
+    </row>
+    <row r="167" spans="4:4">
+      <c r="D167" s="28"/>
+    </row>
+    <row r="168" spans="4:4">
+      <c r="D168" s="28"/>
+    </row>
+    <row r="169" spans="4:4">
+      <c r="D169" s="28"/>
+    </row>
+    <row r="170" spans="4:4">
+      <c r="D170" s="28"/>
+    </row>
+    <row r="171" spans="4:4">
+      <c r="D171" s="28"/>
+    </row>
+    <row r="172" spans="4:4">
+      <c r="D172" s="28"/>
+    </row>
+    <row r="173" spans="4:4">
+      <c r="D173" s="28"/>
+    </row>
+    <row r="174" spans="4:4">
+      <c r="D174" s="28"/>
+    </row>
+    <row r="175" spans="4:4">
+      <c r="D175" s="28"/>
+    </row>
+    <row r="176" spans="4:4">
+      <c r="D176" s="28"/>
+    </row>
+    <row r="177" spans="4:4">
+      <c r="D177" s="28"/>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="28"/>
+    </row>
+    <row r="179" spans="4:4">
+      <c r="D179" s="28"/>
+    </row>
+    <row r="180" spans="4:4">
+      <c r="D180" s="28"/>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" s="28"/>
+    </row>
+    <row r="182" spans="4:4">
+      <c r="D182" s="28"/>
+    </row>
+    <row r="183" spans="4:4">
+      <c r="D183" s="28"/>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" s="28"/>
+    </row>
+    <row r="185" spans="4:4">
+      <c r="D185" s="28"/>
+    </row>
+    <row r="186" spans="4:4">
+      <c r="D186" s="28"/>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" s="28"/>
+    </row>
+    <row r="188" spans="4:4">
+      <c r="D188" s="28"/>
+    </row>
+    <row r="189" spans="4:4">
+      <c r="D189" s="28"/>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" s="28"/>
+    </row>
+    <row r="191" spans="4:4">
+      <c r="D191" s="28"/>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" s="28"/>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="28"/>
+    </row>
+    <row r="194" spans="4:4">
+      <c r="D194" s="28"/>
+    </row>
+    <row r="195" spans="4:4">
+      <c r="D195" s="28"/>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="28"/>
+    </row>
+    <row r="197" spans="4:4">
+      <c r="D197" s="28"/>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" s="28"/>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" s="28"/>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" s="28"/>
+    </row>
+    <row r="201" spans="4:4">
+      <c r="D201" s="28"/>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" s="28"/>
+    </row>
+    <row r="203" spans="4:4">
+      <c r="D203" s="28"/>
+    </row>
+    <row r="204" spans="4:4">
+      <c r="D204" s="28"/>
+    </row>
+    <row r="205" spans="4:4">
+      <c r="D205" s="28"/>
+    </row>
+    <row r="206" spans="4:4">
+      <c r="D206" s="28"/>
+    </row>
+    <row r="207" spans="4:4">
+      <c r="D207" s="28"/>
+    </row>
+    <row r="208" spans="4:4">
+      <c r="D208" s="28"/>
+    </row>
+    <row r="209" spans="4:4">
+      <c r="D209" s="28"/>
+    </row>
+    <row r="210" spans="4:4">
+      <c r="D210" s="28"/>
+    </row>
+    <row r="211" spans="4:4">
+      <c r="D211" s="46"/>
+    </row>
+    <row r="212" spans="4:4">
+      <c r="D212" s="46"/>
+    </row>
+    <row r="213" spans="4:4">
+      <c r="D213" s="46"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="B1:O131"/>
@@ -3781,20 +6915,20 @@
   <sheetData>
     <row r="1" spans="4:15">
       <c r="D1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="10">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I1" s="1">
         <v>10000000</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -3803,24 +6937,24 @@
     </row>
     <row r="2" spans="4:15">
       <c r="D2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E2" s="11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I2" s="14">
         <v>0.03</v>
       </c>
       <c r="J2" s="1"/>
       <c r="K2" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L2" s="1">
         <f>F9</f>
-        <v>1868531.2</v>
+        <v>1366560</v>
       </c>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -3828,13 +6962,13 @@
     </row>
     <row r="3" spans="4:15">
       <c r="D3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E3">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" s="1">
         <f>I1*I2</f>
@@ -3842,7 +6976,7 @@
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L3" s="1">
         <v>207000</v>
@@ -3853,14 +6987,14 @@
     </row>
     <row r="4" spans="4:15">
       <c r="D4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E4" s="1">
         <f>K18</f>
-        <v>173506.24</v>
+        <v>73112</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I4" s="1">
         <f>I3/12</f>
@@ -3868,11 +7002,11 @@
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L4" s="1">
         <f>L2-L3</f>
-        <v>1661531.2</v>
+        <v>1159560</v>
       </c>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -3884,7 +7018,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L5" s="1">
         <f>I3</f>
@@ -3897,28 +7031,28 @@
     <row r="6" spans="2:15">
       <c r="B6" s="1">
         <f>C6*(1+E1)^E2</f>
-        <v>95180.8</v>
+        <v>95040</v>
       </c>
       <c r="C6" s="1">
-        <v>88000</v>
+        <v>95040</v>
       </c>
       <c r="D6" s="1">
         <v>14</v>
       </c>
       <c r="E6" s="1">
         <f>C6*D6</f>
-        <v>1232000</v>
+        <v>1330560</v>
       </c>
       <c r="F6" s="1">
         <f>E6*(1+E1)^E2</f>
-        <v>1332531.2</v>
+        <v>1330560</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" s="1">
         <v>270000</v>
@@ -3947,7 +7081,7 @@
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -3959,22 +7093,22 @@
     <row r="8" spans="3:15">
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="1">
         <f>$E$3</f>
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1">
         <f>$E$3</f>
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L8" s="1">
         <v>124000</v>
@@ -3986,33 +7120,33 @@
     <row r="9" spans="2:15">
       <c r="B9" s="1">
         <f>E9/12</f>
-        <v>147333.333333333</v>
+        <v>113880</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E9" s="1">
         <f>SUM(E6:E8)</f>
-        <v>1768000</v>
+        <v>1366560</v>
       </c>
       <c r="F9" s="1">
         <f>SUM(F6:F8)</f>
-        <v>1868531.2</v>
+        <v>1366560</v>
       </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1">
         <f>F9/12</f>
-        <v>155710.933333333</v>
+        <v>113880</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L9" s="1">
         <f>(L4+MAX(0,L5-L6))-L8</f>
-        <v>1567531.2</v>
+        <v>1065560</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
@@ -4021,31 +7155,31 @@
     <row r="10" spans="2:15">
       <c r="B10" s="1">
         <f>E10/12</f>
-        <v>172333.333333333</v>
+        <v>138880</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1">
         <f>E9+$I$3</f>
-        <v>2068000</v>
+        <v>1666560</v>
       </c>
       <c r="F10" s="1">
         <f>F9+$I$3</f>
-        <v>2168531.2</v>
+        <v>1666560</v>
       </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1">
         <f>F10/12</f>
-        <v>180710.933333333</v>
+        <v>138880</v>
       </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -4053,25 +7187,25 @@
     <row r="11" spans="3:15">
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="1">
         <f>E10-$E$4</f>
-        <v>1894493.76</v>
+        <v>1593448</v>
       </c>
       <c r="F11" s="1">
         <f>F10-$E$4</f>
-        <v>1995024.96</v>
+        <v>1593448</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -4079,22 +7213,22 @@
     <row r="12" spans="3:15">
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1">
         <f>E11/12</f>
-        <v>157874.48</v>
+        <v>132787.333333333</v>
       </c>
       <c r="F12" s="1">
         <f>F11/12</f>
-        <v>166252.08</v>
+        <v>132787.333333333</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L12" s="12">
         <v>0.05</v>
@@ -4118,7 +7252,7 @@
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L13" s="12">
         <v>0.12</v>
@@ -4132,7 +7266,7 @@
     <row r="14" spans="2:15">
       <c r="B14" s="10">
         <f>B13/E12</f>
-        <v>0.50673167696261</v>
+        <v>0.602467102785908</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -4143,7 +7277,7 @@
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L14" s="12">
         <v>0.2</v>
@@ -4164,7 +7298,7 @@
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L15" s="12">
         <v>0.3</v>
@@ -4185,7 +7319,7 @@
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L16" s="12">
         <v>0.4</v>
@@ -4218,7 +7352,7 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1">
         <f>L9*L14-M14</f>
-        <v>173506.24</v>
+        <v>73112</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -4243,7 +7377,7 @@
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J20" s="1">
         <v>3500000</v>
@@ -4259,7 +7393,7 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J21" s="1">
         <f>IF(J20&lt;560000,J20-J20*L12,IF(J20&lt;1260000,J20-(J20*L13-M13),IF(J20&lt;2520000,J20-(J20*L14-M14),IF(J20&lt;4720000,J20-(J20*L15-M15),J20-(J20*L16-M16)))))</f>
@@ -5602,7 +8736,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="B2:O187"/>
@@ -5615,9 +8749,9 @@
     <col min="6" max="6" width="10.4444444444444" style="1"/>
     <col min="7" max="8" width="8.88888888888889" style="1"/>
     <col min="9" max="9" width="23.1111111111111" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5555555555556" style="1"/>
-    <col min="11" max="12" width="8.88888888888889" style="1"/>
-    <col min="13" max="13" width="8.88888888888889" style="4"/>
+    <col min="10" max="11" width="11.5555555555556" style="1"/>
+    <col min="12" max="12" width="8.88888888888889" style="1"/>
+    <col min="13" max="13" width="9.66666666666667" style="4"/>
     <col min="14" max="14" width="9.44444444444444" style="1"/>
     <col min="15" max="15" width="8.88888888888889" style="1"/>
   </cols>
@@ -5646,10 +8780,10 @@
         <v>0.14005196969697</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J3" s="1">
-        <v>21470696</v>
+        <v>31961392</v>
       </c>
     </row>
     <row r="4" spans="2:10">
@@ -5668,7 +8802,7 @@
         <v>0.0599474266391099</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J4" s="1">
         <v>-7860000</v>
@@ -5690,13 +8824,13 @@
         <v>-0.0388919287890977</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J5" s="1">
         <v>5790000</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="2:10">
@@ -5718,7 +8852,7 @@
         <v>5</v>
       </c>
       <c r="J6" s="1">
-        <v>-1389043</v>
+        <v>-1342643</v>
       </c>
     </row>
     <row r="7" ht="16.95" spans="2:14">
@@ -5737,15 +8871,15 @@
         <v>0.0852958051483765</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J7" s="1">
-        <v>61132</v>
+        <v>54842</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9">
         <f>SUM(N8:N99)</f>
-        <v>61710</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -5764,20 +8898,14 @@
         <v>-0.0471663352257339</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J8" s="1">
         <f>N7</f>
-        <v>61710</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M8" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="N8" s="1">
-        <v>61710</v>
       </c>
       <c r="O8" s="4"/>
     </row>
@@ -5796,13 +8924,14 @@
         <f t="shared" si="1"/>
         <v>-0.0242376362491937</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="9" t="s">
         <v>108</v>
       </c>
+      <c r="J9" s="9"/>
       <c r="L9" s="4"/>
       <c r="O9" s="4"/>
     </row>
-    <row r="10" ht="16.95" spans="2:10">
+    <row r="10" spans="2:11">
       <c r="B10" s="3">
         <v>45565</v>
       </c>
@@ -5817,17 +8946,21 @@
         <f t="shared" si="1"/>
         <v>0.0264542637625841</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="9">
-        <f>股票損益!R12</f>
-        <v>313000</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
+      <c r="J10" s="1">
+        <f>SUM(J3:J9)</f>
+        <v>28603591</v>
+      </c>
+      <c r="K10" s="1">
+        <f>J10-J5</f>
+        <v>22813591</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
       <c r="B11" s="3">
-        <v>45597</v>
+        <v>45596</v>
       </c>
       <c r="C11" s="1">
         <v>8017685</v>
@@ -5840,13 +8973,6 @@
         <f t="shared" si="1"/>
         <v>0.0226648161548103</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J11" s="1">
-        <f>SUM(J3:J10)</f>
-        <v>18447495</v>
-      </c>
     </row>
     <row r="12" spans="2:5">
       <c r="B12" s="3">
@@ -5864,7 +8990,7 @@
         <v>0.0104930537929589</v>
       </c>
     </row>
-    <row r="13" spans="2:5">
+    <row r="13" spans="2:9">
       <c r="B13" s="3">
         <v>45657</v>
       </c>
@@ -5879,6 +9005,7 @@
         <f t="shared" si="1"/>
         <v>0.0499362179955973</v>
       </c>
+      <c r="I13"/>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="3">
@@ -5897,7 +9024,7 @@
       </c>
       <c r="I14"/>
     </row>
-    <row r="15" spans="2:9">
+    <row r="15" spans="2:5">
       <c r="B15" s="3">
         <v>45747</v>
       </c>
@@ -5912,7 +9039,6 @@
         <f t="shared" si="1"/>
         <v>-0.150456622797108</v>
       </c>
-      <c r="I15"/>
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="3">
@@ -6126,26 +9252,33 @@
       <c r="B29" s="3">
         <v>46142</v>
       </c>
-      <c r="D29" s="1" t="str">
+      <c r="C29" s="1">
+        <v>25704540</v>
+      </c>
+      <c r="D29" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E29" s="6" t="str">
+        <v>7257045</v>
+      </c>
+      <c r="E29" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.393389183734702</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="3">
         <v>46173</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="C30" s="1">
+        <f>J10</f>
+        <v>28603591</v>
+      </c>
+      <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E30" s="6" t="str">
+        <v>2899051</v>
+      </c>
+      <c r="E30" s="6">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.112783617213146</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -7742,11 +10875,12 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="C1:G19"/>
@@ -7758,10 +10892,10 @@
   <sheetData>
     <row r="1" spans="4:5">
       <c r="D1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" t="s">
         <v>111</v>
-      </c>
-      <c r="E1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="3:4">

--- a/股票損益&房貸試算收入試算.xlsx
+++ b/股票損益&房貸試算收入試算.xlsx
@@ -4,14 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22391" windowHeight="10067" activeTab="3"/>
+    <workbookView windowWidth="22391" windowHeight="10067" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="股票損益" sheetId="1" r:id="rId1"/>
-    <sheet name="股票損益 (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="房貸收入試算" sheetId="3" r:id="rId3"/>
-    <sheet name="淨值表" sheetId="4" r:id="rId4"/>
-    <sheet name="東哥券差借券紀錄" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet name="房貸收入試算" sheetId="2" r:id="rId2"/>
+    <sheet name="淨值表" sheetId="3" r:id="rId3"/>
+    <sheet name="東哥券差借券紀錄" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -88,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123">
   <si>
     <t>股利+借券</t>
   </si>
@@ -396,28 +395,61 @@
     <t>總台新資產</t>
   </si>
   <si>
+    <t>元大正2</t>
+  </si>
+  <si>
     <t>扣除爸媽的錢</t>
   </si>
   <si>
+    <t>但有200萬是贈與的</t>
+  </si>
+  <si>
+    <t>群益正2</t>
+  </si>
+  <si>
     <t>補加上房貸已繳的錢</t>
   </si>
   <si>
     <t>第11期工程款</t>
   </si>
   <si>
+    <t>總共</t>
+  </si>
+  <si>
     <t>LINE</t>
   </si>
   <si>
+    <t>正二*2</t>
+  </si>
+  <si>
     <t>現金股利</t>
   </si>
   <si>
     <t>股利</t>
   </si>
   <si>
+    <t>稅6/11</t>
+  </si>
+  <si>
     <t>股票尚未交割金額</t>
   </si>
   <si>
+    <t>台股目前</t>
+  </si>
+  <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>如果漲到多少</t>
+  </si>
+  <si>
+    <t>漲幅</t>
+  </si>
+  <si>
+    <t>將會賺</t>
+  </si>
+  <si>
+    <t>到時財富</t>
   </si>
   <si>
     <t>轉出</t>
@@ -435,14 +467,14 @@
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="178" formatCode="#,##0_ ;[Red]\-#,##0\ "/>
-    <numFmt numFmtId="179" formatCode="m/d;@"/>
-    <numFmt numFmtId="180" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="181" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="180" formatCode="m/d;@"/>
+    <numFmt numFmtId="181" formatCode="0.0%"/>
     <numFmt numFmtId="182" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    <numFmt numFmtId="183" formatCode="0.0%"/>
+    <numFmt numFmtId="183" formatCode="0.00_ "/>
     <numFmt numFmtId="184" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
@@ -474,8 +506,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -522,22 +555,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -560,22 +585,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="新細明體"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -596,16 +606,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="新細明體"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="新細明體"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -639,13 +671,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -657,7 +743,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -669,49 +779,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -729,19 +803,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -753,73 +845,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,6 +956,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -959,17 +1006,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -979,15 +1020,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1026,10 +1058,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1038,13 +1070,13 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1053,125 +1085,125 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1184,37 +1216,43 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="4" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1244,28 +1282,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
@@ -1277,7 +1315,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1">
@@ -1286,22 +1324,19 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="9" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
@@ -1310,7 +1345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1604,7 +1639,7 @@
                   <c:v>25704540</c:v>
                 </c:pt>
                 <c:pt idx="28" c:formatCode="#,##0_ ;[Red]\-#,##0\ ">
-                  <c:v>28603591</c:v>
+                  <c:v>29860592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1678,7 +1713,7 @@
         <c:axId val="533450541"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="29000000"/>
+          <c:max val="31000000"/>
           <c:min val="6000000"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -2634,18 +2669,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17">
+      <c r="A1" s="19">
         <f>D32+D50+D70+D87+D110+D120</f>
         <v>8235533</v>
       </c>
-      <c r="C1" s="17"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="17">
+      <c r="A2" s="19">
         <f>A1+M8</f>
-        <v>20114060</v>
-      </c>
-      <c r="C2" s="17"/>
+        <v>21566919</v>
+      </c>
+      <c r="C2" s="19"/>
       <c r="O2" s="1">
         <f>O6*R6</f>
         <v>600000</v>
@@ -2656,7 +2691,7 @@
       </c>
     </row>
     <row r="3" ht="16.95" spans="3:16">
-      <c r="C3" s="17"/>
+      <c r="C3" s="19"/>
       <c r="O3" s="1">
         <f>(O6+P6)*R6-P6*T6</f>
         <v>640000</v>
@@ -2667,35 +2702,35 @@
       </c>
     </row>
     <row r="4" ht="16.95" spans="2:10">
-      <c r="B4" s="18">
+      <c r="B4" s="20">
         <v>2026</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20">
+      <c r="C4" s="21"/>
+      <c r="D4" s="22">
         <f>SUM($D5:$D10)</f>
-        <v>8538149</v>
-      </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="22" t="s">
+        <v>9188910</v>
+      </c>
+      <c r="E4" s="23"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20">
+      <c r="H4" s="21"/>
+      <c r="I4" s="22">
         <f>SUM($I5:$I18)</f>
         <v>117104</v>
       </c>
-      <c r="J4" s="36"/>
+      <c r="J4" s="38"/>
     </row>
     <row r="5" spans="2:22">
-      <c r="B5" s="23"/>
+      <c r="B5" s="25"/>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="1">
         <v>1273965</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="26">
         <v>45665</v>
       </c>
       <c r="H5" t="s">
@@ -2704,12 +2739,12 @@
       <c r="I5" s="1">
         <v>48000</v>
       </c>
-      <c r="J5" s="37"/>
+      <c r="J5" s="39"/>
       <c r="L5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="M5" s="1">
-        <v>8655253</v>
+        <v>9306014</v>
       </c>
       <c r="O5" s="1" t="s">
         <v>4</v>
@@ -2737,7 +2772,7 @@
       </c>
     </row>
     <row r="6" spans="2:22">
-      <c r="B6" s="23"/>
+      <c r="B6" s="25"/>
       <c r="C6" t="s">
         <v>12</v>
       </c>
@@ -2753,12 +2788,12 @@
       <c r="I6" s="1">
         <v>6650</v>
       </c>
-      <c r="J6" s="37"/>
+      <c r="J6" s="39"/>
       <c r="L6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="M6" s="1">
-        <v>8457384</v>
+        <v>9259482</v>
       </c>
       <c r="N6" s="1">
         <f>Q12</f>
@@ -2774,14 +2809,14 @@
         <f>(O6+P6)*1.6</f>
         <v>22400000</v>
       </c>
-      <c r="R6" s="38">
+      <c r="R6" s="40">
         <v>0.05</v>
       </c>
       <c r="S6" s="1">
         <f>Q6*R6</f>
         <v>1120000</v>
       </c>
-      <c r="T6" s="38">
+      <c r="T6" s="40">
         <v>0.03</v>
       </c>
       <c r="U6" s="1">
@@ -2794,14 +2829,14 @@
       </c>
     </row>
     <row r="7" ht="16.95" spans="2:23">
-      <c r="B7" s="23"/>
+      <c r="B7" s="25"/>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>7337504</v>
-      </c>
-      <c r="E7" s="13"/>
+        <v>7988265</v>
+      </c>
+      <c r="E7" s="15"/>
       <c r="G7" s="4">
         <v>46121</v>
       </c>
@@ -2811,19 +2846,19 @@
       <c r="I7" s="1">
         <v>61710</v>
       </c>
-      <c r="J7" s="37"/>
-      <c r="L7" s="26" t="s">
+      <c r="J7" s="39"/>
+      <c r="L7" s="29" t="s">
         <v>15</v>
       </c>
       <c r="M7" s="9">
         <v>5234110</v>
       </c>
-      <c r="R7" s="38"/>
+      <c r="R7" s="40"/>
       <c r="S7" s="1">
         <f t="shared" ref="S7:V7" si="0">S6/12</f>
         <v>93333.3333333333</v>
       </c>
-      <c r="T7" s="38"/>
+      <c r="T7" s="40"/>
       <c r="U7" s="1">
         <f t="shared" si="0"/>
         <v>26000</v>
@@ -2837,8 +2872,8 @@
       </c>
     </row>
     <row r="8" spans="2:22">
-      <c r="B8" s="23"/>
-      <c r="E8" s="13"/>
+      <c r="B8" s="25"/>
+      <c r="E8" s="15"/>
       <c r="G8" s="4">
         <v>46142</v>
       </c>
@@ -2848,11 +2883,11 @@
       <c r="I8" s="1">
         <v>744</v>
       </c>
-      <c r="J8" s="37"/>
+      <c r="J8" s="39"/>
       <c r="L8"/>
       <c r="M8" s="1">
         <f>M5+M6-M7+N6</f>
-        <v>11878527</v>
+        <v>13331386</v>
       </c>
       <c r="Q8" s="1" t="s">
         <v>18</v>
@@ -2862,11 +2897,11 @@
       <c r="V8" s="1"/>
     </row>
     <row r="9" spans="2:22">
-      <c r="B9" s="23"/>
-      <c r="E9" s="13"/>
+      <c r="B9" s="25"/>
+      <c r="E9" s="15"/>
       <c r="G9" s="4"/>
       <c r="I9" s="1"/>
-      <c r="J9" s="37"/>
+      <c r="J9" s="39"/>
       <c r="Q9" s="1">
         <f>(O6+P6)*1.96</f>
         <v>27440000</v>
@@ -2886,11 +2921,11 @@
       </c>
     </row>
     <row r="10" spans="2:22">
-      <c r="B10" s="23"/>
-      <c r="E10" s="13"/>
+      <c r="B10" s="25"/>
+      <c r="E10" s="15"/>
       <c r="G10" s="4"/>
       <c r="I10" s="1"/>
-      <c r="J10" s="37"/>
+      <c r="J10" s="39"/>
       <c r="L10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2909,11 +2944,11 @@
       </c>
     </row>
     <row r="11" spans="2:22">
-      <c r="B11" s="23"/>
-      <c r="E11" s="13"/>
+      <c r="B11" s="25"/>
+      <c r="E11" s="15"/>
       <c r="G11" s="4"/>
       <c r="I11" s="1"/>
-      <c r="J11" s="37"/>
+      <c r="J11" s="39"/>
       <c r="M11" s="1" t="s">
         <v>20</v>
       </c>
@@ -2934,20 +2969,20 @@
       <c r="V11" s="1"/>
     </row>
     <row r="12" spans="2:22">
-      <c r="B12" s="23"/>
+      <c r="B12" s="25"/>
       <c r="G12" s="4"/>
       <c r="I12" s="1"/>
-      <c r="J12" s="37"/>
+      <c r="J12" s="39"/>
       <c r="L12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="M12" s="1">
         <v>0</v>
       </c>
-      <c r="N12" s="13">
+      <c r="N12" s="15">
         <v>179.5</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="15">
         <v>160</v>
       </c>
       <c r="P12" s="1">
@@ -2961,64 +2996,66 @@
         <f>O12*M12*1000</f>
         <v>0</v>
       </c>
-      <c r="S12" s="40"/>
+      <c r="S12" s="11"/>
       <c r="T12" s="1"/>
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
     <row r="13" spans="2:22">
-      <c r="B13" s="23"/>
+      <c r="B13" s="25"/>
       <c r="C13" t="s">
         <v>24</v>
       </c>
+      <c r="D13" s="1">
+        <f>M6</f>
+        <v>9259482</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="I13" s="1"/>
-      <c r="J13" s="37"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="38">
+      <c r="J13" s="39"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="40">
         <f>(O12-N12)/N12</f>
         <v>-0.108635097493036</v>
       </c>
       <c r="P13"/>
       <c r="Q13"/>
-      <c r="R13" s="7">
-        <v>22315376</v>
-      </c>
+      <c r="R13" s="7"/>
       <c r="S13"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
     <row r="14" spans="2:22">
-      <c r="B14" s="23"/>
+      <c r="B14" s="25"/>
       <c r="C14" t="s">
         <v>26</v>
       </c>
+      <c r="D14" s="1">
+        <f>D4+I4</f>
+        <v>9306014</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="I14" s="1"/>
-      <c r="J14" s="37"/>
+      <c r="J14" s="39"/>
       <c r="Q14"/>
-      <c r="R14" s="1">
-        <f>SUM(R11:R13)</f>
-        <v>22315376</v>
-      </c>
       <c r="S14"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="23"/>
+      <c r="B15" s="25"/>
       <c r="C15" t="s">
         <v>27</v>
       </c>
       <c r="D15" s="1">
         <f>D13+D14</f>
-        <v>0</v>
+        <v>18565496</v>
       </c>
       <c r="G15" s="4"/>
       <c r="I15" s="1"/>
-      <c r="J15" s="37"/>
+      <c r="J15" s="39"/>
       <c r="Q15"/>
       <c r="S15"/>
       <c r="T15" s="1"/>
@@ -3026,70 +3063,70 @@
       <c r="V15" s="1"/>
     </row>
     <row r="16" spans="2:10">
-      <c r="B16" s="23"/>
+      <c r="B16" s="25"/>
       <c r="C16" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="27">
         <f>D15-D29</f>
-        <v>-5234110</v>
+        <v>13331386</v>
       </c>
       <c r="G16" s="4"/>
       <c r="I16" s="1"/>
-      <c r="J16" s="37"/>
+      <c r="J16" s="39"/>
     </row>
     <row r="17" spans="2:10">
-      <c r="B17" s="23"/>
+      <c r="B17" s="25"/>
       <c r="G17" s="4"/>
       <c r="I17" s="1"/>
-      <c r="J17" s="37"/>
+      <c r="J17" s="39"/>
     </row>
     <row r="18" ht="16.95" spans="2:10">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="26"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="29"/>
       <c r="I18" s="9"/>
-      <c r="J18" s="39"/>
+      <c r="J18" s="41"/>
     </row>
     <row r="19" spans="3:3">
-      <c r="C19" s="17"/>
+      <c r="C19" s="19"/>
     </row>
     <row r="20" ht="16.95" spans="3:3">
-      <c r="C20" s="17"/>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="16.95" spans="2:15">
-      <c r="B21" s="18">
+      <c r="B21" s="20">
         <v>2025</v>
       </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22" t="s">
+      <c r="C21" s="21"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="20">
+      <c r="H21" s="21"/>
+      <c r="I21" s="22">
         <f>SUM($I22:$I36)</f>
         <v>490723</v>
       </c>
-      <c r="J21" s="36"/>
+      <c r="J21" s="38"/>
       <c r="N21" s="4"/>
       <c r="O21"/>
     </row>
     <row r="22" spans="2:15">
-      <c r="B22" s="23"/>
+      <c r="B22" s="25"/>
       <c r="C22" t="s">
         <v>29</v>
       </c>
       <c r="D22" s="1">
         <v>-139300</v>
       </c>
-      <c r="G22" s="24">
+      <c r="G22" s="26">
         <v>45666</v>
       </c>
       <c r="H22" t="s">
@@ -3098,12 +3135,12 @@
       <c r="I22" s="1">
         <v>12000</v>
       </c>
-      <c r="J22" s="37"/>
+      <c r="J22" s="39"/>
       <c r="N22" s="4"/>
       <c r="O22"/>
     </row>
     <row r="23" spans="2:15">
-      <c r="B23" s="23"/>
+      <c r="B23" s="25"/>
       <c r="C23" t="s">
         <v>30</v>
       </c>
@@ -3119,12 +3156,12 @@
       <c r="I23" s="1">
         <v>201960</v>
       </c>
-      <c r="J23" s="37"/>
+      <c r="J23" s="39"/>
       <c r="N23" s="4"/>
       <c r="O23"/>
     </row>
     <row r="24" spans="2:15">
-      <c r="B24" s="23"/>
+      <c r="B24" s="25"/>
       <c r="C24" t="s">
         <v>32</v>
       </c>
@@ -3140,12 +3177,12 @@
       <c r="I24" s="1">
         <v>17325</v>
       </c>
-      <c r="J24" s="37"/>
+      <c r="J24" s="39"/>
       <c r="N24" s="4"/>
       <c r="O24"/>
     </row>
     <row r="25" spans="2:15">
-      <c r="B25" s="23"/>
+      <c r="B25" s="25"/>
       <c r="C25" t="s">
         <v>34</v>
       </c>
@@ -3161,11 +3198,11 @@
       <c r="I25" s="1">
         <v>360</v>
       </c>
-      <c r="J25" s="37"/>
-      <c r="O25" s="13"/>
+      <c r="J25" s="39"/>
+      <c r="O25" s="15"/>
     </row>
     <row r="26" spans="2:29">
-      <c r="B26" s="23"/>
+      <c r="B26" s="25"/>
       <c r="C26" t="s">
         <v>36</v>
       </c>
@@ -3181,15 +3218,15 @@
       <c r="I26" s="1">
         <v>2078</v>
       </c>
-      <c r="J26" s="37"/>
-      <c r="O26" s="13"/>
+      <c r="J26" s="39"/>
+      <c r="O26" s="15"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
     </row>
     <row r="27" spans="2:29">
-      <c r="B27" s="23"/>
+      <c r="B27" s="25"/>
       <c r="C27" t="s">
         <v>37</v>
       </c>
@@ -3205,15 +3242,15 @@
       <c r="I27" s="1">
         <v>20250</v>
       </c>
-      <c r="J27" s="37"/>
+      <c r="J27" s="39"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
     </row>
     <row r="28" spans="2:29">
-      <c r="B28" s="23"/>
-      <c r="D28" s="28"/>
+      <c r="B28" s="25"/>
+      <c r="D28" s="31"/>
       <c r="G28" s="4">
         <v>45763</v>
       </c>
@@ -3223,14 +3260,14 @@
       <c r="I28" s="1">
         <v>175500</v>
       </c>
-      <c r="J28" s="37"/>
+      <c r="J28" s="39"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
     </row>
     <row r="29" spans="2:29">
-      <c r="B29" s="23"/>
+      <c r="B29" s="25"/>
       <c r="C29" t="s">
         <v>24</v>
       </c>
@@ -3246,14 +3283,14 @@
       <c r="I29" s="1">
         <v>20250</v>
       </c>
-      <c r="J29" s="37"/>
+      <c r="J29" s="39"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
     </row>
     <row r="30" spans="2:29">
-      <c r="B30" s="23"/>
+      <c r="B30" s="25"/>
       <c r="C30" t="s">
         <v>26</v>
       </c>
@@ -3270,14 +3307,14 @@
       <c r="I30" s="1">
         <v>41000</v>
       </c>
-      <c r="J30" s="37"/>
+      <c r="J30" s="39"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
     </row>
     <row r="31" spans="2:29">
-      <c r="B31" s="23"/>
+      <c r="B31" s="25"/>
       <c r="C31" t="s">
         <v>27</v>
       </c>
@@ -3287,24 +3324,24 @@
       </c>
       <c r="G31" s="4"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="37"/>
+      <c r="J31" s="39"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
     </row>
     <row r="32" spans="2:29">
-      <c r="B32" s="23"/>
+      <c r="B32" s="25"/>
       <c r="C32" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="27">
         <f>D31-D47</f>
         <v>4458133</v>
       </c>
       <c r="G32" s="4"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="37"/>
+      <c r="J32" s="39"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
@@ -3314,10 +3351,10 @@
       <c r="AC32" s="1"/>
     </row>
     <row r="33" spans="2:29">
-      <c r="B33" s="23"/>
+      <c r="B33" s="25"/>
       <c r="G33" s="4"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="37"/>
+      <c r="J33" s="39"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
@@ -3327,13 +3364,13 @@
       <c r="AC33" s="1"/>
     </row>
     <row r="34" spans="2:29">
-      <c r="B34" s="23"/>
+      <c r="B34" s="25"/>
       <c r="C34" t="s">
         <v>38</v>
       </c>
       <c r="G34" s="4"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="37"/>
+      <c r="J34" s="39"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
@@ -3343,13 +3380,13 @@
       <c r="AC34" s="1"/>
     </row>
     <row r="35" spans="2:29">
-      <c r="B35" s="23"/>
+      <c r="B35" s="25"/>
       <c r="C35" t="s">
         <v>39</v>
       </c>
       <c r="G35" s="4"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="37"/>
+      <c r="J35" s="39"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
@@ -3359,15 +3396,15 @@
       <c r="AC35" s="1"/>
     </row>
     <row r="36" ht="16.95" spans="2:29">
-      <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="26"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="29"/>
       <c r="I36" s="9"/>
-      <c r="J36" s="39"/>
+      <c r="J36" s="41"/>
       <c r="W36" s="1"/>
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
@@ -3401,22 +3438,22 @@
       <c r="AC38" s="1"/>
     </row>
     <row r="39" ht="16.95" spans="2:29">
-      <c r="B39" s="18">
+      <c r="B39" s="20">
         <v>2024</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="22" t="s">
+      <c r="C39" s="21"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20">
+      <c r="H39" s="21"/>
+      <c r="I39" s="22">
         <f>SUM(I$40:I$56)</f>
         <v>307025</v>
       </c>
-      <c r="J39" s="36"/>
+      <c r="J39" s="38"/>
       <c r="T39" s="1"/>
       <c r="U39" s="1"/>
       <c r="V39" s="1"/>
@@ -3429,7 +3466,7 @@
       <c r="AC39" s="1"/>
     </row>
     <row r="40" spans="2:29">
-      <c r="B40" s="23"/>
+      <c r="B40" s="25"/>
       <c r="C40" t="s">
         <v>40</v>
       </c>
@@ -3445,7 +3482,7 @@
       <c r="I40" s="1">
         <v>6210</v>
       </c>
-      <c r="J40" s="37"/>
+      <c r="J40" s="39"/>
       <c r="T40" s="1"/>
       <c r="U40" s="1"/>
       <c r="V40" s="1"/>
@@ -3458,7 +3495,7 @@
       <c r="AC40" s="1"/>
     </row>
     <row r="41" spans="2:29">
-      <c r="B41" s="23"/>
+      <c r="B41" s="25"/>
       <c r="C41" t="s">
         <v>42</v>
       </c>
@@ -3474,7 +3511,7 @@
       <c r="I41" s="1">
         <v>12080</v>
       </c>
-      <c r="J41" s="37"/>
+      <c r="J41" s="39"/>
       <c r="T41" s="1"/>
       <c r="U41" s="1"/>
       <c r="V41" s="1"/>
@@ -3487,7 +3524,7 @@
       <c r="AC41" s="1"/>
     </row>
     <row r="42" spans="2:29">
-      <c r="B42" s="23"/>
+      <c r="B42" s="25"/>
       <c r="C42" t="s">
         <v>41</v>
       </c>
@@ -3503,7 +3540,7 @@
       <c r="I42" s="1">
         <v>3900</v>
       </c>
-      <c r="J42" s="37"/>
+      <c r="J42" s="39"/>
       <c r="T42" s="1"/>
       <c r="U42" s="1"/>
       <c r="V42" s="1"/>
@@ -3516,7 +3553,7 @@
       <c r="AC42" s="1"/>
     </row>
     <row r="43" spans="2:29">
-      <c r="B43" s="23"/>
+      <c r="B43" s="25"/>
       <c r="C43" t="s">
         <v>43</v>
       </c>
@@ -3532,7 +3569,7 @@
       <c r="I43" s="1">
         <v>7000</v>
       </c>
-      <c r="J43" s="37"/>
+      <c r="J43" s="39"/>
       <c r="T43" s="1"/>
       <c r="U43" s="1"/>
       <c r="V43" s="1"/>
@@ -3545,7 +3582,7 @@
       <c r="AC43" s="1"/>
     </row>
     <row r="44" spans="2:29">
-      <c r="B44" s="23"/>
+      <c r="B44" s="25"/>
       <c r="C44" t="s">
         <v>30</v>
       </c>
@@ -3561,7 +3598,7 @@
       <c r="I44" s="1">
         <v>155000</v>
       </c>
-      <c r="J44" s="37"/>
+      <c r="J44" s="39"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -3574,14 +3611,14 @@
       <c r="AC44" s="1"/>
     </row>
     <row r="45" spans="2:10">
-      <c r="B45" s="23"/>
+      <c r="B45" s="25"/>
       <c r="C45" t="s">
         <v>29</v>
       </c>
       <c r="D45" s="1">
         <v>-74000</v>
       </c>
-      <c r="E45" s="13"/>
+      <c r="E45" s="15"/>
       <c r="G45" s="4">
         <v>45470</v>
       </c>
@@ -3591,10 +3628,10 @@
       <c r="I45" s="1">
         <v>3879</v>
       </c>
-      <c r="J45" s="37"/>
+      <c r="J45" s="39"/>
     </row>
     <row r="46" spans="2:10">
-      <c r="B46" s="23"/>
+      <c r="B46" s="25"/>
       <c r="G46" s="4">
         <v>45484</v>
       </c>
@@ -3604,10 +3641,10 @@
       <c r="I46" s="1">
         <v>7000</v>
       </c>
-      <c r="J46" s="37"/>
+      <c r="J46" s="39"/>
     </row>
     <row r="47" spans="2:10">
-      <c r="B47" s="23"/>
+      <c r="B47" s="25"/>
       <c r="C47" t="s">
         <v>24</v>
       </c>
@@ -3623,10 +3660,10 @@
       <c r="I47" s="1">
         <v>13902</v>
       </c>
-      <c r="J47" s="37"/>
+      <c r="J47" s="39"/>
     </row>
     <row r="48" spans="2:10">
-      <c r="B48" s="23"/>
+      <c r="B48" s="25"/>
       <c r="C48" t="s">
         <v>26</v>
       </c>
@@ -3643,10 +3680,10 @@
       <c r="I48" s="1">
         <v>81600</v>
       </c>
-      <c r="J48" s="37"/>
+      <c r="J48" s="39"/>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="23"/>
+      <c r="B49" s="25"/>
       <c r="C49" t="s">
         <v>27</v>
       </c>
@@ -3663,14 +3700,14 @@
       <c r="I49" s="1">
         <v>783</v>
       </c>
-      <c r="J49" s="37"/>
+      <c r="J49" s="39"/>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="23"/>
+      <c r="B50" s="25"/>
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="29">
+      <c r="D50" s="27">
         <f>D49-D67</f>
         <v>1455625</v>
       </c>
@@ -3683,10 +3720,10 @@
       <c r="I50" s="1">
         <v>1161</v>
       </c>
-      <c r="J50" s="37"/>
+      <c r="J50" s="39"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="23"/>
+      <c r="B51" s="25"/>
       <c r="G51" s="4">
         <v>45525</v>
       </c>
@@ -3696,10 +3733,10 @@
       <c r="I51" s="1">
         <v>1237</v>
       </c>
-      <c r="J51" s="37"/>
+      <c r="J51" s="39"/>
     </row>
     <row r="52" spans="2:10">
-      <c r="B52" s="23"/>
+      <c r="B52" s="25"/>
       <c r="C52" t="s">
         <v>38</v>
       </c>
@@ -3712,10 +3749,10 @@
       <c r="I52" s="1">
         <v>12000</v>
       </c>
-      <c r="J52" s="37"/>
+      <c r="J52" s="39"/>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="30"/>
+      <c r="B53" s="32"/>
       <c r="C53" t="s">
         <v>39</v>
       </c>
@@ -3728,28 +3765,28 @@
       <c r="I53" s="1">
         <v>1273</v>
       </c>
-      <c r="J53" s="37"/>
+      <c r="J53" s="39"/>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="30"/>
-      <c r="J54" s="37"/>
+      <c r="B54" s="32"/>
+      <c r="J54" s="39"/>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="30"/>
-      <c r="G55" s="31"/>
+      <c r="B55" s="32"/>
+      <c r="G55" s="33"/>
       <c r="I55" s="1"/>
-      <c r="J55" s="37"/>
+      <c r="J55" s="39"/>
     </row>
     <row r="56" ht="16.95" spans="2:10">
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="26"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="29"/>
       <c r="I56" s="9"/>
-      <c r="J56" s="39"/>
+      <c r="J56" s="41"/>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" s="4"/>
@@ -3758,991 +3795,991 @@
       <c r="B58" s="4"/>
     </row>
     <row r="59" ht="16.95" spans="2:10">
-      <c r="B59" s="18">
+      <c r="B59" s="20">
         <v>2023</v>
       </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="22" t="s">
+      <c r="C59" s="21"/>
+      <c r="D59" s="23"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="H59" s="19"/>
-      <c r="I59" s="20">
+      <c r="H59" s="21"/>
+      <c r="I59" s="22">
         <f>SUM(I60:I66)</f>
         <v>103800</v>
       </c>
-      <c r="J59" s="36"/>
+      <c r="J59" s="38"/>
     </row>
     <row r="60" spans="2:10">
-      <c r="B60" s="23"/>
-      <c r="C60" s="32" t="s">
+      <c r="B60" s="25"/>
+      <c r="C60" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="35">
         <v>346100</v>
       </c>
-      <c r="E60" s="34"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="35">
+      <c r="E60" s="36"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="37">
         <v>45135</v>
       </c>
-      <c r="H60" s="32" t="s">
+      <c r="H60" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="I60" s="34">
+      <c r="I60" s="36">
         <v>4750</v>
       </c>
-      <c r="J60" s="37"/>
+      <c r="J60" s="39"/>
     </row>
     <row r="61" spans="2:10">
-      <c r="B61" s="23"/>
-      <c r="C61" s="32" t="s">
+      <c r="B61" s="25"/>
+      <c r="C61" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="33">
+      <c r="D61" s="35">
         <v>32738</v>
       </c>
-      <c r="E61" s="34"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="35">
+      <c r="E61" s="36"/>
+      <c r="F61" s="34"/>
+      <c r="G61" s="37">
         <v>45149</v>
       </c>
-      <c r="H61" s="32" t="s">
+      <c r="H61" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="I61" s="34">
+      <c r="I61" s="36">
         <v>2300</v>
       </c>
-      <c r="J61" s="37"/>
+      <c r="J61" s="39"/>
     </row>
     <row r="62" spans="2:10">
-      <c r="B62" s="23"/>
-      <c r="C62" s="32" t="s">
+      <c r="B62" s="25"/>
+      <c r="C62" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="35">
         <v>-14900</v>
       </c>
-      <c r="E62" s="34"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="35">
+      <c r="E62" s="36"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="37">
         <v>45149</v>
       </c>
-      <c r="H62" s="32" t="s">
+      <c r="H62" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="34">
+      <c r="I62" s="36">
         <v>54266</v>
       </c>
-      <c r="J62" s="37"/>
+      <c r="J62" s="39"/>
     </row>
     <row r="63" spans="2:10">
-      <c r="B63" s="23"/>
-      <c r="C63" s="32" t="s">
+      <c r="B63" s="25"/>
+      <c r="C63" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="35">
         <v>-171900</v>
       </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="35">
+      <c r="E63" s="36"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="37">
         <v>45244</v>
       </c>
-      <c r="H63" s="32" t="s">
+      <c r="H63" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="I63" s="34">
+      <c r="I63" s="36">
         <v>4790</v>
       </c>
-      <c r="J63" s="37"/>
+      <c r="J63" s="39"/>
     </row>
     <row r="64" spans="2:10">
-      <c r="B64" s="23"/>
-      <c r="C64" s="32" t="s">
+      <c r="B64" s="25"/>
+      <c r="C64" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D64" s="33">
+      <c r="D64" s="35">
         <v>-68600</v>
       </c>
-      <c r="E64" s="34"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="35">
+      <c r="E64" s="36"/>
+      <c r="F64" s="34"/>
+      <c r="G64" s="37">
         <v>45244</v>
       </c>
-      <c r="H64" s="32" t="s">
+      <c r="H64" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I64" s="34">
+      <c r="I64" s="36">
         <v>635</v>
       </c>
-      <c r="J64" s="37"/>
+      <c r="J64" s="39"/>
     </row>
     <row r="65" spans="2:10">
-      <c r="B65" s="23"/>
-      <c r="C65" s="32" t="s">
+      <c r="B65" s="25"/>
+      <c r="C65" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="35">
         <v>18500</v>
       </c>
-      <c r="E65" s="34"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="35">
+      <c r="E65" s="36"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="37">
         <v>45272</v>
       </c>
-      <c r="H65" s="32" t="s">
+      <c r="H65" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="I65" s="34">
+      <c r="I65" s="36">
         <v>34599</v>
       </c>
-      <c r="J65" s="37"/>
+      <c r="J65" s="39"/>
     </row>
     <row r="66" spans="2:10">
-      <c r="B66" s="23"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="35">
+      <c r="B66" s="25"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="35"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="34"/>
+      <c r="G66" s="37">
         <v>45272</v>
       </c>
-      <c r="H66" s="32" t="s">
+      <c r="H66" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="I66" s="34">
+      <c r="I66" s="36">
         <v>2460</v>
       </c>
-      <c r="J66" s="37"/>
+      <c r="J66" s="39"/>
     </row>
     <row r="67" spans="2:10">
-      <c r="B67" s="23"/>
-      <c r="C67" s="32" t="s">
+      <c r="B67" s="25"/>
+      <c r="C67" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D67" s="33">
+      <c r="D67" s="35">
         <v>338000</v>
       </c>
-      <c r="E67" s="34"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="37"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="34"/>
+      <c r="G67" s="34"/>
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="39"/>
     </row>
     <row r="68" spans="2:10">
-      <c r="B68" s="23"/>
-      <c r="C68" s="32" t="s">
+      <c r="B68" s="25"/>
+      <c r="C68" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D68" s="33">
+      <c r="D68" s="35">
         <f>SUM(D60:D65)+I59</f>
         <v>245738</v>
       </c>
-      <c r="E68" s="34"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="37"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="34"/>
+      <c r="G68" s="34"/>
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="39"/>
     </row>
     <row r="69" spans="2:10">
-      <c r="B69" s="23"/>
-      <c r="C69" s="32" t="s">
+      <c r="B69" s="25"/>
+      <c r="C69" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D69" s="34">
+      <c r="D69" s="36">
         <f>D67+D68</f>
         <v>583738</v>
       </c>
-      <c r="E69" s="34"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="37"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="34"/>
+      <c r="G69" s="34"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="39"/>
     </row>
     <row r="70" ht="16.95" spans="2:10">
-      <c r="B70" s="41"/>
-      <c r="C70" s="26" t="s">
+      <c r="B70" s="42"/>
+      <c r="C70" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D70" s="42">
+      <c r="D70" s="43">
         <f>D69-D84</f>
         <v>443038</v>
       </c>
       <c r="E70" s="9"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="39"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="41"/>
     </row>
     <row r="71" spans="2:10">
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="34"/>
+      <c r="B71" s="34"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="36"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="36"/>
     </row>
     <row r="72" ht="16.95" spans="2:10">
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="34"/>
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="36"/>
     </row>
     <row r="73" spans="2:10">
-      <c r="B73" s="18">
+      <c r="B73" s="20">
         <v>2022</v>
       </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="34"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="38"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="34"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="36"/>
     </row>
     <row r="74" spans="2:10">
-      <c r="B74" s="23"/>
-      <c r="C74" s="32" t="s">
+      <c r="B74" s="25"/>
+      <c r="C74" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D74" s="37">
+      <c r="D74" s="39">
         <v>890500</v>
       </c>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="34"/>
+      <c r="F74" s="34"/>
+      <c r="G74" s="34"/>
+      <c r="H74" s="34"/>
+      <c r="I74" s="34"/>
+      <c r="J74" s="36"/>
     </row>
     <row r="75" spans="2:10">
-      <c r="B75" s="23"/>
-      <c r="C75" s="32" t="s">
+      <c r="B75" s="25"/>
+      <c r="C75" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="D75" s="37">
+      <c r="D75" s="39">
         <v>-9600</v>
       </c>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="34"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="36"/>
     </row>
     <row r="76" spans="2:10">
-      <c r="B76" s="23"/>
-      <c r="C76" s="32" t="s">
+      <c r="B76" s="25"/>
+      <c r="C76" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D76" s="37">
+      <c r="D76" s="39">
         <v>-38800</v>
       </c>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="34"/>
+      <c r="F76" s="34"/>
+      <c r="G76" s="34"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="34"/>
+      <c r="J76" s="36"/>
     </row>
     <row r="77" spans="2:10">
-      <c r="B77" s="23"/>
-      <c r="C77" s="32" t="s">
+      <c r="B77" s="25"/>
+      <c r="C77" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D77" s="37">
+      <c r="D77" s="39">
         <v>137800</v>
       </c>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="34"/>
+      <c r="F77" s="34"/>
+      <c r="G77" s="34"/>
+      <c r="H77" s="34"/>
+      <c r="I77" s="34"/>
+      <c r="J77" s="36"/>
     </row>
     <row r="78" spans="2:10">
-      <c r="B78" s="23"/>
-      <c r="C78" s="32" t="s">
+      <c r="B78" s="25"/>
+      <c r="C78" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D78" s="37">
+      <c r="D78" s="39">
         <v>-49300</v>
       </c>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="34"/>
+      <c r="F78" s="34"/>
+      <c r="G78" s="34"/>
+      <c r="H78" s="34"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="36"/>
     </row>
     <row r="79" spans="2:10">
-      <c r="B79" s="23"/>
-      <c r="C79" s="32" t="s">
+      <c r="B79" s="25"/>
+      <c r="C79" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D79" s="37">
+      <c r="D79" s="39">
         <v>15600</v>
       </c>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="34"/>
+      <c r="F79" s="34"/>
+      <c r="G79" s="34"/>
+      <c r="H79" s="34"/>
+      <c r="I79" s="34"/>
+      <c r="J79" s="36"/>
     </row>
     <row r="80" spans="2:10">
-      <c r="B80" s="23"/>
-      <c r="C80" s="32" t="s">
+      <c r="B80" s="25"/>
+      <c r="C80" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="D80" s="37">
+      <c r="D80" s="39">
         <v>-19600</v>
       </c>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="34"/>
+      <c r="F80" s="34"/>
+      <c r="G80" s="34"/>
+      <c r="H80" s="34"/>
+      <c r="I80" s="34"/>
+      <c r="J80" s="36"/>
     </row>
     <row r="81" spans="2:10">
-      <c r="B81" s="23"/>
-      <c r="C81" s="32" t="s">
+      <c r="B81" s="25"/>
+      <c r="C81" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="D81" s="37">
+      <c r="D81" s="39">
         <v>58600</v>
       </c>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="34"/>
+      <c r="F81" s="34"/>
+      <c r="G81" s="34"/>
+      <c r="H81" s="34"/>
+      <c r="I81" s="34"/>
+      <c r="J81" s="36"/>
     </row>
     <row r="82" spans="2:10">
-      <c r="B82" s="23"/>
+      <c r="B82" s="25"/>
       <c r="C82" t="s">
         <v>48</v>
       </c>
-      <c r="D82" s="37">
+      <c r="D82" s="39">
         <v>75005</v>
       </c>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
+      <c r="J82" s="36"/>
     </row>
     <row r="83" spans="2:10">
-      <c r="B83" s="23"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="37"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="34"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="34"/>
+      <c r="D83" s="39"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+      <c r="J83" s="36"/>
     </row>
     <row r="84" spans="2:10">
-      <c r="B84" s="23"/>
-      <c r="C84" s="32" t="s">
+      <c r="B84" s="25"/>
+      <c r="C84" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D84" s="37">
+      <c r="D84" s="39">
         <v>140700</v>
       </c>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="34"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="34"/>
+      <c r="H84" s="34"/>
+      <c r="I84" s="34"/>
+      <c r="J84" s="36"/>
     </row>
     <row r="85" spans="2:10">
-      <c r="B85" s="23"/>
-      <c r="C85" s="32" t="s">
+      <c r="B85" s="25"/>
+      <c r="C85" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="D85" s="37">
+      <c r="D85" s="39">
         <f>SUM(D74:D82)</f>
         <v>1060205</v>
       </c>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="34"/>
+      <c r="F85" s="34"/>
+      <c r="G85" s="34"/>
+      <c r="H85" s="34"/>
+      <c r="I85" s="34"/>
+      <c r="J85" s="36"/>
     </row>
     <row r="86" spans="2:10">
-      <c r="B86" s="23"/>
-      <c r="C86" s="32" t="s">
+      <c r="B86" s="25"/>
+      <c r="C86" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="D86" s="37">
+      <c r="D86" s="39">
         <f>D84+D85</f>
         <v>1200905</v>
       </c>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="34"/>
+      <c r="F86" s="34"/>
+      <c r="G86" s="34"/>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
+      <c r="J86" s="36"/>
     </row>
     <row r="87" ht="16.95" spans="2:4">
-      <c r="B87" s="41"/>
-      <c r="C87" s="26" t="s">
+      <c r="B87" s="42"/>
+      <c r="C87" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D87" s="44">
+      <c r="D87" s="45">
         <f>D86-D107</f>
         <v>488305</v>
       </c>
     </row>
     <row r="88" spans="4:4">
-      <c r="D88" s="28"/>
+      <c r="D88" s="31"/>
     </row>
     <row r="89" ht="16.95" spans="4:4">
-      <c r="D89" s="28"/>
+      <c r="D89" s="31"/>
     </row>
     <row r="90" spans="2:4">
-      <c r="B90" s="18">
+      <c r="B90" s="20">
         <v>2021</v>
       </c>
-      <c r="C90" s="19"/>
-      <c r="D90" s="45"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="46"/>
     </row>
     <row r="91" spans="2:4">
-      <c r="B91" s="23"/>
+      <c r="B91" s="25"/>
       <c r="C91" t="s">
         <v>58</v>
       </c>
-      <c r="D91" s="37">
+      <c r="D91" s="39">
         <v>11300</v>
       </c>
     </row>
     <row r="92" spans="2:4">
-      <c r="B92" s="23"/>
+      <c r="B92" s="25"/>
       <c r="C92" t="s">
         <v>59</v>
       </c>
-      <c r="D92" s="37">
+      <c r="D92" s="39">
         <v>33300</v>
       </c>
     </row>
     <row r="93" spans="2:4">
-      <c r="B93" s="23"/>
+      <c r="B93" s="25"/>
       <c r="C93" t="s">
         <v>60</v>
       </c>
-      <c r="D93" s="37">
+      <c r="D93" s="39">
         <v>108700</v>
       </c>
     </row>
     <row r="94" spans="2:4">
-      <c r="B94" s="23"/>
+      <c r="B94" s="25"/>
       <c r="C94" t="s">
         <v>61</v>
       </c>
-      <c r="D94" s="37">
+      <c r="D94" s="39">
         <v>-14800</v>
       </c>
     </row>
     <row r="95" spans="2:4">
-      <c r="B95" s="23"/>
+      <c r="B95" s="25"/>
       <c r="C95" t="s">
         <v>62</v>
       </c>
-      <c r="D95" s="37">
+      <c r="D95" s="39">
         <v>35300</v>
       </c>
     </row>
     <row r="96" spans="2:4">
-      <c r="B96" s="23"/>
+      <c r="B96" s="25"/>
       <c r="C96" t="s">
         <v>63</v>
       </c>
-      <c r="D96" s="37">
+      <c r="D96" s="39">
         <v>-8900</v>
       </c>
     </row>
     <row r="97" spans="2:4">
-      <c r="B97" s="23"/>
+      <c r="B97" s="25"/>
       <c r="C97" t="s">
         <v>64</v>
       </c>
-      <c r="D97" s="37">
+      <c r="D97" s="39">
         <v>-6000</v>
       </c>
     </row>
     <row r="98" spans="2:4">
-      <c r="B98" s="23"/>
+      <c r="B98" s="25"/>
       <c r="C98" t="s">
         <v>53</v>
       </c>
-      <c r="D98" s="37">
+      <c r="D98" s="39">
         <v>56100</v>
       </c>
     </row>
     <row r="99" spans="2:4">
-      <c r="B99" s="23"/>
+      <c r="B99" s="25"/>
       <c r="C99" t="s">
         <v>65</v>
       </c>
-      <c r="D99" s="37">
+      <c r="D99" s="39">
         <v>1900</v>
       </c>
     </row>
     <row r="100" spans="2:4">
-      <c r="B100" s="23"/>
+      <c r="B100" s="25"/>
       <c r="C100" t="s">
         <v>66</v>
       </c>
-      <c r="D100" s="37">
+      <c r="D100" s="39">
         <v>-12700</v>
       </c>
     </row>
     <row r="101" spans="2:4">
-      <c r="B101" s="23"/>
+      <c r="B101" s="25"/>
       <c r="C101" t="s">
         <v>67</v>
       </c>
-      <c r="D101" s="37">
+      <c r="D101" s="39">
         <v>77700</v>
       </c>
     </row>
     <row r="102" spans="2:4">
-      <c r="B102" s="23"/>
+      <c r="B102" s="25"/>
       <c r="C102" t="s">
         <v>68</v>
       </c>
-      <c r="D102" s="37">
+      <c r="D102" s="39">
         <v>-13200</v>
       </c>
     </row>
     <row r="103" spans="2:4">
-      <c r="B103" s="23"/>
+      <c r="B103" s="25"/>
       <c r="C103" t="s">
         <v>69</v>
       </c>
-      <c r="D103" s="37">
+      <c r="D103" s="39">
         <v>-10500</v>
       </c>
     </row>
     <row r="104" spans="2:4">
-      <c r="B104" s="23"/>
+      <c r="B104" s="25"/>
       <c r="C104" t="s">
         <v>46</v>
       </c>
-      <c r="D104" s="37">
+      <c r="D104" s="39">
         <v>244900</v>
       </c>
     </row>
     <row r="105" spans="2:4">
-      <c r="B105" s="23"/>
+      <c r="B105" s="25"/>
       <c r="C105" t="s">
         <v>48</v>
       </c>
-      <c r="D105" s="37">
+      <c r="D105" s="39">
         <v>67032</v>
       </c>
     </row>
     <row r="106" spans="2:4">
-      <c r="B106" s="23"/>
-      <c r="D106" s="37"/>
+      <c r="B106" s="25"/>
+      <c r="D106" s="39"/>
     </row>
     <row r="107" spans="2:4">
-      <c r="B107" s="23"/>
+      <c r="B107" s="25"/>
       <c r="C107" t="s">
         <v>24</v>
       </c>
-      <c r="D107" s="37">
+      <c r="D107" s="39">
         <v>712600</v>
       </c>
     </row>
     <row r="108" spans="2:4">
-      <c r="B108" s="23"/>
+      <c r="B108" s="25"/>
       <c r="C108" t="s">
         <v>26</v>
       </c>
-      <c r="D108" s="37">
+      <c r="D108" s="39">
         <f>SUM(D91:D105)</f>
         <v>570132</v>
       </c>
     </row>
     <row r="109" spans="2:4">
-      <c r="B109" s="23"/>
+      <c r="B109" s="25"/>
       <c r="C109" t="s">
         <v>27</v>
       </c>
-      <c r="D109" s="37">
+      <c r="D109" s="39">
         <f>D107+D108</f>
         <v>1282732</v>
       </c>
     </row>
     <row r="110" ht="16.95" spans="2:4">
-      <c r="B110" s="41"/>
-      <c r="C110" s="26" t="s">
+      <c r="B110" s="42"/>
+      <c r="C110" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="D110" s="44">
+      <c r="D110" s="45">
         <f>D109-D118</f>
         <v>1219032</v>
       </c>
     </row>
     <row r="112" ht="16.95"/>
     <row r="113" spans="2:4">
-      <c r="B113" s="18">
+      <c r="B113" s="20">
         <v>2020</v>
       </c>
-      <c r="C113" s="19"/>
-      <c r="D113" s="36"/>
+      <c r="C113" s="21"/>
+      <c r="D113" s="38"/>
     </row>
     <row r="114" spans="2:4">
-      <c r="B114" s="23"/>
+      <c r="B114" s="25"/>
       <c r="C114" t="s">
         <v>58</v>
       </c>
-      <c r="D114" s="37">
+      <c r="D114" s="39">
         <v>49400</v>
       </c>
     </row>
     <row r="115" spans="2:4">
-      <c r="B115" s="23"/>
+      <c r="B115" s="25"/>
       <c r="C115" t="s">
         <v>59</v>
       </c>
-      <c r="D115" s="37">
+      <c r="D115" s="39">
         <v>64300</v>
       </c>
     </row>
     <row r="116" spans="2:4">
-      <c r="B116" s="23"/>
+      <c r="B116" s="25"/>
       <c r="C116" t="s">
         <v>70</v>
       </c>
-      <c r="D116" s="37">
+      <c r="D116" s="39">
         <v>-6000</v>
       </c>
     </row>
     <row r="117" spans="2:4">
-      <c r="B117" s="23"/>
-      <c r="D117" s="37"/>
+      <c r="B117" s="25"/>
+      <c r="D117" s="39"/>
     </row>
     <row r="118" spans="2:4">
-      <c r="B118" s="23"/>
+      <c r="B118" s="25"/>
       <c r="C118" t="s">
         <v>24</v>
       </c>
-      <c r="D118" s="37">
+      <c r="D118" s="39">
         <v>63700</v>
       </c>
     </row>
     <row r="119" spans="2:4">
-      <c r="B119" s="23"/>
+      <c r="B119" s="25"/>
       <c r="C119" t="s">
         <v>26</v>
       </c>
-      <c r="D119" s="37">
+      <c r="D119" s="39">
         <f>SUM(D114:D116)</f>
         <v>107700</v>
       </c>
     </row>
     <row r="120" ht="16.95" spans="2:4">
-      <c r="B120" s="41"/>
-      <c r="C120" s="26" t="s">
+      <c r="B120" s="42"/>
+      <c r="C120" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D120" s="44">
+      <c r="D120" s="45">
         <f>D118+D119</f>
         <v>171400</v>
       </c>
     </row>
     <row r="121" spans="4:4">
-      <c r="D121" s="28"/>
+      <c r="D121" s="31"/>
     </row>
     <row r="122" spans="4:4">
-      <c r="D122" s="28"/>
+      <c r="D122" s="31"/>
     </row>
     <row r="123" spans="4:4">
-      <c r="D123" s="28"/>
+      <c r="D123" s="31"/>
     </row>
     <row r="124" spans="4:4">
-      <c r="D124" s="28"/>
+      <c r="D124" s="31"/>
     </row>
     <row r="125" spans="4:4">
-      <c r="D125" s="28"/>
+      <c r="D125" s="31"/>
     </row>
     <row r="126" spans="4:4">
-      <c r="D126" s="28"/>
+      <c r="D126" s="31"/>
     </row>
     <row r="127" spans="4:4">
-      <c r="D127" s="28"/>
+      <c r="D127" s="31"/>
     </row>
     <row r="128" spans="4:4">
-      <c r="D128" s="28"/>
+      <c r="D128" s="31"/>
     </row>
     <row r="129" spans="4:4">
-      <c r="D129" s="28"/>
+      <c r="D129" s="31"/>
     </row>
     <row r="130" spans="4:4">
-      <c r="D130" s="28"/>
+      <c r="D130" s="31"/>
     </row>
     <row r="131" spans="4:4">
-      <c r="D131" s="28"/>
+      <c r="D131" s="31"/>
     </row>
     <row r="132" spans="4:4">
-      <c r="D132" s="28"/>
+      <c r="D132" s="31"/>
     </row>
     <row r="133" spans="4:4">
-      <c r="D133" s="28"/>
+      <c r="D133" s="31"/>
     </row>
     <row r="134" spans="4:4">
-      <c r="D134" s="28"/>
+      <c r="D134" s="31"/>
     </row>
     <row r="135" spans="4:4">
-      <c r="D135" s="28"/>
+      <c r="D135" s="31"/>
     </row>
     <row r="136" spans="4:4">
-      <c r="D136" s="28"/>
+      <c r="D136" s="31"/>
     </row>
     <row r="137" spans="4:4">
-      <c r="D137" s="28"/>
+      <c r="D137" s="31"/>
     </row>
     <row r="138" spans="4:4">
-      <c r="D138" s="28"/>
+      <c r="D138" s="31"/>
     </row>
     <row r="139" spans="4:4">
-      <c r="D139" s="28"/>
+      <c r="D139" s="31"/>
     </row>
     <row r="140" spans="4:4">
-      <c r="D140" s="28"/>
+      <c r="D140" s="31"/>
     </row>
     <row r="141" spans="4:4">
-      <c r="D141" s="28"/>
+      <c r="D141" s="31"/>
     </row>
     <row r="142" spans="4:4">
-      <c r="D142" s="28"/>
+      <c r="D142" s="31"/>
     </row>
     <row r="143" spans="4:4">
-      <c r="D143" s="28"/>
+      <c r="D143" s="31"/>
     </row>
     <row r="144" spans="4:4">
-      <c r="D144" s="28"/>
+      <c r="D144" s="31"/>
     </row>
     <row r="145" spans="4:4">
-      <c r="D145" s="28"/>
+      <c r="D145" s="31"/>
     </row>
     <row r="146" spans="4:4">
-      <c r="D146" s="28"/>
+      <c r="D146" s="31"/>
     </row>
     <row r="147" spans="4:4">
-      <c r="D147" s="28"/>
+      <c r="D147" s="31"/>
     </row>
     <row r="148" spans="4:4">
-      <c r="D148" s="28"/>
+      <c r="D148" s="31"/>
     </row>
     <row r="149" spans="4:4">
-      <c r="D149" s="28"/>
+      <c r="D149" s="31"/>
     </row>
     <row r="150" spans="4:4">
-      <c r="D150" s="28"/>
+      <c r="D150" s="31"/>
     </row>
     <row r="151" spans="4:4">
-      <c r="D151" s="28"/>
+      <c r="D151" s="31"/>
     </row>
     <row r="152" spans="4:4">
-      <c r="D152" s="28"/>
+      <c r="D152" s="31"/>
     </row>
     <row r="153" spans="4:4">
-      <c r="D153" s="28"/>
+      <c r="D153" s="31"/>
     </row>
     <row r="154" spans="4:4">
-      <c r="D154" s="28"/>
+      <c r="D154" s="31"/>
     </row>
     <row r="155" spans="4:4">
-      <c r="D155" s="28"/>
+      <c r="D155" s="31"/>
     </row>
     <row r="156" spans="4:4">
-      <c r="D156" s="28"/>
+      <c r="D156" s="31"/>
     </row>
     <row r="157" spans="4:4">
-      <c r="D157" s="28"/>
+      <c r="D157" s="31"/>
     </row>
     <row r="158" spans="4:4">
-      <c r="D158" s="28"/>
+      <c r="D158" s="31"/>
     </row>
     <row r="159" spans="4:4">
-      <c r="D159" s="28"/>
+      <c r="D159" s="31"/>
     </row>
     <row r="160" spans="4:4">
-      <c r="D160" s="28"/>
+      <c r="D160" s="31"/>
     </row>
     <row r="161" spans="4:4">
-      <c r="D161" s="28"/>
+      <c r="D161" s="31"/>
     </row>
     <row r="162" spans="4:4">
-      <c r="D162" s="28"/>
+      <c r="D162" s="31"/>
     </row>
     <row r="163" spans="4:4">
-      <c r="D163" s="28"/>
+      <c r="D163" s="31"/>
     </row>
     <row r="164" spans="4:4">
-      <c r="D164" s="28"/>
+      <c r="D164" s="31"/>
     </row>
     <row r="165" spans="4:4">
-      <c r="D165" s="28"/>
+      <c r="D165" s="31"/>
     </row>
     <row r="166" spans="4:4">
-      <c r="D166" s="28"/>
+      <c r="D166" s="31"/>
     </row>
     <row r="167" spans="4:4">
-      <c r="D167" s="28"/>
+      <c r="D167" s="31"/>
     </row>
     <row r="168" spans="4:4">
-      <c r="D168" s="28"/>
+      <c r="D168" s="31"/>
     </row>
     <row r="169" spans="4:4">
-      <c r="D169" s="28"/>
+      <c r="D169" s="31"/>
     </row>
     <row r="170" spans="4:4">
-      <c r="D170" s="28"/>
+      <c r="D170" s="31"/>
     </row>
     <row r="171" spans="4:4">
-      <c r="D171" s="28"/>
+      <c r="D171" s="31"/>
     </row>
     <row r="172" spans="4:4">
-      <c r="D172" s="28"/>
+      <c r="D172" s="31"/>
     </row>
     <row r="173" spans="4:4">
-      <c r="D173" s="28"/>
+      <c r="D173" s="31"/>
     </row>
     <row r="174" spans="4:4">
-      <c r="D174" s="28"/>
+      <c r="D174" s="31"/>
     </row>
     <row r="175" spans="4:4">
-      <c r="D175" s="28"/>
+      <c r="D175" s="31"/>
     </row>
     <row r="176" spans="4:4">
-      <c r="D176" s="28"/>
+      <c r="D176" s="31"/>
     </row>
     <row r="177" spans="4:4">
-      <c r="D177" s="28"/>
+      <c r="D177" s="31"/>
     </row>
     <row r="178" spans="4:4">
-      <c r="D178" s="28"/>
+      <c r="D178" s="31"/>
     </row>
     <row r="179" spans="4:4">
-      <c r="D179" s="28"/>
+      <c r="D179" s="31"/>
     </row>
     <row r="180" spans="4:4">
-      <c r="D180" s="28"/>
+      <c r="D180" s="31"/>
     </row>
     <row r="181" spans="4:4">
-      <c r="D181" s="28"/>
+      <c r="D181" s="31"/>
     </row>
     <row r="182" spans="4:4">
-      <c r="D182" s="28"/>
+      <c r="D182" s="31"/>
     </row>
     <row r="183" spans="4:4">
-      <c r="D183" s="28"/>
+      <c r="D183" s="31"/>
     </row>
     <row r="184" spans="4:4">
-      <c r="D184" s="28"/>
+      <c r="D184" s="31"/>
     </row>
     <row r="185" spans="4:4">
-      <c r="D185" s="28"/>
+      <c r="D185" s="31"/>
     </row>
     <row r="186" spans="4:4">
-      <c r="D186" s="28"/>
+      <c r="D186" s="31"/>
     </row>
     <row r="187" spans="4:4">
-      <c r="D187" s="28"/>
+      <c r="D187" s="31"/>
     </row>
     <row r="188" spans="4:4">
-      <c r="D188" s="28"/>
+      <c r="D188" s="31"/>
     </row>
     <row r="189" spans="4:4">
-      <c r="D189" s="28"/>
+      <c r="D189" s="31"/>
     </row>
     <row r="190" spans="4:4">
-      <c r="D190" s="28"/>
+      <c r="D190" s="31"/>
     </row>
     <row r="191" spans="4:4">
-      <c r="D191" s="28"/>
+      <c r="D191" s="31"/>
     </row>
     <row r="192" spans="4:4">
-      <c r="D192" s="28"/>
+      <c r="D192" s="31"/>
     </row>
     <row r="193" spans="4:4">
-      <c r="D193" s="28"/>
+      <c r="D193" s="31"/>
     </row>
     <row r="194" spans="4:4">
-      <c r="D194" s="28"/>
+      <c r="D194" s="31"/>
     </row>
     <row r="195" spans="4:4">
-      <c r="D195" s="28"/>
+      <c r="D195" s="31"/>
     </row>
     <row r="196" spans="4:4">
-      <c r="D196" s="28"/>
+      <c r="D196" s="31"/>
     </row>
     <row r="197" spans="4:4">
-      <c r="D197" s="28"/>
+      <c r="D197" s="31"/>
     </row>
     <row r="198" spans="4:4">
-      <c r="D198" s="28"/>
+      <c r="D198" s="31"/>
     </row>
     <row r="199" spans="4:4">
-      <c r="D199" s="28"/>
+      <c r="D199" s="31"/>
     </row>
     <row r="200" spans="4:4">
-      <c r="D200" s="28"/>
+      <c r="D200" s="31"/>
     </row>
     <row r="201" spans="4:4">
-      <c r="D201" s="28"/>
+      <c r="D201" s="31"/>
     </row>
     <row r="202" spans="4:4">
-      <c r="D202" s="28"/>
+      <c r="D202" s="31"/>
     </row>
     <row r="203" spans="4:4">
-      <c r="D203" s="28"/>
+      <c r="D203" s="31"/>
     </row>
     <row r="204" spans="4:4">
-      <c r="D204" s="28"/>
+      <c r="D204" s="31"/>
     </row>
     <row r="205" spans="4:4">
-      <c r="D205" s="28"/>
+      <c r="D205" s="31"/>
     </row>
     <row r="206" spans="4:4">
-      <c r="D206" s="28"/>
+      <c r="D206" s="31"/>
     </row>
     <row r="207" spans="4:4">
-      <c r="D207" s="28"/>
+      <c r="D207" s="31"/>
     </row>
     <row r="208" spans="4:4">
-      <c r="D208" s="28"/>
+      <c r="D208" s="31"/>
     </row>
     <row r="209" spans="4:4">
-      <c r="D209" s="28"/>
+      <c r="D209" s="31"/>
     </row>
     <row r="210" spans="4:4">
-      <c r="D210" s="28"/>
+      <c r="D210" s="31"/>
     </row>
     <row r="211" spans="4:4">
-      <c r="D211" s="46"/>
+      <c r="D211" s="47"/>
     </row>
     <row r="212" spans="4:4">
-      <c r="D212" s="46"/>
+      <c r="D212" s="47"/>
     </row>
     <row r="213" spans="4:4">
-      <c r="D213" s="46"/>
+      <c r="D213" s="47"/>
     </row>
   </sheetData>
   <sortState ref="G5:I11">
@@ -4754,2148 +4791,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr/>
-  <dimension ref="A1:AC213"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="16.2"/>
-  <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="10.1111111111111"/>
-    <col min="3" max="3" width="14.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="12.2222222222222" style="1"/>
-    <col min="5" max="5" width="11.3333333333333" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="11.5555555555556"/>
-    <col min="9" max="9" width="13.1111111111111" customWidth="1"/>
-    <col min="10" max="10" width="14.6666666666667" style="1" customWidth="1"/>
-    <col min="11" max="12" width="11.5555555555556" style="1"/>
-    <col min="13" max="15" width="10.6666666666667" style="1" customWidth="1"/>
-    <col min="16" max="17" width="10.4444444444444" style="1" customWidth="1"/>
-    <col min="18" max="18" width="11.5555555555556" style="1"/>
-    <col min="19" max="19" width="10.4444444444444" style="1"/>
-    <col min="20" max="20" width="11.5555555555556"/>
-    <col min="21" max="21" width="15.6666666666667" customWidth="1"/>
-    <col min="22" max="22" width="10.4444444444444"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="17">
-        <f>D32+D50+D70+D87+D110+D120</f>
-        <v>8235533</v>
-      </c>
-      <c r="C1" s="17"/>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="17">
-        <f>A1+M8</f>
-        <v>20114060</v>
-      </c>
-      <c r="C2" s="17"/>
-      <c r="O2" s="1">
-        <f>O6*R6</f>
-        <v>550000</v>
-      </c>
-      <c r="P2" s="1">
-        <f>O2/12</f>
-        <v>45833.3333333333</v>
-      </c>
-    </row>
-    <row r="3" ht="16.95" spans="3:16">
-      <c r="C3" s="17"/>
-      <c r="O3" s="1">
-        <f>(O6+P6)*R6-P6*T6</f>
-        <v>550000</v>
-      </c>
-      <c r="P3" s="1">
-        <f>O3/12</f>
-        <v>45833.3333333333</v>
-      </c>
-    </row>
-    <row r="4" ht="16.95" spans="2:10">
-      <c r="B4" s="18">
-        <v>2026</v>
-      </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20">
-        <f>SUM($D5:$D10)</f>
-        <v>8538149</v>
-      </c>
-      <c r="E4" s="21"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="20">
-        <f>SUM($I5:$I18)</f>
-        <v>117104</v>
-      </c>
-      <c r="J4" s="36"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="23"/>
-      <c r="C5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1273965</v>
-      </c>
-      <c r="G5" s="24">
-        <v>45665</v>
-      </c>
-      <c r="H5" t="s">
-        <v>2</v>
-      </c>
-      <c r="I5" s="1">
-        <v>48000</v>
-      </c>
-      <c r="J5" s="37"/>
-      <c r="L5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" s="1">
-        <v>8655253</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="S5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="V5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" s="23"/>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1">
-        <v>-73320</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46055</v>
-      </c>
-      <c r="H6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I6" s="1">
-        <v>6650</v>
-      </c>
-      <c r="J6" s="37"/>
-      <c r="L6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="1">
-        <v>8457384</v>
-      </c>
-      <c r="N6" s="1">
-        <f>Q12</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>10000000</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <f>(O6+P6)*1.6</f>
-        <v>16000000</v>
-      </c>
-      <c r="R6" s="38">
-        <v>0.055</v>
-      </c>
-      <c r="S6" s="1">
-        <f>Q6*R6</f>
-        <v>880000</v>
-      </c>
-      <c r="T6" s="38">
-        <v>0.03</v>
-      </c>
-      <c r="U6" s="1">
-        <f>(Q6-O6)*T6</f>
-        <v>180000</v>
-      </c>
-      <c r="V6" s="1">
-        <f>S6-U6</f>
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="7" ht="16.95" spans="2:23">
-      <c r="B7" s="23"/>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7337504</v>
-      </c>
-      <c r="E7" s="13"/>
-      <c r="G7" s="4">
-        <v>46121</v>
-      </c>
-      <c r="H7" t="s">
-        <v>2</v>
-      </c>
-      <c r="I7" s="1">
-        <v>61710</v>
-      </c>
-      <c r="J7" s="37"/>
-      <c r="L7" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="9">
-        <v>5234110</v>
-      </c>
-      <c r="R7" s="38"/>
-      <c r="S7" s="1">
-        <f t="shared" ref="S7:V7" si="0">S6/12</f>
-        <v>73333.3333333333</v>
-      </c>
-      <c r="T7" s="38"/>
-      <c r="U7" s="1">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-      <c r="V7" s="1">
-        <f t="shared" si="0"/>
-        <v>58333.3333333333</v>
-      </c>
-      <c r="W7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" s="23"/>
-      <c r="E8" s="13"/>
-      <c r="G8" s="4">
-        <v>46142</v>
-      </c>
-      <c r="H8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="1">
-        <v>744</v>
-      </c>
-      <c r="J8" s="37"/>
-      <c r="L8"/>
-      <c r="M8" s="1">
-        <f>M5+M6-M7+N6</f>
-        <v>11878527</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" s="23"/>
-      <c r="E9" s="13"/>
-      <c r="G9" s="4"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="37"/>
-      <c r="Q9" s="1">
-        <f>(O6+P6)*1.96</f>
-        <v>19600000</v>
-      </c>
-      <c r="S9" s="1">
-        <f>Q9*R6</f>
-        <v>1078000</v>
-      </c>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1">
-        <f>(Q9-O6)*T6</f>
-        <v>288000</v>
-      </c>
-      <c r="V9" s="1">
-        <f>S9-U9</f>
-        <v>790000</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="23"/>
-      <c r="E10" s="13"/>
-      <c r="G10" s="4"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="37"/>
-      <c r="L10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S10" s="1">
-        <f t="shared" ref="S10:V10" si="1">S9/12</f>
-        <v>89833.3333333333</v>
-      </c>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1">
-        <f t="shared" si="1"/>
-        <v>24000</v>
-      </c>
-      <c r="V10" s="1">
-        <f t="shared" si="1"/>
-        <v>65833.3333333333</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="23"/>
-      <c r="E11" s="13"/>
-      <c r="G11" s="4"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="37"/>
-      <c r="M11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="23"/>
-      <c r="G12" s="4"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="37"/>
-      <c r="L12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="13">
-        <v>179.5</v>
-      </c>
-      <c r="O12" s="13">
-        <v>160</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <f>(O12-N12)*M12*1000+P12</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <f>O12*M12*1000</f>
-        <v>0</v>
-      </c>
-      <c r="S12" s="40"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-    </row>
-    <row r="13" spans="2:22">
-      <c r="B13" s="23"/>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="37"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="38">
-        <f>(O12-N12)/N12</f>
-        <v>-0.108635097493036</v>
-      </c>
-      <c r="P13"/>
-      <c r="Q13"/>
-      <c r="R13" s="7">
-        <v>22315376</v>
-      </c>
-      <c r="S13"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-    </row>
-    <row r="14" spans="2:22">
-      <c r="B14" s="23"/>
-      <c r="C14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="37"/>
-      <c r="Q14"/>
-      <c r="R14" s="1">
-        <f>SUM(R11:R13)</f>
-        <v>22315376</v>
-      </c>
-      <c r="S14"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-    </row>
-    <row r="15" spans="2:22">
-      <c r="B15" s="23"/>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="1">
-        <f>D13+D14</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="37"/>
-      <c r="Q15"/>
-      <c r="S15"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="23"/>
-      <c r="C16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D16" s="1">
-        <f>D15-D29</f>
-        <v>-5234110</v>
-      </c>
-      <c r="G16" s="4"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="37"/>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="23"/>
-      <c r="G17" s="4"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="37"/>
-    </row>
-    <row r="18" ht="16.95" spans="2:10">
-      <c r="B18" s="25"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="39"/>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="17"/>
-    </row>
-    <row r="20" ht="16.95" spans="3:3">
-      <c r="C20" s="17"/>
-    </row>
-    <row r="21" ht="16.95" spans="2:15">
-      <c r="B21" s="18">
-        <v>2025</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="20">
-        <f>SUM($I22:$I36)</f>
-        <v>490723</v>
-      </c>
-      <c r="J21" s="36"/>
-      <c r="N21" s="4"/>
-      <c r="O21"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="23"/>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="1">
-        <v>-139300</v>
-      </c>
-      <c r="G22" s="24">
-        <v>45666</v>
-      </c>
-      <c r="H22" t="s">
-        <v>2</v>
-      </c>
-      <c r="I22" s="1">
-        <v>12000</v>
-      </c>
-      <c r="J22" s="37"/>
-      <c r="N22" s="4"/>
-      <c r="O22"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="23"/>
-      <c r="C23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="1">
-        <v>-210100</v>
-      </c>
-      <c r="G23" s="4">
-        <v>45706</v>
-      </c>
-      <c r="H23" t="s">
-        <v>31</v>
-      </c>
-      <c r="I23" s="1">
-        <v>201960</v>
-      </c>
-      <c r="J23" s="37"/>
-      <c r="N23" s="4"/>
-      <c r="O23"/>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="23"/>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="1">
-        <v>-91300</v>
-      </c>
-      <c r="G24" s="4">
-        <v>45723</v>
-      </c>
-      <c r="H24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="1">
-        <v>17325</v>
-      </c>
-      <c r="J24" s="37"/>
-      <c r="N24" s="4"/>
-      <c r="O24"/>
-    </row>
-    <row r="25" spans="2:15">
-      <c r="B25" s="23"/>
-      <c r="C25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D25" s="1">
-        <v>-610300</v>
-      </c>
-      <c r="G25" s="4">
-        <v>45733</v>
-      </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" s="1">
-        <v>360</v>
-      </c>
-      <c r="J25" s="37"/>
-      <c r="O25" s="13"/>
-    </row>
-    <row r="26" spans="2:29">
-      <c r="B26" s="23"/>
-      <c r="C26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26" s="1">
-        <v>180900</v>
-      </c>
-      <c r="G26" s="4">
-        <v>45737</v>
-      </c>
-      <c r="H26" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="1">
-        <v>2078</v>
-      </c>
-      <c r="J26" s="37"/>
-      <c r="O26" s="13"/>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
-      <c r="AB26" s="1"/>
-      <c r="AC26" s="1"/>
-    </row>
-    <row r="27" spans="2:29">
-      <c r="B27" s="23"/>
-      <c r="C27" t="s">
-        <v>37</v>
-      </c>
-      <c r="D27" s="1">
-        <v>-165600</v>
-      </c>
-      <c r="G27" s="4">
-        <v>45757</v>
-      </c>
-      <c r="H27" t="s">
-        <v>2</v>
-      </c>
-      <c r="I27" s="1">
-        <v>20250</v>
-      </c>
-      <c r="J27" s="37"/>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
-      <c r="AB27" s="1"/>
-      <c r="AC27" s="1"/>
-    </row>
-    <row r="28" spans="2:29">
-      <c r="B28" s="23"/>
-      <c r="D28" s="28"/>
-      <c r="G28" s="4">
-        <v>45763</v>
-      </c>
-      <c r="H28" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="1">
-        <v>175500</v>
-      </c>
-      <c r="J28" s="37"/>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-    </row>
-    <row r="29" spans="2:29">
-      <c r="B29" s="23"/>
-      <c r="C29" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="1">
-        <v>5234110</v>
-      </c>
-      <c r="G29" s="4">
-        <v>45848</v>
-      </c>
-      <c r="H29" t="s">
-        <v>2</v>
-      </c>
-      <c r="I29" s="1">
-        <v>20250</v>
-      </c>
-      <c r="J29" s="37"/>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
-      <c r="AB29" s="1"/>
-      <c r="AC29" s="1"/>
-    </row>
-    <row r="30" spans="2:29">
-      <c r="B30" s="23"/>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="1">
-        <f>SUM(D22:D27)+I21</f>
-        <v>-544977</v>
-      </c>
-      <c r="G30" s="4">
-        <v>45939</v>
-      </c>
-      <c r="H30" t="s">
-        <v>2</v>
-      </c>
-      <c r="I30" s="1">
-        <v>41000</v>
-      </c>
-      <c r="J30" s="37"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-      <c r="AB30" s="1"/>
-      <c r="AC30" s="1"/>
-    </row>
-    <row r="31" spans="2:29">
-      <c r="B31" s="23"/>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="1">
-        <f>D29+D30</f>
-        <v>4689133</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="37"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-      <c r="AC31" s="1"/>
-    </row>
-    <row r="32" spans="2:29">
-      <c r="B32" s="23"/>
-      <c r="C32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="29">
-        <f>D31-D47</f>
-        <v>4458133</v>
-      </c>
-      <c r="G32" s="4"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="37"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-      <c r="Y32" s="1"/>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
-      <c r="AB32" s="1"/>
-      <c r="AC32" s="1"/>
-    </row>
-    <row r="33" spans="2:29">
-      <c r="B33" s="23"/>
-      <c r="G33" s="4"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="37"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-      <c r="Y33" s="1"/>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
-      <c r="AB33" s="1"/>
-      <c r="AC33" s="1"/>
-    </row>
-    <row r="34" spans="2:29">
-      <c r="B34" s="23"/>
-      <c r="C34" t="s">
-        <v>38</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="37"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
-      <c r="AB34" s="1"/>
-      <c r="AC34" s="1"/>
-    </row>
-    <row r="35" spans="2:29">
-      <c r="B35" s="23"/>
-      <c r="C35" t="s">
-        <v>39</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="37"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1"/>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
-      <c r="AB35" s="1"/>
-      <c r="AC35" s="1"/>
-    </row>
-    <row r="36" ht="16.95" spans="2:29">
-      <c r="B36" s="25"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="39"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-      <c r="Y36" s="1"/>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
-      <c r="AB36" s="1"/>
-      <c r="AC36" s="1"/>
-    </row>
-    <row r="37" spans="20:29">
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1"/>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="1"/>
-    </row>
-    <row r="38" ht="16.95" spans="20:29">
-      <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1"/>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
-      <c r="AB38" s="1"/>
-      <c r="AC38" s="1"/>
-    </row>
-    <row r="39" ht="16.95" spans="2:29">
-      <c r="B39" s="18">
-        <v>2024</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="H39" s="19"/>
-      <c r="I39" s="20">
-        <f>SUM(I$40:I$56)</f>
-        <v>307025</v>
-      </c>
-      <c r="J39" s="36"/>
-      <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1"/>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
-      <c r="AB39" s="1"/>
-      <c r="AC39" s="1"/>
-    </row>
-    <row r="40" spans="2:29">
-      <c r="B40" s="23"/>
-      <c r="C40" t="s">
-        <v>40</v>
-      </c>
-      <c r="D40" s="1">
-        <v>-19000</v>
-      </c>
-      <c r="G40" s="4">
-        <v>45303</v>
-      </c>
-      <c r="H40" t="s">
-        <v>41</v>
-      </c>
-      <c r="I40" s="1">
-        <v>6210</v>
-      </c>
-      <c r="J40" s="37"/>
-      <c r="T40" s="1"/>
-      <c r="U40" s="1"/>
-      <c r="V40" s="1"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="1"/>
-      <c r="Y40" s="1"/>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
-      <c r="AB40" s="1"/>
-      <c r="AC40" s="1"/>
-    </row>
-    <row r="41" spans="2:29">
-      <c r="B41" s="23"/>
-      <c r="C41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D41" s="1">
-        <v>657000</v>
-      </c>
-      <c r="G41" s="4">
-        <v>45343</v>
-      </c>
-      <c r="H41" t="s">
-        <v>41</v>
-      </c>
-      <c r="I41" s="1">
-        <v>12080</v>
-      </c>
-      <c r="J41" s="37"/>
-      <c r="T41" s="1"/>
-      <c r="U41" s="1"/>
-      <c r="V41" s="1"/>
-      <c r="W41" s="1"/>
-      <c r="X41" s="1"/>
-      <c r="Y41" s="1"/>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="1"/>
-    </row>
-    <row r="42" spans="2:29">
-      <c r="B42" s="23"/>
-      <c r="C42" t="s">
-        <v>41</v>
-      </c>
-      <c r="D42" s="1">
-        <v>-10000</v>
-      </c>
-      <c r="G42" s="4">
-        <v>45376</v>
-      </c>
-      <c r="H42" t="s">
-        <v>41</v>
-      </c>
-      <c r="I42" s="1">
-        <v>3900</v>
-      </c>
-      <c r="J42" s="37"/>
-      <c r="T42" s="1"/>
-      <c r="U42" s="1"/>
-      <c r="V42" s="1"/>
-      <c r="W42" s="1"/>
-      <c r="X42" s="1"/>
-      <c r="Y42" s="1"/>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
-      <c r="AB42" s="1"/>
-      <c r="AC42" s="1"/>
-    </row>
-    <row r="43" spans="2:29">
-      <c r="B43" s="23"/>
-      <c r="C43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="1">
-        <v>663000</v>
-      </c>
-      <c r="G43" s="4">
-        <v>45393</v>
-      </c>
-      <c r="H43" t="s">
-        <v>2</v>
-      </c>
-      <c r="I43" s="1">
-        <v>7000</v>
-      </c>
-      <c r="J43" s="37"/>
-      <c r="T43" s="1"/>
-      <c r="U43" s="1"/>
-      <c r="V43" s="1"/>
-      <c r="W43" s="1"/>
-      <c r="X43" s="1"/>
-      <c r="Y43" s="1"/>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
-      <c r="AB43" s="1"/>
-      <c r="AC43" s="1"/>
-    </row>
-    <row r="44" spans="2:29">
-      <c r="B44" s="23"/>
-      <c r="C44" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" s="1">
-        <v>38600</v>
-      </c>
-      <c r="G44" s="4">
-        <v>45400</v>
-      </c>
-      <c r="H44" t="s">
-        <v>34</v>
-      </c>
-      <c r="I44" s="1">
-        <v>155000</v>
-      </c>
-      <c r="J44" s="37"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="1"/>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="23"/>
-      <c r="C45" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="1">
-        <v>-74000</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="G45" s="4">
-        <v>45470</v>
-      </c>
-      <c r="H45" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" s="1">
-        <v>3879</v>
-      </c>
-      <c r="J45" s="37"/>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="23"/>
-      <c r="G46" s="4">
-        <v>45484</v>
-      </c>
-      <c r="H46" t="s">
-        <v>2</v>
-      </c>
-      <c r="I46" s="1">
-        <v>7000</v>
-      </c>
-      <c r="J46" s="37"/>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" s="23"/>
-      <c r="C47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="1">
-        <v>231000</v>
-      </c>
-      <c r="G47" s="4">
-        <v>45489</v>
-      </c>
-      <c r="H47" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="1">
-        <v>13902</v>
-      </c>
-      <c r="J47" s="37"/>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" s="23"/>
-      <c r="C48" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="1">
-        <f>SUM(D40:D45)+I39</f>
-        <v>1562625</v>
-      </c>
-      <c r="G48" s="4">
-        <v>45506</v>
-      </c>
-      <c r="H48" t="s">
-        <v>29</v>
-      </c>
-      <c r="I48" s="1">
-        <v>81600</v>
-      </c>
-      <c r="J48" s="37"/>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="23"/>
-      <c r="C49" t="s">
-        <v>27</v>
-      </c>
-      <c r="D49" s="1">
-        <f>D47+D48</f>
-        <v>1793625</v>
-      </c>
-      <c r="G49" s="4">
-        <v>45513</v>
-      </c>
-      <c r="H49" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="1">
-        <v>783</v>
-      </c>
-      <c r="J49" s="37"/>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="23"/>
-      <c r="C50" t="s">
-        <v>28</v>
-      </c>
-      <c r="D50" s="29">
-        <f>D49-D67</f>
-        <v>1455625</v>
-      </c>
-      <c r="G50" s="4">
-        <v>45523</v>
-      </c>
-      <c r="H50" t="s">
-        <v>44</v>
-      </c>
-      <c r="I50" s="1">
-        <v>1161</v>
-      </c>
-      <c r="J50" s="37"/>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="23"/>
-      <c r="G51" s="4">
-        <v>45525</v>
-      </c>
-      <c r="H51" t="s">
-        <v>35</v>
-      </c>
-      <c r="I51" s="1">
-        <v>1237</v>
-      </c>
-      <c r="J51" s="37"/>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="23"/>
-      <c r="C52" t="s">
-        <v>38</v>
-      </c>
-      <c r="G52" s="4">
-        <v>45574</v>
-      </c>
-      <c r="H52" t="s">
-        <v>2</v>
-      </c>
-      <c r="I52" s="1">
-        <v>12000</v>
-      </c>
-      <c r="J52" s="37"/>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="30"/>
-      <c r="C53" t="s">
-        <v>39</v>
-      </c>
-      <c r="G53" s="4">
-        <v>45643</v>
-      </c>
-      <c r="H53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I53" s="1">
-        <v>1273</v>
-      </c>
-      <c r="J53" s="37"/>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="30"/>
-      <c r="J54" s="37"/>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="30"/>
-      <c r="G55" s="31"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="37"/>
-    </row>
-    <row r="56" ht="16.95" spans="2:10">
-      <c r="B56" s="25"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="9"/>
-      <c r="J56" s="39"/>
-    </row>
-    <row r="57" spans="2:2">
-      <c r="B57" s="4"/>
-    </row>
-    <row r="58" ht="16.95" spans="2:2">
-      <c r="B58" s="4"/>
-    </row>
-    <row r="59" ht="16.95" spans="2:10">
-      <c r="B59" s="18">
-        <v>2023</v>
-      </c>
-      <c r="C59" s="19"/>
-      <c r="D59" s="21"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="H59" s="19"/>
-      <c r="I59" s="20">
-        <f>SUM(I60:I66)</f>
-        <v>103800</v>
-      </c>
-      <c r="J59" s="36"/>
-    </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="23"/>
-      <c r="C60" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D60" s="33">
-        <v>346100</v>
-      </c>
-      <c r="E60" s="34"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="35">
-        <v>45135</v>
-      </c>
-      <c r="H60" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="I60" s="34">
-        <v>4750</v>
-      </c>
-      <c r="J60" s="37"/>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="23"/>
-      <c r="C61" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D61" s="33">
-        <v>32738</v>
-      </c>
-      <c r="E61" s="34"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="35">
-        <v>45149</v>
-      </c>
-      <c r="H61" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="I61" s="34">
-        <v>2300</v>
-      </c>
-      <c r="J61" s="37"/>
-    </row>
-    <row r="62" spans="2:10">
-      <c r="B62" s="23"/>
-      <c r="C62" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D62" s="33">
-        <v>-14900</v>
-      </c>
-      <c r="E62" s="34"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="35">
-        <v>45149</v>
-      </c>
-      <c r="H62" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I62" s="34">
-        <v>54266</v>
-      </c>
-      <c r="J62" s="37"/>
-    </row>
-    <row r="63" spans="2:10">
-      <c r="B63" s="23"/>
-      <c r="C63" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D63" s="33">
-        <v>-171900</v>
-      </c>
-      <c r="E63" s="34"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="35">
-        <v>45244</v>
-      </c>
-      <c r="H63" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="I63" s="34">
-        <v>4790</v>
-      </c>
-      <c r="J63" s="37"/>
-    </row>
-    <row r="64" spans="2:10">
-      <c r="B64" s="23"/>
-      <c r="C64" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="D64" s="33">
-        <v>-68600</v>
-      </c>
-      <c r="E64" s="34"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="35">
-        <v>45244</v>
-      </c>
-      <c r="H64" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I64" s="34">
-        <v>635</v>
-      </c>
-      <c r="J64" s="37"/>
-    </row>
-    <row r="65" spans="2:10">
-      <c r="B65" s="23"/>
-      <c r="C65" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="D65" s="33">
-        <v>18500</v>
-      </c>
-      <c r="E65" s="34"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="35">
-        <v>45272</v>
-      </c>
-      <c r="H65" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I65" s="34">
-        <v>34599</v>
-      </c>
-      <c r="J65" s="37"/>
-    </row>
-    <row r="66" spans="2:10">
-      <c r="B66" s="23"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="33"/>
-      <c r="E66" s="34"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="35">
-        <v>45272</v>
-      </c>
-      <c r="H66" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="I66" s="34">
-        <v>2460</v>
-      </c>
-      <c r="J66" s="37"/>
-    </row>
-    <row r="67" spans="2:10">
-      <c r="B67" s="23"/>
-      <c r="C67" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D67" s="33">
-        <v>338000</v>
-      </c>
-      <c r="E67" s="34"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="37"/>
-    </row>
-    <row r="68" spans="2:10">
-      <c r="B68" s="23"/>
-      <c r="C68" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="33">
-        <f>SUM(D60:D65)+I59</f>
-        <v>245738</v>
-      </c>
-      <c r="E68" s="34"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="37"/>
-    </row>
-    <row r="69" spans="2:10">
-      <c r="B69" s="23"/>
-      <c r="C69" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D69" s="34">
-        <f>D67+D68</f>
-        <v>583738</v>
-      </c>
-      <c r="E69" s="34"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="37"/>
-    </row>
-    <row r="70" ht="16.95" spans="2:10">
-      <c r="B70" s="41"/>
-      <c r="C70" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D70" s="42">
-        <f>D69-D84</f>
-        <v>443038</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="26"/>
-      <c r="H70" s="26"/>
-      <c r="I70" s="26"/>
-      <c r="J70" s="39"/>
-    </row>
-    <row r="71" spans="2:10">
-      <c r="B71" s="32"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="34"/>
-    </row>
-    <row r="72" ht="16.95" spans="2:10">
-      <c r="B72" s="32"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="43"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="34"/>
-    </row>
-    <row r="73" spans="2:10">
-      <c r="B73" s="18">
-        <v>2022</v>
-      </c>
-      <c r="C73" s="19"/>
-      <c r="D73" s="36"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="34"/>
-    </row>
-    <row r="74" spans="2:10">
-      <c r="B74" s="23"/>
-      <c r="C74" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D74" s="37">
-        <v>890500</v>
-      </c>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="34"/>
-    </row>
-    <row r="75" spans="2:10">
-      <c r="B75" s="23"/>
-      <c r="C75" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="D75" s="37">
-        <v>-9600</v>
-      </c>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="34"/>
-    </row>
-    <row r="76" spans="2:10">
-      <c r="B76" s="23"/>
-      <c r="C76" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D76" s="37">
-        <v>-38800</v>
-      </c>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="34"/>
-    </row>
-    <row r="77" spans="2:10">
-      <c r="B77" s="23"/>
-      <c r="C77" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="D77" s="37">
-        <v>137800</v>
-      </c>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="34"/>
-    </row>
-    <row r="78" spans="2:10">
-      <c r="B78" s="23"/>
-      <c r="C78" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" s="37">
-        <v>-49300</v>
-      </c>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="34"/>
-    </row>
-    <row r="79" spans="2:10">
-      <c r="B79" s="23"/>
-      <c r="C79" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="D79" s="37">
-        <v>15600</v>
-      </c>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="34"/>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" s="23"/>
-      <c r="C80" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" s="37">
-        <v>-19600</v>
-      </c>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="34"/>
-    </row>
-    <row r="81" spans="2:10">
-      <c r="B81" s="23"/>
-      <c r="C81" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="37">
-        <v>58600</v>
-      </c>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="34"/>
-    </row>
-    <row r="82" spans="2:10">
-      <c r="B82" s="23"/>
-      <c r="C82" t="s">
-        <v>48</v>
-      </c>
-      <c r="D82" s="37">
-        <v>75005</v>
-      </c>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="34"/>
-    </row>
-    <row r="83" spans="2:10">
-      <c r="B83" s="23"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="37"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="34"/>
-    </row>
-    <row r="84" spans="2:10">
-      <c r="B84" s="23"/>
-      <c r="C84" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" s="37">
-        <v>140700</v>
-      </c>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="34"/>
-    </row>
-    <row r="85" spans="2:10">
-      <c r="B85" s="23"/>
-      <c r="C85" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="D85" s="37">
-        <f>SUM(D74:D82)</f>
-        <v>1060205</v>
-      </c>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="34"/>
-    </row>
-    <row r="86" spans="2:10">
-      <c r="B86" s="23"/>
-      <c r="C86" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D86" s="37">
-        <f>D84+D85</f>
-        <v>1200905</v>
-      </c>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="34"/>
-    </row>
-    <row r="87" ht="16.95" spans="2:4">
-      <c r="B87" s="41"/>
-      <c r="C87" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D87" s="44">
-        <f>D86-D107</f>
-        <v>488305</v>
-      </c>
-    </row>
-    <row r="88" spans="4:4">
-      <c r="D88" s="28"/>
-    </row>
-    <row r="89" ht="16.95" spans="4:4">
-      <c r="D89" s="28"/>
-    </row>
-    <row r="90" spans="2:4">
-      <c r="B90" s="18">
-        <v>2021</v>
-      </c>
-      <c r="C90" s="19"/>
-      <c r="D90" s="45"/>
-    </row>
-    <row r="91" spans="2:4">
-      <c r="B91" s="23"/>
-      <c r="C91" t="s">
-        <v>58</v>
-      </c>
-      <c r="D91" s="37">
-        <v>11300</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4">
-      <c r="B92" s="23"/>
-      <c r="C92" t="s">
-        <v>59</v>
-      </c>
-      <c r="D92" s="37">
-        <v>33300</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4">
-      <c r="B93" s="23"/>
-      <c r="C93" t="s">
-        <v>60</v>
-      </c>
-      <c r="D93" s="37">
-        <v>108700</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4">
-      <c r="B94" s="23"/>
-      <c r="C94" t="s">
-        <v>61</v>
-      </c>
-      <c r="D94" s="37">
-        <v>-14800</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4">
-      <c r="B95" s="23"/>
-      <c r="C95" t="s">
-        <v>62</v>
-      </c>
-      <c r="D95" s="37">
-        <v>35300</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4">
-      <c r="B96" s="23"/>
-      <c r="C96" t="s">
-        <v>63</v>
-      </c>
-      <c r="D96" s="37">
-        <v>-8900</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4">
-      <c r="B97" s="23"/>
-      <c r="C97" t="s">
-        <v>64</v>
-      </c>
-      <c r="D97" s="37">
-        <v>-6000</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4">
-      <c r="B98" s="23"/>
-      <c r="C98" t="s">
-        <v>53</v>
-      </c>
-      <c r="D98" s="37">
-        <v>56100</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4">
-      <c r="B99" s="23"/>
-      <c r="C99" t="s">
-        <v>65</v>
-      </c>
-      <c r="D99" s="37">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4">
-      <c r="B100" s="23"/>
-      <c r="C100" t="s">
-        <v>66</v>
-      </c>
-      <c r="D100" s="37">
-        <v>-12700</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4">
-      <c r="B101" s="23"/>
-      <c r="C101" t="s">
-        <v>67</v>
-      </c>
-      <c r="D101" s="37">
-        <v>77700</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4">
-      <c r="B102" s="23"/>
-      <c r="C102" t="s">
-        <v>68</v>
-      </c>
-      <c r="D102" s="37">
-        <v>-13200</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4">
-      <c r="B103" s="23"/>
-      <c r="C103" t="s">
-        <v>69</v>
-      </c>
-      <c r="D103" s="37">
-        <v>-10500</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4">
-      <c r="B104" s="23"/>
-      <c r="C104" t="s">
-        <v>46</v>
-      </c>
-      <c r="D104" s="37">
-        <v>244900</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" s="23"/>
-      <c r="C105" t="s">
-        <v>48</v>
-      </c>
-      <c r="D105" s="37">
-        <v>67032</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" s="23"/>
-      <c r="D106" s="37"/>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107" s="23"/>
-      <c r="C107" t="s">
-        <v>24</v>
-      </c>
-      <c r="D107" s="37">
-        <v>712600</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" s="23"/>
-      <c r="C108" t="s">
-        <v>26</v>
-      </c>
-      <c r="D108" s="37">
-        <f>SUM(D91:D105)</f>
-        <v>570132</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" s="23"/>
-      <c r="C109" t="s">
-        <v>27</v>
-      </c>
-      <c r="D109" s="37">
-        <f>D107+D108</f>
-        <v>1282732</v>
-      </c>
-    </row>
-    <row r="110" ht="16.95" spans="2:4">
-      <c r="B110" s="41"/>
-      <c r="C110" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="D110" s="44">
-        <f>D109-D118</f>
-        <v>1219032</v>
-      </c>
-    </row>
-    <row r="112" ht="16.95"/>
-    <row r="113" spans="2:4">
-      <c r="B113" s="18">
-        <v>2020</v>
-      </c>
-      <c r="C113" s="19"/>
-      <c r="D113" s="36"/>
-    </row>
-    <row r="114" spans="2:4">
-      <c r="B114" s="23"/>
-      <c r="C114" t="s">
-        <v>58</v>
-      </c>
-      <c r="D114" s="37">
-        <v>49400</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4">
-      <c r="B115" s="23"/>
-      <c r="C115" t="s">
-        <v>59</v>
-      </c>
-      <c r="D115" s="37">
-        <v>64300</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4">
-      <c r="B116" s="23"/>
-      <c r="C116" t="s">
-        <v>70</v>
-      </c>
-      <c r="D116" s="37">
-        <v>-6000</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4">
-      <c r="B117" s="23"/>
-      <c r="D117" s="37"/>
-    </row>
-    <row r="118" spans="2:4">
-      <c r="B118" s="23"/>
-      <c r="C118" t="s">
-        <v>24</v>
-      </c>
-      <c r="D118" s="37">
-        <v>63700</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4">
-      <c r="B119" s="23"/>
-      <c r="C119" t="s">
-        <v>26</v>
-      </c>
-      <c r="D119" s="37">
-        <f>SUM(D114:D116)</f>
-        <v>107700</v>
-      </c>
-    </row>
-    <row r="120" ht="16.95" spans="2:4">
-      <c r="B120" s="41"/>
-      <c r="C120" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="D120" s="44">
-        <f>D118+D119</f>
-        <v>171400</v>
-      </c>
-    </row>
-    <row r="121" spans="4:4">
-      <c r="D121" s="28"/>
-    </row>
-    <row r="122" spans="4:4">
-      <c r="D122" s="28"/>
-    </row>
-    <row r="123" spans="4:4">
-      <c r="D123" s="28"/>
-    </row>
-    <row r="124" spans="4:4">
-      <c r="D124" s="28"/>
-    </row>
-    <row r="125" spans="4:4">
-      <c r="D125" s="28"/>
-    </row>
-    <row r="126" spans="4:4">
-      <c r="D126" s="28"/>
-    </row>
-    <row r="127" spans="4:4">
-      <c r="D127" s="28"/>
-    </row>
-    <row r="128" spans="4:4">
-      <c r="D128" s="28"/>
-    </row>
-    <row r="129" spans="4:4">
-      <c r="D129" s="28"/>
-    </row>
-    <row r="130" spans="4:4">
-      <c r="D130" s="28"/>
-    </row>
-    <row r="131" spans="4:4">
-      <c r="D131" s="28"/>
-    </row>
-    <row r="132" spans="4:4">
-      <c r="D132" s="28"/>
-    </row>
-    <row r="133" spans="4:4">
-      <c r="D133" s="28"/>
-    </row>
-    <row r="134" spans="4:4">
-      <c r="D134" s="28"/>
-    </row>
-    <row r="135" spans="4:4">
-      <c r="D135" s="28"/>
-    </row>
-    <row r="136" spans="4:4">
-      <c r="D136" s="28"/>
-    </row>
-    <row r="137" spans="4:4">
-      <c r="D137" s="28"/>
-    </row>
-    <row r="138" spans="4:4">
-      <c r="D138" s="28"/>
-    </row>
-    <row r="139" spans="4:4">
-      <c r="D139" s="28"/>
-    </row>
-    <row r="140" spans="4:4">
-      <c r="D140" s="28"/>
-    </row>
-    <row r="141" spans="4:4">
-      <c r="D141" s="28"/>
-    </row>
-    <row r="142" spans="4:4">
-      <c r="D142" s="28"/>
-    </row>
-    <row r="143" spans="4:4">
-      <c r="D143" s="28"/>
-    </row>
-    <row r="144" spans="4:4">
-      <c r="D144" s="28"/>
-    </row>
-    <row r="145" spans="4:4">
-      <c r="D145" s="28"/>
-    </row>
-    <row r="146" spans="4:4">
-      <c r="D146" s="28"/>
-    </row>
-    <row r="147" spans="4:4">
-      <c r="D147" s="28"/>
-    </row>
-    <row r="148" spans="4:4">
-      <c r="D148" s="28"/>
-    </row>
-    <row r="149" spans="4:4">
-      <c r="D149" s="28"/>
-    </row>
-    <row r="150" spans="4:4">
-      <c r="D150" s="28"/>
-    </row>
-    <row r="151" spans="4:4">
-      <c r="D151" s="28"/>
-    </row>
-    <row r="152" spans="4:4">
-      <c r="D152" s="28"/>
-    </row>
-    <row r="153" spans="4:4">
-      <c r="D153" s="28"/>
-    </row>
-    <row r="154" spans="4:4">
-      <c r="D154" s="28"/>
-    </row>
-    <row r="155" spans="4:4">
-      <c r="D155" s="28"/>
-    </row>
-    <row r="156" spans="4:4">
-      <c r="D156" s="28"/>
-    </row>
-    <row r="157" spans="4:4">
-      <c r="D157" s="28"/>
-    </row>
-    <row r="158" spans="4:4">
-      <c r="D158" s="28"/>
-    </row>
-    <row r="159" spans="4:4">
-      <c r="D159" s="28"/>
-    </row>
-    <row r="160" spans="4:4">
-      <c r="D160" s="28"/>
-    </row>
-    <row r="161" spans="4:4">
-      <c r="D161" s="28"/>
-    </row>
-    <row r="162" spans="4:4">
-      <c r="D162" s="28"/>
-    </row>
-    <row r="163" spans="4:4">
-      <c r="D163" s="28"/>
-    </row>
-    <row r="164" spans="4:4">
-      <c r="D164" s="28"/>
-    </row>
-    <row r="165" spans="4:4">
-      <c r="D165" s="28"/>
-    </row>
-    <row r="166" spans="4:4">
-      <c r="D166" s="28"/>
-    </row>
-    <row r="167" spans="4:4">
-      <c r="D167" s="28"/>
-    </row>
-    <row r="168" spans="4:4">
-      <c r="D168" s="28"/>
-    </row>
-    <row r="169" spans="4:4">
-      <c r="D169" s="28"/>
-    </row>
-    <row r="170" spans="4:4">
-      <c r="D170" s="28"/>
-    </row>
-    <row r="171" spans="4:4">
-      <c r="D171" s="28"/>
-    </row>
-    <row r="172" spans="4:4">
-      <c r="D172" s="28"/>
-    </row>
-    <row r="173" spans="4:4">
-      <c r="D173" s="28"/>
-    </row>
-    <row r="174" spans="4:4">
-      <c r="D174" s="28"/>
-    </row>
-    <row r="175" spans="4:4">
-      <c r="D175" s="28"/>
-    </row>
-    <row r="176" spans="4:4">
-      <c r="D176" s="28"/>
-    </row>
-    <row r="177" spans="4:4">
-      <c r="D177" s="28"/>
-    </row>
-    <row r="178" spans="4:4">
-      <c r="D178" s="28"/>
-    </row>
-    <row r="179" spans="4:4">
-      <c r="D179" s="28"/>
-    </row>
-    <row r="180" spans="4:4">
-      <c r="D180" s="28"/>
-    </row>
-    <row r="181" spans="4:4">
-      <c r="D181" s="28"/>
-    </row>
-    <row r="182" spans="4:4">
-      <c r="D182" s="28"/>
-    </row>
-    <row r="183" spans="4:4">
-      <c r="D183" s="28"/>
-    </row>
-    <row r="184" spans="4:4">
-      <c r="D184" s="28"/>
-    </row>
-    <row r="185" spans="4:4">
-      <c r="D185" s="28"/>
-    </row>
-    <row r="186" spans="4:4">
-      <c r="D186" s="28"/>
-    </row>
-    <row r="187" spans="4:4">
-      <c r="D187" s="28"/>
-    </row>
-    <row r="188" spans="4:4">
-      <c r="D188" s="28"/>
-    </row>
-    <row r="189" spans="4:4">
-      <c r="D189" s="28"/>
-    </row>
-    <row r="190" spans="4:4">
-      <c r="D190" s="28"/>
-    </row>
-    <row r="191" spans="4:4">
-      <c r="D191" s="28"/>
-    </row>
-    <row r="192" spans="4:4">
-      <c r="D192" s="28"/>
-    </row>
-    <row r="193" spans="4:4">
-      <c r="D193" s="28"/>
-    </row>
-    <row r="194" spans="4:4">
-      <c r="D194" s="28"/>
-    </row>
-    <row r="195" spans="4:4">
-      <c r="D195" s="28"/>
-    </row>
-    <row r="196" spans="4:4">
-      <c r="D196" s="28"/>
-    </row>
-    <row r="197" spans="4:4">
-      <c r="D197" s="28"/>
-    </row>
-    <row r="198" spans="4:4">
-      <c r="D198" s="28"/>
-    </row>
-    <row r="199" spans="4:4">
-      <c r="D199" s="28"/>
-    </row>
-    <row r="200" spans="4:4">
-      <c r="D200" s="28"/>
-    </row>
-    <row r="201" spans="4:4">
-      <c r="D201" s="28"/>
-    </row>
-    <row r="202" spans="4:4">
-      <c r="D202" s="28"/>
-    </row>
-    <row r="203" spans="4:4">
-      <c r="D203" s="28"/>
-    </row>
-    <row r="204" spans="4:4">
-      <c r="D204" s="28"/>
-    </row>
-    <row r="205" spans="4:4">
-      <c r="D205" s="28"/>
-    </row>
-    <row r="206" spans="4:4">
-      <c r="D206" s="28"/>
-    </row>
-    <row r="207" spans="4:4">
-      <c r="D207" s="28"/>
-    </row>
-    <row r="208" spans="4:4">
-      <c r="D208" s="28"/>
-    </row>
-    <row r="209" spans="4:4">
-      <c r="D209" s="28"/>
-    </row>
-    <row r="210" spans="4:4">
-      <c r="D210" s="28"/>
-    </row>
-    <row r="211" spans="4:4">
-      <c r="D211" s="46"/>
-    </row>
-    <row r="212" spans="4:4">
-      <c r="D212" s="46"/>
-    </row>
-    <row r="213" spans="4:4">
-      <c r="D213" s="46"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="B1:O131"/>
@@ -6917,7 +4812,7 @@
       <c r="D1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="10">
+      <c r="E1" s="13">
         <v>0.03</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -6939,13 +4834,13 @@
       <c r="D2" t="s">
         <v>74</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="14">
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="16">
         <v>0.03</v>
       </c>
       <c r="J2" s="1"/>
@@ -6975,7 +4870,7 @@
         <v>300000</v>
       </c>
       <c r="J3" s="1"/>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="17" t="s">
         <v>79</v>
       </c>
       <c r="L3" s="1">
@@ -7001,7 +4896,7 @@
         <v>25000</v>
       </c>
       <c r="J4" s="1"/>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="17" t="s">
         <v>82</v>
       </c>
       <c r="L4" s="1">
@@ -7017,7 +4912,7 @@
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="17" t="s">
         <v>83</v>
       </c>
       <c r="L5" s="1">
@@ -7051,7 +4946,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="17" t="s">
         <v>84</v>
       </c>
       <c r="L6" s="1">
@@ -7080,7 +4975,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="15" t="s">
+      <c r="K7" s="17" t="s">
         <v>85</v>
       </c>
       <c r="L7" s="1">
@@ -7107,7 +5002,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="18" t="s">
         <v>86</v>
       </c>
       <c r="L8" s="1">
@@ -7264,7 +5159,7 @@
       <c r="O13" s="1"/>
     </row>
     <row r="14" spans="2:15">
-      <c r="B14" s="10">
+      <c r="B14" s="13">
         <f>B13/E12</f>
         <v>0.602467102785908</v>
       </c>
@@ -7450,7 +5345,7 @@
     </row>
     <row r="25" spans="3:15">
       <c r="C25" s="1"/>
-      <c r="D25" s="13"/>
+      <c r="D25" s="15"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -8736,10 +6631,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
-  <dimension ref="B2:O187"/>
+  <dimension ref="B2:R187"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="16.2"/>
   <cols>
     <col min="2" max="2" width="9.66666666666667" style="3" customWidth="1"/>
@@ -8754,6 +6649,8 @@
     <col min="13" max="13" width="9.66666666666667" style="4"/>
     <col min="14" max="14" width="9.44444444444444" style="1"/>
     <col min="15" max="15" width="8.88888888888889" style="1"/>
+    <col min="17" max="17" width="15"/>
+    <col min="18" max="18" width="12.8888888888889"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3">
@@ -8764,7 +6661,7 @@
         <v>6600000</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:18">
       <c r="B3" s="3">
         <v>45356</v>
       </c>
@@ -8783,10 +6680,16 @@
         <v>101</v>
       </c>
       <c r="J3" s="1">
-        <v>31961392</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10">
+        <v>33451393</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R3" s="10">
+        <v>17571458</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18">
       <c r="B4" s="3">
         <v>45382</v>
       </c>
@@ -8802,13 +6705,22 @@
         <v>0.0599474266391099</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J4" s="1">
         <v>-7860000</v>
       </c>
-    </row>
-    <row r="5" spans="2:11">
+      <c r="K4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>105</v>
+      </c>
+      <c r="R4" s="10">
+        <v>6365389</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18">
       <c r="B5" s="3">
         <v>45412</v>
       </c>
@@ -8824,16 +6736,22 @@
         <v>-0.0388919287890977</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="J5" s="1">
         <v>5790000</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10">
+        <v>107</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>2</v>
+      </c>
+      <c r="R5" s="10">
+        <v>9139389</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18">
       <c r="B6" s="3">
         <v>45443</v>
       </c>
@@ -8854,8 +6772,15 @@
       <c r="J6" s="1">
         <v>-1342643</v>
       </c>
-    </row>
-    <row r="7" ht="16.95" spans="2:14">
+      <c r="Q6" t="s">
+        <v>108</v>
+      </c>
+      <c r="R6" s="10">
+        <f>SUM(R3:R5)</f>
+        <v>33076236</v>
+      </c>
+    </row>
+    <row r="7" ht="16.95" spans="2:18">
       <c r="B7" s="3">
         <v>45473</v>
       </c>
@@ -8871,15 +6796,22 @@
         <v>0.0852958051483765</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="J7" s="1">
-        <v>54842</v>
+        <v>29842</v>
       </c>
       <c r="M7" s="8"/>
       <c r="N7" s="9">
         <f>SUM(N8:N99)</f>
-        <v>0</v>
+        <v>-208000</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>110</v>
+      </c>
+      <c r="R7" s="10">
+        <f>SUM(R3:R5)+R3+R4</f>
+        <v>57013083</v>
       </c>
     </row>
     <row r="8" spans="2:15">
@@ -8898,18 +6830,24 @@
         <v>-0.0471663352257339</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J8" s="1">
         <f>N7</f>
-        <v>0</v>
+        <v>-208000</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="N8" s="1">
+        <v>-208000</v>
       </c>
       <c r="O8" s="4"/>
     </row>
-    <row r="9" spans="2:15">
+    <row r="9" spans="2:18">
       <c r="B9" s="3">
         <v>45535</v>
       </c>
@@ -8925,13 +6863,19 @@
         <v>-0.0242376362491937</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="J9" s="9"/>
       <c r="L9" s="4"/>
       <c r="O9" s="4"/>
-    </row>
-    <row r="10" spans="2:11">
+      <c r="Q9" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="10">
+        <v>43636</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18">
       <c r="B10" s="3">
         <v>45565</v>
       </c>
@@ -8947,18 +6891,24 @@
         <v>0.0264542637625841</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="J10" s="1">
         <f>SUM(J3:J9)</f>
-        <v>28603591</v>
+        <v>29860592</v>
       </c>
       <c r="K10" s="1">
         <f>J10-J5</f>
-        <v>22813591</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5">
+        <v>24070592</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>117</v>
+      </c>
+      <c r="R10" s="10">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18">
       <c r="B11" s="3">
         <v>45596</v>
       </c>
@@ -8973,8 +6923,19 @@
         <f t="shared" si="1"/>
         <v>0.0226648161548103</v>
       </c>
-    </row>
-    <row r="12" spans="2:5">
+      <c r="K11" s="1">
+        <f>K10-J4</f>
+        <v>31930592</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>118</v>
+      </c>
+      <c r="R11" s="11">
+        <f>(R10-R9)/R9</f>
+        <v>0.145842882024017</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18">
       <c r="B12" s="3">
         <v>45626</v>
       </c>
@@ -8989,8 +6950,15 @@
         <f t="shared" si="1"/>
         <v>0.0104930537929589</v>
       </c>
-    </row>
-    <row r="13" spans="2:9">
+      <c r="Q12" t="s">
+        <v>119</v>
+      </c>
+      <c r="R12" s="10">
+        <f>R7*R11</f>
+        <v>8314952.33779448</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18">
       <c r="B13" s="3">
         <v>45657</v>
       </c>
@@ -9006,6 +6974,13 @@
         <v>0.0499362179955973</v>
       </c>
       <c r="I13"/>
+      <c r="Q13" t="s">
+        <v>120</v>
+      </c>
+      <c r="R13" s="10">
+        <f>J10+R12</f>
+        <v>38175544.3377945</v>
+      </c>
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="3">
@@ -9040,7 +7015,7 @@
         <v>-0.150456622797108</v>
       </c>
     </row>
-    <row r="16" spans="2:5">
+    <row r="16" spans="2:18">
       <c r="B16" s="3">
         <v>45749</v>
       </c>
@@ -9055,6 +7030,9 @@
         <f t="shared" si="1"/>
         <v>0.0541905290226416</v>
       </c>
+      <c r="R16">
+        <v>38419</v>
+      </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="3">
@@ -9072,7 +7050,7 @@
         <v>-0.0650245063155781</v>
       </c>
     </row>
-    <row r="18" spans="2:5">
+    <row r="18" spans="2:18">
       <c r="B18" s="3">
         <v>45806</v>
       </c>
@@ -9087,6 +7065,7 @@
         <f t="shared" si="1"/>
         <v>0.0600088161780572</v>
       </c>
+      <c r="R18" s="12"/>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="3">
@@ -9270,15 +7249,15 @@
       </c>
       <c r="C30" s="1">
         <f>J10</f>
-        <v>28603591</v>
+        <v>29860592</v>
       </c>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>2899051</v>
+        <v>4156052</v>
       </c>
       <c r="E30" s="6">
         <f t="shared" si="1"/>
-        <v>0.112783617213146</v>
+        <v>0.161685523257759</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -10880,7 +8859,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr/>
   <dimension ref="C1:G19"/>
@@ -10892,10 +8871,10 @@
   <sheetData>
     <row r="1" spans="4:5">
       <c r="D1" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="3:4">
